--- a/LineClass/levels_pub.xlsx
+++ b/LineClass/levels_pub.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NIST\ASD\Pr\Pr3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E3826E-6BDD-44A0-A51F-4DA62DE0FCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A526BD-E163-4603-8974-96EC9BBEB39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2460" windowWidth="42315" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="47115" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
   </bookViews>
   <sheets>
     <sheet name="levels_pub" sheetId="1" r:id="rId1"/>
@@ -3592,6 +3592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S1037"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3675,7 +3676,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3748,7 +3749,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3812,7 +3813,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3903,7 +3904,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3944,7 +3945,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4035,7 +4036,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4085,7 +4086,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4185,7 +4186,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4217,7 +4218,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4326,7 +4327,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4358,7 +4359,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4408,7 +4409,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4508,7 +4509,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -4549,7 +4550,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4590,7 +4591,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -4631,7 +4632,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4681,7 +4682,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4731,7 +4732,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -4781,7 +4782,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -4831,7 +4832,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -4954,7 +4955,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -4986,7 +4987,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -5068,7 +5069,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -5159,7 +5160,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -5209,7 +5210,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -5309,7 +5310,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -5359,7 +5360,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -5409,7 +5410,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -5501,7 +5502,7 @@
       </c>
       <c r="S42"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -5551,7 +5552,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -5651,7 +5652,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -5701,7 +5702,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -5751,7 +5752,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -5801,7 +5802,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -5851,7 +5852,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -5901,7 +5902,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -5951,7 +5952,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -6001,7 +6002,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -6051,7 +6052,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -6142,7 +6143,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -6234,7 +6235,7 @@
       </c>
       <c r="S57"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -6293,7 +6294,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -6343,7 +6344,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -6443,7 +6444,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -6502,7 +6503,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -6552,7 +6553,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -6661,7 +6662,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -6761,7 +6762,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -6861,7 +6862,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -6911,7 +6912,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -6961,7 +6962,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -7011,7 +7012,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -7053,7 +7054,7 @@
       </c>
       <c r="S73"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -7103,7 +7104,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -7203,7 +7204,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -7253,7 +7254,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -7303,7 +7304,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -7444,7 +7445,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -7503,7 +7504,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -7553,7 +7554,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -7653,7 +7654,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -7703,7 +7704,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -7753,7 +7754,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -7803,7 +7804,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -7853,7 +7854,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -7903,7 +7904,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -7953,7 +7954,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -8044,7 +8045,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -8094,7 +8095,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -8144,7 +8145,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -8194,7 +8195,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -8235,7 +8236,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -8285,7 +8286,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -8335,7 +8336,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -8385,7 +8386,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -8494,7 +8495,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -8536,7 +8537,7 @@
       </c>
       <c r="S103"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -8586,7 +8587,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -8636,7 +8637,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -8686,7 +8687,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -8736,7 +8737,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -8786,7 +8787,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -8836,7 +8837,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -8886,7 +8887,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -8937,7 +8938,7 @@
       </c>
       <c r="S111"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -8969,7 +8970,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -9019,7 +9020,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -9069,7 +9070,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -9111,7 +9112,7 @@
       </c>
       <c r="S115"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -9161,7 +9162,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -9203,7 +9204,7 @@
       </c>
       <c r="S117"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -9245,7 +9246,7 @@
       </c>
       <c r="S118"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -9295,7 +9296,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -9345,7 +9346,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -9445,7 +9446,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -9495,7 +9496,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -9545,7 +9546,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -9645,7 +9646,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -9687,7 +9688,7 @@
       </c>
       <c r="S127"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -9737,7 +9738,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -9779,7 +9780,7 @@
       </c>
       <c r="S129"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -9829,7 +9830,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -9871,7 +9872,7 @@
       </c>
       <c r="S131"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -9921,7 +9922,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -9971,7 +9972,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -10030,7 +10031,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -10080,7 +10081,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -10130,7 +10131,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -10189,7 +10190,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -10231,7 +10232,7 @@
       </c>
       <c r="S138"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -10273,7 +10274,7 @@
       </c>
       <c r="S139"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -10323,7 +10324,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -10373,7 +10374,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -10424,7 +10425,7 @@
       </c>
       <c r="S142"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -10474,7 +10475,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -10524,7 +10525,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -10574,7 +10575,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -10624,7 +10625,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -10774,7 +10775,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -10824,7 +10825,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -10883,7 +10884,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -10933,7 +10934,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -10983,7 +10984,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -11083,7 +11084,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -11133,7 +11134,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -11183,7 +11184,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -11233,7 +11234,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -11274,7 +11275,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -11324,7 +11325,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -11374,7 +11375,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -11424,7 +11425,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -11474,7 +11475,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -11524,7 +11525,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -11574,7 +11575,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -11624,7 +11625,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -11674,7 +11675,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -11724,7 +11725,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -11766,7 +11767,7 @@
       </c>
       <c r="S169"/>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -11866,7 +11867,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -11916,7 +11917,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -11958,7 +11959,7 @@
       </c>
       <c r="S173"/>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -12008,7 +12009,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -12050,7 +12051,7 @@
       </c>
       <c r="S175"/>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -12100,7 +12101,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -12150,7 +12151,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -12200,7 +12201,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -12250,7 +12251,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -12292,7 +12293,7 @@
       </c>
       <c r="S180"/>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -12351,7 +12352,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -12401,7 +12402,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -12451,7 +12452,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -12493,7 +12494,7 @@
       </c>
       <c r="S184"/>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -12543,7 +12544,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -12593,7 +12594,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>16</v>
       </c>
@@ -12635,7 +12636,7 @@
       </c>
       <c r="S187"/>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>16</v>
       </c>
@@ -12676,7 +12677,7 @@
         <v>1.1559999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -12717,7 +12718,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -12767,7 +12768,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>16</v>
       </c>
@@ -12817,7 +12818,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -12867,7 +12868,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>16</v>
       </c>
@@ -12917,7 +12918,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -12967,7 +12968,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -13017,7 +13018,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -13059,7 +13060,7 @@
       </c>
       <c r="S196"/>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -13109,7 +13110,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -13150,7 +13151,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -13200,7 +13201,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -13242,7 +13243,7 @@
       </c>
       <c r="S200"/>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -13292,7 +13293,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -13334,7 +13335,7 @@
       </c>
       <c r="S202"/>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -13376,7 +13377,7 @@
       </c>
       <c r="S203"/>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -13408,7 +13409,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -13459,7 +13460,7 @@
       </c>
       <c r="S205"/>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -13509,7 +13510,7 @@
         <v>1.1870000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -13541,7 +13542,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -13591,7 +13592,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -13633,7 +13634,7 @@
       </c>
       <c r="S209"/>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -13675,7 +13676,7 @@
       </c>
       <c r="S210"/>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -13716,7 +13717,7 @@
         <v>1.282</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -13816,7 +13817,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -13858,7 +13859,7 @@
       </c>
       <c r="S214"/>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -13908,7 +13909,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -13950,7 +13951,7 @@
       </c>
       <c r="S216"/>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -14000,7 +14001,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -14042,7 +14043,7 @@
       </c>
       <c r="S218"/>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -14084,7 +14085,7 @@
       </c>
       <c r="S219"/>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -14134,7 +14135,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -14176,7 +14177,7 @@
       </c>
       <c r="S221"/>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -14226,7 +14227,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -14268,7 +14269,7 @@
       </c>
       <c r="S223"/>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -14310,7 +14311,7 @@
       </c>
       <c r="S224"/>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -14352,7 +14353,7 @@
       </c>
       <c r="S225"/>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -14402,7 +14403,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -14452,7 +14453,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -14494,7 +14495,7 @@
       </c>
       <c r="S228"/>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -14536,7 +14537,7 @@
       </c>
       <c r="S229"/>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -14578,7 +14579,7 @@
       </c>
       <c r="S230"/>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -14619,7 +14620,7 @@
         <v>1.143</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -14652,7 +14653,7 @@
       </c>
       <c r="S232"/>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -14702,7 +14703,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -14752,7 +14753,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -14793,7 +14794,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -14843,7 +14844,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -14893,7 +14894,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -14943,7 +14944,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -14993,7 +14994,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -15043,7 +15044,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -15093,7 +15094,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -15143,7 +15144,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -15193,7 +15194,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -15243,7 +15244,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -15293,7 +15294,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -15343,7 +15344,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -15393,7 +15394,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -15443,7 +15444,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -15476,7 +15477,7 @@
       </c>
       <c r="S249"/>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -15526,7 +15527,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -15576,7 +15577,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -15626,7 +15627,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -15676,7 +15677,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -15726,7 +15727,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -15767,7 +15768,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -15817,7 +15818,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -15867,7 +15868,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -15967,7 +15968,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -16017,7 +16018,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -16067,7 +16068,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -16117,7 +16118,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -16167,7 +16168,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -16217,7 +16218,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -16276,7 +16277,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -16326,7 +16327,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -16376,7 +16377,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -16426,7 +16427,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -16485,7 +16486,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -16526,7 +16527,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -16576,7 +16577,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -16617,7 +16618,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -16649,7 +16650,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -16699,7 +16700,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -16749,7 +16750,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -16799,7 +16800,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -16858,7 +16859,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -16908,7 +16909,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -16958,7 +16959,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -17008,7 +17009,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -17058,7 +17059,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -17108,7 +17109,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -17158,7 +17159,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -17208,7 +17209,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -17258,7 +17259,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -17308,7 +17309,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -17358,7 +17359,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -17408,7 +17409,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -17458,7 +17459,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -17491,7 +17492,7 @@
       </c>
       <c r="S290"/>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -17541,7 +17542,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -17591,7 +17592,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -17641,7 +17642,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -17691,7 +17692,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -17735,7 +17736,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -17777,7 +17778,7 @@
       </c>
       <c r="S296"/>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -17819,7 +17820,7 @@
       </c>
       <c r="S297"/>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -17869,7 +17870,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -17919,7 +17920,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -17969,7 +17970,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -18011,7 +18012,7 @@
       </c>
       <c r="S301"/>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -18061,7 +18062,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -18111,7 +18112,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -18161,7 +18162,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -18211,7 +18212,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>16</v>
       </c>
@@ -18252,7 +18253,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -18302,7 +18303,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -18343,7 +18344,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -18393,7 +18394,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -18443,7 +18444,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>16</v>
       </c>
@@ -18493,7 +18494,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -18543,7 +18544,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -18593,7 +18594,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -18643,7 +18644,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -18685,7 +18686,7 @@
       </c>
       <c r="S315"/>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -18718,7 +18719,7 @@
       </c>
       <c r="S316"/>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -18750,7 +18751,7 @@
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -18792,7 +18793,7 @@
       </c>
       <c r="S318"/>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -18842,7 +18843,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -18866,7 +18867,7 @@
       </c>
       <c r="S320"/>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -18899,7 +18900,7 @@
       </c>
       <c r="S321"/>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>16</v>
       </c>
@@ -18958,7 +18959,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>16</v>
       </c>
@@ -19008,7 +19009,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>16</v>
       </c>
@@ -19058,7 +19059,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>16</v>
       </c>
@@ -19099,7 +19100,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>16</v>
       </c>
@@ -19149,7 +19150,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>16</v>
       </c>
@@ -19199,7 +19200,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>16</v>
       </c>
@@ -19249,7 +19250,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>16</v>
       </c>
@@ -19299,7 +19300,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>16</v>
       </c>
@@ -19349,7 +19350,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>16</v>
       </c>
@@ -19408,7 +19409,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>16</v>
       </c>
@@ -19449,7 +19450,7 @@
         <v>1.252</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>16</v>
       </c>
@@ -19491,7 +19492,7 @@
       </c>
       <c r="S333"/>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>16</v>
       </c>
@@ -19541,7 +19542,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>16</v>
       </c>
@@ -19591,7 +19592,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>16</v>
       </c>
@@ -19641,7 +19642,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>16</v>
       </c>
@@ -19691,7 +19692,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>16</v>
       </c>
@@ -19750,7 +19751,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>16</v>
       </c>
@@ -19800,7 +19801,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>16</v>
       </c>
@@ -19850,7 +19851,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>16</v>
       </c>
@@ -19883,7 +19884,7 @@
       </c>
       <c r="S341"/>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>16</v>
       </c>
@@ -19907,7 +19908,7 @@
       </c>
       <c r="S342"/>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>16</v>
       </c>
@@ -19940,7 +19941,7 @@
       </c>
       <c r="S343"/>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>16</v>
       </c>
@@ -19963,7 +19964,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>16</v>
       </c>
@@ -19996,7 +19997,7 @@
       </c>
       <c r="S345"/>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>16</v>
       </c>
@@ -20028,7 +20029,7 @@
         <v>1.1319999999999999</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -20070,7 +20071,7 @@
       </c>
       <c r="S347"/>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>16</v>
       </c>
@@ -20103,7 +20104,7 @@
       </c>
       <c r="S348"/>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>16</v>
       </c>
@@ -20153,7 +20154,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>16</v>
       </c>
@@ -20195,7 +20196,7 @@
       </c>
       <c r="S350"/>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>16</v>
       </c>
@@ -20245,7 +20246,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>16</v>
       </c>
@@ -20295,7 +20296,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>16</v>
       </c>
@@ -20345,7 +20346,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>16</v>
       </c>
@@ -20395,7 +20396,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>16</v>
       </c>
@@ -20445,7 +20446,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>16</v>
       </c>
@@ -20495,7 +20496,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>16</v>
       </c>
@@ -20545,7 +20546,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>16</v>
       </c>
@@ -20577,7 +20578,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>16</v>
       </c>
@@ -20636,7 +20637,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>16</v>
       </c>
@@ -20669,7 +20670,7 @@
       </c>
       <c r="S360"/>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>16</v>
       </c>
@@ -20719,7 +20720,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>16</v>
       </c>
@@ -20761,7 +20762,7 @@
       </c>
       <c r="S362"/>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>16</v>
       </c>
@@ -20811,7 +20812,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>16</v>
       </c>
@@ -20853,7 +20854,7 @@
       </c>
       <c r="S364"/>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>16</v>
       </c>
@@ -20886,7 +20887,7 @@
       </c>
       <c r="S365"/>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>16</v>
       </c>
@@ -20919,7 +20920,7 @@
       </c>
       <c r="S366"/>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>16</v>
       </c>
@@ -20952,7 +20953,7 @@
       </c>
       <c r="S367"/>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>16</v>
       </c>
@@ -20984,7 +20985,7 @@
         <v>1.075</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>16</v>
       </c>
@@ -21034,7 +21035,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>16</v>
       </c>
@@ -21084,7 +21085,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>16</v>
       </c>
@@ -21126,7 +21127,7 @@
       </c>
       <c r="S371"/>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>16</v>
       </c>
@@ -21176,7 +21177,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>16</v>
       </c>
@@ -21226,7 +21227,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>16</v>
       </c>
@@ -21276,7 +21277,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>16</v>
       </c>
@@ -21326,7 +21327,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>16</v>
       </c>
@@ -21376,7 +21377,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>16</v>
       </c>
@@ -21418,7 +21419,7 @@
       </c>
       <c r="S377"/>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>16</v>
       </c>
@@ -21468,7 +21469,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>16</v>
       </c>
@@ -21510,7 +21511,7 @@
       </c>
       <c r="S379"/>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>16</v>
       </c>
@@ -21552,7 +21553,7 @@
       </c>
       <c r="S380"/>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>16</v>
       </c>
@@ -21594,7 +21595,7 @@
       </c>
       <c r="S381"/>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>16</v>
       </c>
@@ -21635,7 +21636,7 @@
         <v>1.161</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>16</v>
       </c>
@@ -21677,7 +21678,7 @@
       </c>
       <c r="S383"/>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>16</v>
       </c>
@@ -21719,7 +21720,7 @@
       </c>
       <c r="S384"/>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>16</v>
       </c>
@@ -21761,7 +21762,7 @@
       </c>
       <c r="S385"/>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>16</v>
       </c>
@@ -21811,7 +21812,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>16</v>
       </c>
@@ -21861,7 +21862,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>16</v>
       </c>
@@ -21911,7 +21912,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>16</v>
       </c>
@@ -21961,7 +21962,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>16</v>
       </c>
@@ -22003,7 +22004,7 @@
       </c>
       <c r="S390"/>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>16</v>
       </c>
@@ -22045,7 +22046,7 @@
       </c>
       <c r="S391"/>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>16</v>
       </c>
@@ -22095,7 +22096,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>16</v>
       </c>
@@ -22137,7 +22138,7 @@
       </c>
       <c r="S393"/>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -22170,7 +22171,7 @@
       </c>
       <c r="S394"/>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>16</v>
       </c>
@@ -22212,7 +22213,7 @@
       </c>
       <c r="S395"/>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>16</v>
       </c>
@@ -22262,7 +22263,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>16</v>
       </c>
@@ -22306,7 +22307,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>16</v>
       </c>
@@ -22356,7 +22357,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>16</v>
       </c>
@@ -22388,7 +22389,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>16</v>
       </c>
@@ -22420,7 +22421,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>16</v>
       </c>
@@ -22470,7 +22471,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>16</v>
       </c>
@@ -22520,7 +22521,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>16</v>
       </c>
@@ -22570,7 +22571,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>16</v>
       </c>
@@ -22611,7 +22612,7 @@
         <v>1.1060000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>16</v>
       </c>
@@ -22661,7 +22662,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>16</v>
       </c>
@@ -22703,7 +22704,7 @@
       </c>
       <c r="S406"/>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>16</v>
       </c>
@@ -22745,7 +22746,7 @@
       </c>
       <c r="S407"/>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>16</v>
       </c>
@@ -22787,7 +22788,7 @@
       </c>
       <c r="S408"/>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>16</v>
       </c>
@@ -22837,7 +22838,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -22879,7 +22880,7 @@
       </c>
       <c r="S410"/>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>16</v>
       </c>
@@ -22929,7 +22930,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>16</v>
       </c>
@@ -22970,7 +22971,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -23012,7 +23013,7 @@
       </c>
       <c r="S413"/>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>16</v>
       </c>
@@ -23063,7 +23064,7 @@
       </c>
       <c r="S414"/>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>16</v>
       </c>
@@ -23105,7 +23106,7 @@
       </c>
       <c r="S415"/>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>16</v>
       </c>
@@ -23147,7 +23148,7 @@
       </c>
       <c r="S416"/>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>16</v>
       </c>
@@ -23197,7 +23198,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -23247,7 +23248,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -23288,7 +23289,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>16</v>
       </c>
@@ -23330,7 +23331,7 @@
       </c>
       <c r="S420"/>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>16</v>
       </c>
@@ -23380,7 +23381,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>16</v>
       </c>
@@ -23430,7 +23431,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -23472,7 +23473,7 @@
       </c>
       <c r="S423"/>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -23522,7 +23523,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -23564,7 +23565,7 @@
       </c>
       <c r="S425"/>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -23614,7 +23615,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -23656,7 +23657,7 @@
       </c>
       <c r="S427"/>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -23698,7 +23699,7 @@
       </c>
       <c r="S428"/>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -23748,7 +23749,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -23790,7 +23791,7 @@
       </c>
       <c r="S430"/>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -23823,7 +23824,7 @@
       </c>
       <c r="S431"/>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -23865,7 +23866,7 @@
       </c>
       <c r="S432"/>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -23907,7 +23908,7 @@
       </c>
       <c r="S433"/>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -23957,7 +23958,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -24008,7 +24009,7 @@
       </c>
       <c r="S435"/>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -24058,7 +24059,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -24091,7 +24092,7 @@
       </c>
       <c r="S437"/>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -24133,7 +24134,7 @@
       </c>
       <c r="S438"/>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -24175,7 +24176,7 @@
       </c>
       <c r="S439"/>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -24217,7 +24218,7 @@
       </c>
       <c r="S440"/>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -24241,7 +24242,7 @@
       </c>
       <c r="S441"/>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -24283,7 +24284,7 @@
       </c>
       <c r="S442"/>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -24307,7 +24308,7 @@
       </c>
       <c r="S443"/>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -24348,7 +24349,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -24398,7 +24399,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -24448,7 +24449,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -24490,7 +24491,7 @@
       </c>
       <c r="S447"/>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -24540,7 +24541,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -24581,7 +24582,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -24622,7 +24623,7 @@
         <v>1.3280000000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -24664,7 +24665,7 @@
       </c>
       <c r="S451"/>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -24706,7 +24707,7 @@
       </c>
       <c r="S452"/>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -24739,7 +24740,7 @@
       </c>
       <c r="S453"/>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -24789,7 +24790,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -24830,7 +24831,7 @@
         <v>1.046</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -24872,7 +24873,7 @@
       </c>
       <c r="S456"/>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -24922,7 +24923,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -24972,7 +24973,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -25022,7 +25023,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -25064,7 +25065,7 @@
       </c>
       <c r="S460"/>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -25106,7 +25107,7 @@
       </c>
       <c r="S461"/>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -25148,7 +25149,7 @@
       </c>
       <c r="S462"/>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -25198,7 +25199,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -25239,7 +25240,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -25280,7 +25281,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -25312,7 +25313,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -25354,7 +25355,7 @@
       </c>
       <c r="S467"/>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -25404,7 +25405,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -25445,7 +25446,7 @@
         <v>1.254</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -25495,7 +25496,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -25545,7 +25546,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -25587,7 +25588,7 @@
       </c>
       <c r="S472"/>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -25628,7 +25629,7 @@
         <v>0.73399999999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -25661,7 +25662,7 @@
       </c>
       <c r="S474"/>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -25703,7 +25704,7 @@
       </c>
       <c r="S475"/>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -25745,7 +25746,7 @@
       </c>
       <c r="S476"/>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -25795,7 +25796,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -25836,7 +25837,7 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -25877,7 +25878,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -25919,7 +25920,7 @@
       </c>
       <c r="S480"/>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -25961,7 +25962,7 @@
       </c>
       <c r="S481"/>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -26011,7 +26012,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>139</v>
       </c>
@@ -26070,7 +26071,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>139</v>
       </c>
@@ -26120,7 +26121,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>139</v>
       </c>
@@ -26170,7 +26171,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>139</v>
       </c>
@@ -26220,7 +26221,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>139</v>
       </c>
@@ -26279,7 +26280,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>139</v>
       </c>
@@ -26329,7 +26330,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>139</v>
       </c>
@@ -26379,7 +26380,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>139</v>
       </c>
@@ -26438,7 +26439,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>139</v>
       </c>
@@ -26488,7 +26489,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>139</v>
       </c>
@@ -26520,7 +26521,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>139</v>
       </c>
@@ -26579,7 +26580,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>139</v>
       </c>
@@ -26611,7 +26612,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>139</v>
       </c>
@@ -26661,7 +26662,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>139</v>
       </c>
@@ -26711,7 +26712,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>139</v>
       </c>
@@ -26761,7 +26762,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>139</v>
       </c>
@@ -26802,7 +26803,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>139</v>
       </c>
@@ -26852,7 +26853,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>139</v>
       </c>
@@ -26902,7 +26903,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>139</v>
       </c>
@@ -26952,7 +26953,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>139</v>
       </c>
@@ -27002,7 +27003,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>139</v>
       </c>
@@ -27034,7 +27035,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>139</v>
       </c>
@@ -27084,7 +27085,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>139</v>
       </c>
@@ -27184,7 +27185,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>139</v>
       </c>
@@ -27234,7 +27235,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>139</v>
       </c>
@@ -27284,7 +27285,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>139</v>
       </c>
@@ -27334,7 +27335,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>139</v>
       </c>
@@ -27384,7 +27385,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>139</v>
       </c>
@@ -27434,7 +27435,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>139</v>
       </c>
@@ -27534,7 +27535,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>139</v>
       </c>
@@ -27584,7 +27585,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>139</v>
       </c>
@@ -27634,7 +27635,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>139</v>
       </c>
@@ -27684,7 +27685,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>139</v>
       </c>
@@ -27734,7 +27735,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>139</v>
       </c>
@@ -27784,7 +27785,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>139</v>
       </c>
@@ -27834,7 +27835,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>139</v>
       </c>
@@ -27884,7 +27885,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>139</v>
       </c>
@@ -27943,7 +27944,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>139</v>
       </c>
@@ -27993,7 +27994,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>139</v>
       </c>
@@ -28043,7 +28044,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>139</v>
       </c>
@@ -28093,7 +28094,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>139</v>
       </c>
@@ -28143,7 +28144,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>139</v>
       </c>
@@ -28193,7 +28194,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>139</v>
       </c>
@@ -28243,7 +28244,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>139</v>
       </c>
@@ -28343,7 +28344,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>139</v>
       </c>
@@ -28393,7 +28394,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>139</v>
       </c>
@@ -28443,7 +28444,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>139</v>
       </c>
@@ -28502,7 +28503,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>139</v>
       </c>
@@ -28552,7 +28553,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>139</v>
       </c>
@@ -28602,7 +28603,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>139</v>
       </c>
@@ -28652,7 +28653,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>139</v>
       </c>
@@ -28702,7 +28703,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>139</v>
       </c>
@@ -28752,7 +28753,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>139</v>
       </c>
@@ -28802,7 +28803,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>139</v>
       </c>
@@ -28852,7 +28853,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>139</v>
       </c>
@@ -28902,7 +28903,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>139</v>
       </c>
@@ -28952,7 +28953,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>139</v>
       </c>
@@ -29002,7 +29003,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>139</v>
       </c>
@@ -29052,7 +29053,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>139</v>
       </c>
@@ -29102,7 +29103,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>139</v>
       </c>
@@ -29143,7 +29144,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>139</v>
       </c>
@@ -29193,7 +29194,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>139</v>
       </c>
@@ -29243,7 +29244,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>139</v>
       </c>
@@ -29293,7 +29294,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>139</v>
       </c>
@@ -29343,7 +29344,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>139</v>
       </c>
@@ -29393,7 +29394,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>139</v>
       </c>
@@ -29443,7 +29444,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>139</v>
       </c>
@@ -29493,7 +29494,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>139</v>
       </c>
@@ -29543,7 +29544,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>139</v>
       </c>
@@ -29593,7 +29594,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>139</v>
       </c>
@@ -29684,7 +29685,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>139</v>
       </c>
@@ -29734,7 +29735,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>139</v>
       </c>
@@ -29766,7 +29767,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>139</v>
       </c>
@@ -29807,7 +29808,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>139</v>
       </c>
@@ -29857,7 +29858,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>139</v>
       </c>
@@ -29939,7 +29940,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>139</v>
       </c>
@@ -29989,7 +29990,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="564" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>139</v>
       </c>
@@ -30039,7 +30040,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>139</v>
       </c>
@@ -30089,7 +30090,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>139</v>
       </c>
@@ -30139,7 +30140,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>139</v>
       </c>
@@ -30189,7 +30190,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>139</v>
       </c>
@@ -30239,7 +30240,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>139</v>
       </c>
@@ -30289,7 +30290,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>139</v>
       </c>
@@ -30339,7 +30340,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>139</v>
       </c>
@@ -30389,7 +30390,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>139</v>
       </c>
@@ -30430,7 +30431,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>139</v>
       </c>
@@ -30530,7 +30531,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>139</v>
       </c>
@@ -30580,7 +30581,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>139</v>
       </c>
@@ -30630,7 +30631,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>139</v>
       </c>
@@ -30689,7 +30690,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>139</v>
       </c>
@@ -30739,7 +30740,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>139</v>
       </c>
@@ -30839,7 +30840,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>139</v>
       </c>
@@ -30889,7 +30890,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>139</v>
       </c>
@@ -30939,7 +30940,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>139</v>
       </c>
@@ -30980,7 +30981,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>139</v>
       </c>
@@ -31030,7 +31031,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>139</v>
       </c>
@@ -31080,7 +31081,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>139</v>
       </c>
@@ -31130,7 +31131,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>139</v>
       </c>
@@ -31230,7 +31231,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>139</v>
       </c>
@@ -31280,7 +31281,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>139</v>
       </c>
@@ -31330,7 +31331,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>139</v>
       </c>
@@ -31380,7 +31381,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>139</v>
       </c>
@@ -31430,7 +31431,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>139</v>
       </c>
@@ -31480,7 +31481,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>139</v>
       </c>
@@ -31512,7 +31513,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="595" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>139</v>
       </c>
@@ -31553,7 +31554,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="596" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>139</v>
       </c>
@@ -31603,7 +31604,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>139</v>
       </c>
@@ -31653,7 +31654,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>139</v>
       </c>
@@ -31694,7 +31695,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>139</v>
       </c>
@@ -31744,7 +31745,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>139</v>
       </c>
@@ -31794,7 +31795,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="601" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>139</v>
       </c>
@@ -31826,7 +31827,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>139</v>
       </c>
@@ -31876,7 +31877,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>139</v>
       </c>
@@ -31959,7 +31960,7 @@
       </c>
       <c r="S604"/>
     </row>
-    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>139</v>
       </c>
@@ -32000,7 +32001,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>139</v>
       </c>
@@ -32032,7 +32033,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>139</v>
       </c>
@@ -32105,7 +32106,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>139</v>
       </c>
@@ -32146,7 +32147,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>139</v>
       </c>
@@ -32196,7 +32197,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>139</v>
       </c>
@@ -32238,7 +32239,7 @@
       </c>
       <c r="S611"/>
     </row>
-    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>139</v>
       </c>
@@ -32286,7 +32287,7 @@
       </c>
       <c r="S613"/>
     </row>
-    <row r="614" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>139</v>
       </c>
@@ -32327,7 +32328,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>139</v>
       </c>
@@ -32368,7 +32369,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>139</v>
       </c>
@@ -32409,7 +32410,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="617" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>139</v>
       </c>
@@ -32459,7 +32460,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>139</v>
       </c>
@@ -32500,7 +32501,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>139</v>
       </c>
@@ -32541,7 +32542,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>139</v>
       </c>
@@ -32591,7 +32592,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>139</v>
       </c>
@@ -32632,7 +32633,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="622" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>139</v>
       </c>
@@ -32682,7 +32683,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>139</v>
       </c>
@@ -32732,7 +32733,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="624" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>139</v>
       </c>
@@ -32773,7 +32774,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="625" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>139</v>
       </c>
@@ -32823,7 +32824,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="626" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>139</v>
       </c>
@@ -32855,7 +32856,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="627" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>139</v>
       </c>
@@ -32887,7 +32888,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="628" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>139</v>
       </c>
@@ -32928,7 +32929,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="629" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>139</v>
       </c>
@@ -32969,7 +32970,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="630" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>139</v>
       </c>
@@ -33010,7 +33011,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="631" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>139</v>
       </c>
@@ -33051,7 +33052,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>139</v>
       </c>
@@ -33092,7 +33093,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="633" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>139</v>
       </c>
@@ -33133,7 +33134,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>139</v>
       </c>
@@ -33183,7 +33184,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="635" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>139</v>
       </c>
@@ -33224,7 +33225,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>139</v>
       </c>
@@ -33274,7 +33275,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>139</v>
       </c>
@@ -33306,7 +33307,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="638" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>139</v>
       </c>
@@ -33338,7 +33339,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>139</v>
       </c>
@@ -33370,7 +33371,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>139</v>
       </c>
@@ -33411,7 +33412,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="641" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>139</v>
       </c>
@@ -33452,7 +33453,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="642" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>139</v>
       </c>
@@ -33493,7 +33494,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>139</v>
       </c>
@@ -33534,7 +33535,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>139</v>
       </c>
@@ -33575,7 +33576,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>139</v>
       </c>
@@ -33625,7 +33626,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="646" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>139</v>
       </c>
@@ -33666,7 +33667,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="647" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>139</v>
       </c>
@@ -33707,7 +33708,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>139</v>
       </c>
@@ -33739,7 +33740,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="649" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>139</v>
       </c>
@@ -33831,7 +33832,7 @@
       </c>
       <c r="S650"/>
     </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>139</v>
       </c>
@@ -33915,7 +33916,7 @@
       </c>
       <c r="S652"/>
     </row>
-    <row r="653" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>139</v>
       </c>
@@ -33957,7 +33958,7 @@
       </c>
       <c r="S653"/>
     </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>139</v>
       </c>
@@ -34007,7 +34008,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="655" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>139</v>
       </c>
@@ -34049,7 +34050,7 @@
       </c>
       <c r="S655"/>
     </row>
-    <row r="656" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>139</v>
       </c>
@@ -34099,7 +34100,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="657" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>139</v>
       </c>
@@ -34149,7 +34150,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="658" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>139</v>
       </c>
@@ -34199,7 +34200,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="659" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>139</v>
       </c>
@@ -34249,7 +34250,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="660" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>139</v>
       </c>
@@ -34299,7 +34300,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="661" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>139</v>
       </c>
@@ -34340,7 +34341,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="662" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>139</v>
       </c>
@@ -34372,7 +34373,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="663" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>139</v>
       </c>
@@ -34405,7 +34406,7 @@
       </c>
       <c r="S663"/>
     </row>
-    <row r="664" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>139</v>
       </c>
@@ -34446,7 +34447,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="665" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>139</v>
       </c>
@@ -34496,7 +34497,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="666" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>139</v>
       </c>
@@ -34546,7 +34547,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="667" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>139</v>
       </c>
@@ -34596,7 +34597,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="668" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>139</v>
       </c>
@@ -34646,7 +34647,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="669" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>139</v>
       </c>
@@ -34720,7 +34721,7 @@
       </c>
       <c r="S670"/>
     </row>
-    <row r="671" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>139</v>
       </c>
@@ -34762,7 +34763,7 @@
       </c>
       <c r="S671"/>
     </row>
-    <row r="672" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>139</v>
       </c>
@@ -34804,7 +34805,7 @@
       </c>
       <c r="S672"/>
     </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>139</v>
       </c>
@@ -34846,7 +34847,7 @@
       </c>
       <c r="S673"/>
     </row>
-    <row r="674" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>139</v>
       </c>
@@ -34896,7 +34897,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="675" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>139</v>
       </c>
@@ -34938,7 +34939,7 @@
       </c>
       <c r="S675"/>
     </row>
-    <row r="676" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>139</v>
       </c>
@@ -34980,7 +34981,7 @@
       </c>
       <c r="S676"/>
     </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>139</v>
       </c>
@@ -35030,7 +35031,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="678" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>139</v>
       </c>
@@ -35071,7 +35072,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="679" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>139</v>
       </c>
@@ -35113,7 +35114,7 @@
       </c>
       <c r="S679"/>
     </row>
-    <row r="680" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>139</v>
       </c>
@@ -35155,7 +35156,7 @@
       </c>
       <c r="S680"/>
     </row>
-    <row r="681" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>139</v>
       </c>
@@ -35197,7 +35198,7 @@
       </c>
       <c r="S681"/>
     </row>
-    <row r="682" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>139</v>
       </c>
@@ -35239,7 +35240,7 @@
       </c>
       <c r="S682"/>
     </row>
-    <row r="683" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>139</v>
       </c>
@@ -35289,7 +35290,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>139</v>
       </c>
@@ -35339,7 +35340,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="685" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>139</v>
       </c>
@@ -35372,7 +35373,7 @@
       </c>
       <c r="S685"/>
     </row>
-    <row r="686" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>139</v>
       </c>
@@ -35405,7 +35406,7 @@
       </c>
       <c r="S686"/>
     </row>
-    <row r="687" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>139</v>
       </c>
@@ -35438,7 +35439,7 @@
       </c>
       <c r="S687"/>
     </row>
-    <row r="688" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>139</v>
       </c>
@@ -35480,7 +35481,7 @@
       </c>
       <c r="S688"/>
     </row>
-    <row r="689" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>139</v>
       </c>
@@ -35522,7 +35523,7 @@
       </c>
       <c r="S689"/>
     </row>
-    <row r="690" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>139</v>
       </c>
@@ -35563,7 +35564,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="691" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>139</v>
       </c>
@@ -35605,7 +35606,7 @@
       </c>
       <c r="S691"/>
     </row>
-    <row r="692" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>139</v>
       </c>
@@ -35638,7 +35639,7 @@
       </c>
       <c r="S692"/>
     </row>
-    <row r="693" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>139</v>
       </c>
@@ -35688,7 +35689,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="694" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>139</v>
       </c>
@@ -35721,7 +35722,7 @@
       </c>
       <c r="S694"/>
     </row>
-    <row r="695" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>139</v>
       </c>
@@ -35763,7 +35764,7 @@
       </c>
       <c r="S695"/>
     </row>
-    <row r="696" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>139</v>
       </c>
@@ -35796,7 +35797,7 @@
       </c>
       <c r="S696"/>
     </row>
-    <row r="697" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>139</v>
       </c>
@@ -35855,7 +35856,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="698" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>139</v>
       </c>
@@ -35897,7 +35898,7 @@
       </c>
       <c r="S698"/>
     </row>
-    <row r="699" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>139</v>
       </c>
@@ -35956,7 +35957,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="700" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>139</v>
       </c>
@@ -35998,7 +35999,7 @@
       </c>
       <c r="S700"/>
     </row>
-    <row r="701" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>139</v>
       </c>
@@ -36040,7 +36041,7 @@
       </c>
       <c r="S701"/>
     </row>
-    <row r="702" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>139</v>
       </c>
@@ -36082,7 +36083,7 @@
       </c>
       <c r="S702"/>
     </row>
-    <row r="703" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>139</v>
       </c>
@@ -36124,7 +36125,7 @@
       </c>
       <c r="S703"/>
     </row>
-    <row r="704" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>139</v>
       </c>
@@ -36166,7 +36167,7 @@
       </c>
       <c r="S704"/>
     </row>
-    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>139</v>
       </c>
@@ -36208,7 +36209,7 @@
       </c>
       <c r="S705"/>
     </row>
-    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>139</v>
       </c>
@@ -36259,7 +36260,7 @@
       </c>
       <c r="S706"/>
     </row>
-    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>139</v>
       </c>
@@ -36343,7 +36344,7 @@
       </c>
       <c r="S708"/>
     </row>
-    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>139</v>
       </c>
@@ -36385,7 +36386,7 @@
       </c>
       <c r="S709"/>
     </row>
-    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>139</v>
       </c>
@@ -36427,7 +36428,7 @@
       </c>
       <c r="S710"/>
     </row>
-    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>139</v>
       </c>
@@ -36469,7 +36470,7 @@
       </c>
       <c r="S711"/>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>139</v>
       </c>
@@ -36553,7 +36554,7 @@
       </c>
       <c r="S713"/>
     </row>
-    <row r="714" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>139</v>
       </c>
@@ -36595,7 +36596,7 @@
       </c>
       <c r="S714"/>
     </row>
-    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>139</v>
       </c>
@@ -36637,7 +36638,7 @@
       </c>
       <c r="S715"/>
     </row>
-    <row r="716" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>139</v>
       </c>
@@ -36679,7 +36680,7 @@
       </c>
       <c r="S716"/>
     </row>
-    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>139</v>
       </c>
@@ -36721,7 +36722,7 @@
       </c>
       <c r="S717"/>
     </row>
-    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>139</v>
       </c>
@@ -36771,7 +36772,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>139</v>
       </c>
@@ -36855,7 +36856,7 @@
       </c>
       <c r="S720"/>
     </row>
-    <row r="721" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>139</v>
       </c>
@@ -36896,7 +36897,7 @@
         <v>0.88600000000000001</v>
       </c>
     </row>
-    <row r="722" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>139</v>
       </c>
@@ -36937,7 +36938,7 @@
         <v>1.175</v>
       </c>
     </row>
-    <row r="723" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>139</v>
       </c>
@@ -36978,7 +36979,7 @@
         <v>1.115</v>
       </c>
     </row>
-    <row r="724" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>139</v>
       </c>
@@ -37019,7 +37020,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="725" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>139</v>
       </c>
@@ -37060,7 +37061,7 @@
         <v>1.119</v>
       </c>
     </row>
-    <row r="726" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>139</v>
       </c>
@@ -37110,7 +37111,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="727" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>139</v>
       </c>
@@ -37151,7 +37152,7 @@
         <v>1.079</v>
       </c>
     </row>
-    <row r="728" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>139</v>
       </c>
@@ -37192,7 +37193,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="729" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>139</v>
       </c>
@@ -37233,7 +37234,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="730" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>139</v>
       </c>
@@ -37274,7 +37275,7 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="731" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>139</v>
       </c>
@@ -37315,7 +37316,7 @@
         <v>1.022</v>
       </c>
     </row>
-    <row r="732" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>139</v>
       </c>
@@ -37397,7 +37398,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="734" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>139</v>
       </c>
@@ -37438,7 +37439,7 @@
         <v>1.133</v>
       </c>
     </row>
-    <row r="735" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>139</v>
       </c>
@@ -37479,7 +37480,7 @@
         <v>0.92400000000000004</v>
       </c>
     </row>
-    <row r="736" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>139</v>
       </c>
@@ -37520,7 +37521,7 @@
         <v>0.746</v>
       </c>
     </row>
-    <row r="737" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>139</v>
       </c>
@@ -37570,7 +37571,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="738" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>139</v>
       </c>
@@ -37612,7 +37613,7 @@
       </c>
       <c r="S738"/>
     </row>
-    <row r="739" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>139</v>
       </c>
@@ -37654,7 +37655,7 @@
       </c>
       <c r="S739"/>
     </row>
-    <row r="740" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>139</v>
       </c>
@@ -37696,7 +37697,7 @@
       </c>
       <c r="S740"/>
     </row>
-    <row r="741" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>139</v>
       </c>
@@ -37738,7 +37739,7 @@
       </c>
       <c r="S741"/>
     </row>
-    <row r="742" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>139</v>
       </c>
@@ -37771,7 +37772,7 @@
       </c>
       <c r="S742"/>
     </row>
-    <row r="743" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>139</v>
       </c>
@@ -37813,7 +37814,7 @@
       </c>
       <c r="S743"/>
     </row>
-    <row r="744" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>139</v>
       </c>
@@ -37855,7 +37856,7 @@
       </c>
       <c r="S744"/>
     </row>
-    <row r="745" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>139</v>
       </c>
@@ -37897,7 +37898,7 @@
       </c>
       <c r="S745"/>
     </row>
-    <row r="746" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>139</v>
       </c>
@@ -37939,7 +37940,7 @@
       </c>
       <c r="S746"/>
     </row>
-    <row r="747" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>139</v>
       </c>
@@ -38023,7 +38024,7 @@
       </c>
       <c r="S748"/>
     </row>
-    <row r="749" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>139</v>
       </c>
@@ -38073,7 +38074,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="750" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>139</v>
       </c>
@@ -38115,7 +38116,7 @@
       </c>
       <c r="S750"/>
     </row>
-    <row r="751" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>139</v>
       </c>
@@ -38157,7 +38158,7 @@
       </c>
       <c r="S751"/>
     </row>
-    <row r="752" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>139</v>
       </c>
@@ -38240,7 +38241,7 @@
         <v>0.95099999999999996</v>
       </c>
     </row>
-    <row r="754" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>139</v>
       </c>
@@ -38281,7 +38282,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="755" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>139</v>
       </c>
@@ -38322,7 +38323,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="756" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>139</v>
       </c>
@@ -38363,7 +38364,7 @@
         <v>1.169</v>
       </c>
     </row>
-    <row r="757" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>139</v>
       </c>
@@ -38404,7 +38405,7 @@
         <v>1.0489999999999999</v>
       </c>
     </row>
-    <row r="758" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>139</v>
       </c>
@@ -38445,7 +38446,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="759" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>139</v>
       </c>
@@ -38486,7 +38487,7 @@
         <v>1.022</v>
       </c>
     </row>
-    <row r="760" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>139</v>
       </c>
@@ -38527,7 +38528,7 @@
         <v>1.419</v>
       </c>
     </row>
-    <row r="761" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>139</v>
       </c>
@@ -38568,7 +38569,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="762" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>139</v>
       </c>
@@ -38609,7 +38610,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="763" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>139</v>
       </c>
@@ -38650,7 +38651,7 @@
         <v>1.028</v>
       </c>
     </row>
-    <row r="764" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>139</v>
       </c>
@@ -38691,7 +38692,7 @@
         <v>1.613</v>
       </c>
     </row>
-    <row r="765" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>139</v>
       </c>
@@ -38732,7 +38733,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="766" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>139</v>
       </c>
@@ -38773,7 +38774,7 @@
         <v>1.042</v>
       </c>
     </row>
-    <row r="767" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>139</v>
       </c>
@@ -38814,7 +38815,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="768" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>139</v>
       </c>
@@ -38846,7 +38847,7 @@
         <v>1.0640000000000001</v>
       </c>
     </row>
-    <row r="769" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>139</v>
       </c>
@@ -39010,7 +39011,7 @@
         <v>0.96299999999999997</v>
       </c>
     </row>
-    <row r="773" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>139</v>
       </c>
@@ -39051,7 +39052,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="774" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>139</v>
       </c>
@@ -39092,7 +39093,7 @@
         <v>1.2450000000000001</v>
       </c>
     </row>
-    <row r="775" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>139</v>
       </c>
@@ -39133,7 +39134,7 @@
         <v>1.2250000000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>139</v>
       </c>
@@ -39183,7 +39184,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="777" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>139</v>
       </c>
@@ -39224,7 +39225,7 @@
         <v>1.2150000000000001</v>
       </c>
     </row>
-    <row r="778" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>139</v>
       </c>
@@ -39265,7 +39266,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="779" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>139</v>
       </c>
@@ -39297,7 +39298,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="780" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>139</v>
       </c>
@@ -39338,7 +39339,7 @@
         <v>1.264</v>
       </c>
     </row>
-    <row r="781" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>139</v>
       </c>
@@ -39379,7 +39380,7 @@
         <v>1.157</v>
       </c>
     </row>
-    <row r="782" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>139</v>
       </c>
@@ -39420,7 +39421,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="783" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>139</v>
       </c>
@@ -39461,7 +39462,7 @@
         <v>1.0609999999999999</v>
       </c>
     </row>
-    <row r="784" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>139</v>
       </c>
@@ -39511,7 +39512,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="785" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>139</v>
       </c>
@@ -39553,7 +39554,7 @@
       </c>
       <c r="S785"/>
     </row>
-    <row r="786" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>139</v>
       </c>
@@ -39577,7 +39578,7 @@
       </c>
       <c r="S786"/>
     </row>
-    <row r="787" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>139</v>
       </c>
@@ -39619,7 +39620,7 @@
       </c>
       <c r="S787"/>
     </row>
-    <row r="788" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>139</v>
       </c>
@@ -39703,7 +39704,7 @@
       </c>
       <c r="S789"/>
     </row>
-    <row r="790" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>139</v>
       </c>
@@ -39745,7 +39746,7 @@
       </c>
       <c r="S790"/>
     </row>
-    <row r="791" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>139</v>
       </c>
@@ -39838,7 +39839,7 @@
       </c>
       <c r="S792"/>
     </row>
-    <row r="793" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>139</v>
       </c>
@@ -39870,7 +39871,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="794" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>139</v>
       </c>
@@ -39912,7 +39913,7 @@
       </c>
       <c r="S794"/>
     </row>
-    <row r="795" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>139</v>
       </c>
@@ -39954,7 +39955,7 @@
       </c>
       <c r="S795"/>
     </row>
-    <row r="796" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>139</v>
       </c>
@@ -39996,7 +39997,7 @@
       </c>
       <c r="S796"/>
     </row>
-    <row r="797" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>139</v>
       </c>
@@ -40038,7 +40039,7 @@
       </c>
       <c r="S797"/>
     </row>
-    <row r="798" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>139</v>
       </c>
@@ -40080,7 +40081,7 @@
       </c>
       <c r="S798"/>
     </row>
-    <row r="799" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>139</v>
       </c>
@@ -40122,7 +40123,7 @@
       </c>
       <c r="S799"/>
     </row>
-    <row r="800" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>139</v>
       </c>
@@ -40164,7 +40165,7 @@
       </c>
       <c r="S800"/>
     </row>
-    <row r="801" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>139</v>
       </c>
@@ -40206,7 +40207,7 @@
       </c>
       <c r="S801"/>
     </row>
-    <row r="802" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>139</v>
       </c>
@@ -40248,7 +40249,7 @@
       </c>
       <c r="S802"/>
     </row>
-    <row r="803" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>139</v>
       </c>
@@ -40299,7 +40300,7 @@
       </c>
       <c r="S803"/>
     </row>
-    <row r="804" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>139</v>
       </c>
@@ -40331,7 +40332,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="805" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>139</v>
       </c>
@@ -40373,7 +40374,7 @@
       </c>
       <c r="S805"/>
     </row>
-    <row r="806" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>139</v>
       </c>
@@ -40415,7 +40416,7 @@
       </c>
       <c r="S806"/>
     </row>
-    <row r="807" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>139</v>
       </c>
@@ -40499,7 +40500,7 @@
       </c>
       <c r="S808"/>
     </row>
-    <row r="809" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>139</v>
       </c>
@@ -40541,7 +40542,7 @@
       </c>
       <c r="S809"/>
     </row>
-    <row r="810" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>139</v>
       </c>
@@ -40583,7 +40584,7 @@
       </c>
       <c r="S810"/>
     </row>
-    <row r="811" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>139</v>
       </c>
@@ -40667,7 +40668,7 @@
       </c>
       <c r="S812"/>
     </row>
-    <row r="813" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>139</v>
       </c>
@@ -40709,7 +40710,7 @@
       </c>
       <c r="S813"/>
     </row>
-    <row r="814" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>139</v>
       </c>
@@ -40751,7 +40752,7 @@
       </c>
       <c r="S814"/>
     </row>
-    <row r="815" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>139</v>
       </c>
@@ -40801,7 +40802,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="816" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>139</v>
       </c>
@@ -40843,7 +40844,7 @@
       </c>
       <c r="S816"/>
     </row>
-    <row r="817" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>139</v>
       </c>
@@ -40885,7 +40886,7 @@
       </c>
       <c r="S817"/>
     </row>
-    <row r="818" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>139</v>
       </c>
@@ -40927,7 +40928,7 @@
       </c>
       <c r="S818"/>
     </row>
-    <row r="819" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>139</v>
       </c>
@@ -40969,7 +40970,7 @@
       </c>
       <c r="S819"/>
     </row>
-    <row r="820" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>139</v>
       </c>
@@ -41011,7 +41012,7 @@
       </c>
       <c r="S820"/>
     </row>
-    <row r="821" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>139</v>
       </c>
@@ -41053,7 +41054,7 @@
       </c>
       <c r="S821"/>
     </row>
-    <row r="822" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>139</v>
       </c>
@@ -41095,7 +41096,7 @@
       </c>
       <c r="S822"/>
     </row>
-    <row r="823" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>139</v>
       </c>
@@ -41137,7 +41138,7 @@
       </c>
       <c r="S823"/>
     </row>
-    <row r="824" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>139</v>
       </c>
@@ -41179,7 +41180,7 @@
       </c>
       <c r="S824"/>
     </row>
-    <row r="825" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>139</v>
       </c>
@@ -41221,7 +41222,7 @@
       </c>
       <c r="S825"/>
     </row>
-    <row r="826" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>139</v>
       </c>
@@ -41305,7 +41306,7 @@
       </c>
       <c r="S827"/>
     </row>
-    <row r="828" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>139</v>
       </c>
@@ -41346,7 +41347,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="829" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>139</v>
       </c>
@@ -41388,7 +41389,7 @@
       </c>
       <c r="S829"/>
     </row>
-    <row r="830" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>139</v>
       </c>
@@ -41429,7 +41430,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="831" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>139</v>
       </c>
@@ -41471,7 +41472,7 @@
       </c>
       <c r="S831"/>
     </row>
-    <row r="832" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>139</v>
       </c>
@@ -41521,7 +41522,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="833" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>139</v>
       </c>
@@ -41563,7 +41564,7 @@
       </c>
       <c r="S833"/>
     </row>
-    <row r="834" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>139</v>
       </c>
@@ -41605,7 +41606,7 @@
       </c>
       <c r="S834"/>
     </row>
-    <row r="835" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>139</v>
       </c>
@@ -41638,7 +41639,7 @@
       </c>
       <c r="S835"/>
     </row>
-    <row r="836" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>139</v>
       </c>
@@ -41680,7 +41681,7 @@
       </c>
       <c r="S836"/>
     </row>
-    <row r="837" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>139</v>
       </c>
@@ -41721,7 +41722,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="838" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>139</v>
       </c>
@@ -41771,7 +41772,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="839" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>139</v>
       </c>
@@ -41813,7 +41814,7 @@
       </c>
       <c r="S839"/>
     </row>
-    <row r="840" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>139</v>
       </c>
@@ -41854,7 +41855,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="841" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>139</v>
       </c>
@@ -41896,7 +41897,7 @@
       </c>
       <c r="S841"/>
     </row>
-    <row r="842" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>139</v>
       </c>
@@ -41938,7 +41939,7 @@
       </c>
       <c r="S842"/>
     </row>
-    <row r="843" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>139</v>
       </c>
@@ -41980,7 +41981,7 @@
       </c>
       <c r="S843"/>
     </row>
-    <row r="844" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>139</v>
       </c>
@@ -42022,7 +42023,7 @@
       </c>
       <c r="S844"/>
     </row>
-    <row r="845" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>139</v>
       </c>
@@ -42064,7 +42065,7 @@
       </c>
       <c r="S845"/>
     </row>
-    <row r="846" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>139</v>
       </c>
@@ -42106,7 +42107,7 @@
       </c>
       <c r="S846"/>
     </row>
-    <row r="847" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>139</v>
       </c>
@@ -42148,7 +42149,7 @@
       </c>
       <c r="S847"/>
     </row>
-    <row r="848" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>139</v>
       </c>
@@ -42240,7 +42241,7 @@
       </c>
       <c r="S849"/>
     </row>
-    <row r="850" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>139</v>
       </c>
@@ -42290,7 +42291,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="851" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>139</v>
       </c>
@@ -42332,7 +42333,7 @@
       </c>
       <c r="S851"/>
     </row>
-    <row r="852" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>139</v>
       </c>
@@ -42383,7 +42384,7 @@
       </c>
       <c r="S852"/>
     </row>
-    <row r="853" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>139</v>
       </c>
@@ -42425,7 +42426,7 @@
       </c>
       <c r="S853"/>
     </row>
-    <row r="854" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>139</v>
       </c>
@@ -42467,7 +42468,7 @@
       </c>
       <c r="S854"/>
     </row>
-    <row r="855" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>139</v>
       </c>
@@ -42508,7 +42509,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="856" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>139</v>
       </c>
@@ -42550,7 +42551,7 @@
       </c>
       <c r="S856"/>
     </row>
-    <row r="857" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>139</v>
       </c>
@@ -42574,7 +42575,7 @@
       </c>
       <c r="S857"/>
     </row>
-    <row r="858" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>139</v>
       </c>
@@ -42598,7 +42599,7 @@
       </c>
       <c r="S858"/>
     </row>
-    <row r="859" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>139</v>
       </c>
@@ -42648,7 +42649,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="860" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>139</v>
       </c>
@@ -42690,7 +42691,7 @@
       </c>
       <c r="S860"/>
     </row>
-    <row r="861" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>139</v>
       </c>
@@ -42732,7 +42733,7 @@
       </c>
       <c r="S861"/>
     </row>
-    <row r="862" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>139</v>
       </c>
@@ -42774,7 +42775,7 @@
       </c>
       <c r="S862"/>
     </row>
-    <row r="863" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>139</v>
       </c>
@@ -42816,7 +42817,7 @@
       </c>
       <c r="S863"/>
     </row>
-    <row r="864" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>139</v>
       </c>
@@ -42858,7 +42859,7 @@
       </c>
       <c r="S864"/>
     </row>
-    <row r="865" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>139</v>
       </c>
@@ -42900,7 +42901,7 @@
       </c>
       <c r="S865"/>
     </row>
-    <row r="866" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>139</v>
       </c>
@@ -42984,7 +42985,7 @@
       </c>
       <c r="S867"/>
     </row>
-    <row r="868" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>139</v>
       </c>
@@ -43016,7 +43017,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="869" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>139</v>
       </c>
@@ -43048,7 +43049,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="870" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>139</v>
       </c>
@@ -43090,7 +43091,7 @@
       </c>
       <c r="S870"/>
     </row>
-    <row r="871" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>139</v>
       </c>
@@ -43141,7 +43142,7 @@
       </c>
       <c r="S871"/>
     </row>
-    <row r="872" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>139</v>
       </c>
@@ -43183,7 +43184,7 @@
       </c>
       <c r="S872"/>
     </row>
-    <row r="873" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>139</v>
       </c>
@@ -43216,7 +43217,7 @@
       </c>
       <c r="S873"/>
     </row>
-    <row r="874" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>139</v>
       </c>
@@ -43249,7 +43250,7 @@
       </c>
       <c r="S874"/>
     </row>
-    <row r="875" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>139</v>
       </c>
@@ -43282,7 +43283,7 @@
       </c>
       <c r="S875"/>
     </row>
-    <row r="876" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>139</v>
       </c>
@@ -43324,7 +43325,7 @@
       </c>
       <c r="S876"/>
     </row>
-    <row r="877" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>139</v>
       </c>
@@ -43357,7 +43358,7 @@
       </c>
       <c r="S877"/>
     </row>
-    <row r="878" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>139</v>
       </c>
@@ -43381,7 +43382,7 @@
       </c>
       <c r="S878"/>
     </row>
-    <row r="879" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>139</v>
       </c>
@@ -43423,7 +43424,7 @@
       </c>
       <c r="S879"/>
     </row>
-    <row r="880" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>139</v>
       </c>
@@ -43456,7 +43457,7 @@
       </c>
       <c r="S880"/>
     </row>
-    <row r="881" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>139</v>
       </c>
@@ -43506,7 +43507,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="882" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>139</v>
       </c>
@@ -43547,7 +43548,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="883" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>139</v>
       </c>
@@ -43588,7 +43589,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="884" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>139</v>
       </c>
@@ -43638,7 +43639,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="885" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>139</v>
       </c>
@@ -43679,7 +43680,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="886" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>139</v>
       </c>
@@ -43720,7 +43721,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="887" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>139</v>
       </c>
@@ -43761,7 +43762,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="888" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>139</v>
       </c>
@@ -43794,7 +43795,7 @@
       </c>
       <c r="S888"/>
     </row>
-    <row r="889" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>139</v>
       </c>
@@ -43827,7 +43828,7 @@
       </c>
       <c r="S889"/>
     </row>
-    <row r="890" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>139</v>
       </c>
@@ -43868,7 +43869,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="891" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>139</v>
       </c>
@@ -43909,7 +43910,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="892" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>139</v>
       </c>
@@ -43942,7 +43943,7 @@
       </c>
       <c r="S892"/>
     </row>
-    <row r="893" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>139</v>
       </c>
@@ -43983,7 +43984,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="894" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>139</v>
       </c>
@@ -44024,7 +44025,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="895" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>139</v>
       </c>
@@ -44065,7 +44066,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="896" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>139</v>
       </c>
@@ -44148,7 +44149,7 @@
       </c>
       <c r="S897"/>
     </row>
-    <row r="898" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>139</v>
       </c>
@@ -44231,7 +44232,7 @@
       </c>
       <c r="S899"/>
     </row>
-    <row r="900" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>139</v>
       </c>
@@ -44273,7 +44274,7 @@
       </c>
       <c r="S900"/>
     </row>
-    <row r="901" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>139</v>
       </c>
@@ -44357,7 +44358,7 @@
       </c>
       <c r="S902"/>
     </row>
-    <row r="903" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>139</v>
       </c>
@@ -44399,7 +44400,7 @@
       </c>
       <c r="S903"/>
     </row>
-    <row r="904" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>139</v>
       </c>
@@ -44474,7 +44475,7 @@
       </c>
       <c r="S905"/>
     </row>
-    <row r="906" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>139</v>
       </c>
@@ -44516,7 +44517,7 @@
       </c>
       <c r="S906"/>
     </row>
-    <row r="907" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>139</v>
       </c>
@@ -44558,7 +44559,7 @@
       </c>
       <c r="S907"/>
     </row>
-    <row r="908" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>139</v>
       </c>
@@ -44600,7 +44601,7 @@
       </c>
       <c r="S908"/>
     </row>
-    <row r="909" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>139</v>
       </c>
@@ -44642,7 +44643,7 @@
       </c>
       <c r="S909"/>
     </row>
-    <row r="910" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>139</v>
       </c>
@@ -44684,7 +44685,7 @@
       </c>
       <c r="S910"/>
     </row>
-    <row r="911" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>139</v>
       </c>
@@ -44726,7 +44727,7 @@
       </c>
       <c r="S911"/>
     </row>
-    <row r="912" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>139</v>
       </c>
@@ -44758,7 +44759,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="913" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>139</v>
       </c>
@@ -44800,7 +44801,7 @@
       </c>
       <c r="S913"/>
     </row>
-    <row r="914" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>139</v>
       </c>
@@ -44866,7 +44867,7 @@
       </c>
       <c r="S915"/>
     </row>
-    <row r="916" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>139</v>
       </c>
@@ -44908,7 +44909,7 @@
       </c>
       <c r="S916"/>
     </row>
-    <row r="917" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>139</v>
       </c>
@@ -44941,7 +44942,7 @@
       </c>
       <c r="S917"/>
     </row>
-    <row r="918" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>139</v>
       </c>
@@ -44982,7 +44983,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="919" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>139</v>
       </c>
@@ -45024,7 +45025,7 @@
       </c>
       <c r="S919"/>
     </row>
-    <row r="920" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>139</v>
       </c>
@@ -45057,7 +45058,7 @@
       </c>
       <c r="S920"/>
     </row>
-    <row r="921" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>139</v>
       </c>
@@ -45099,7 +45100,7 @@
       </c>
       <c r="S921"/>
     </row>
-    <row r="922" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>139</v>
       </c>
@@ -45141,7 +45142,7 @@
       </c>
       <c r="S922"/>
     </row>
-    <row r="923" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>139</v>
       </c>
@@ -45183,7 +45184,7 @@
       </c>
       <c r="S923"/>
     </row>
-    <row r="924" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>139</v>
       </c>
@@ -45225,7 +45226,7 @@
       </c>
       <c r="S924"/>
     </row>
-    <row r="925" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>139</v>
       </c>
@@ -45267,7 +45268,7 @@
       </c>
       <c r="S925"/>
     </row>
-    <row r="926" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>139</v>
       </c>
@@ -45300,7 +45301,7 @@
       </c>
       <c r="S926"/>
     </row>
-    <row r="927" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>139</v>
       </c>
@@ -45332,7 +45333,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="928" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>139</v>
       </c>
@@ -45364,7 +45365,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="929" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>139</v>
       </c>
@@ -45396,7 +45397,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="930" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>139</v>
       </c>
@@ -45428,7 +45429,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="931" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>139</v>
       </c>
@@ -45460,7 +45461,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="932" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>139</v>
       </c>
@@ -45492,7 +45493,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="933" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>139</v>
       </c>
@@ -45524,7 +45525,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="934" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>139</v>
       </c>
@@ -45556,7 +45557,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="935" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>139</v>
       </c>
@@ -45598,7 +45599,7 @@
       </c>
       <c r="S935"/>
     </row>
-    <row r="936" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>139</v>
       </c>
@@ -45631,7 +45632,7 @@
       </c>
       <c r="S936"/>
     </row>
-    <row r="937" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>139</v>
       </c>
@@ -45705,7 +45706,7 @@
       </c>
       <c r="S938"/>
     </row>
-    <row r="939" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>139</v>
       </c>
@@ -45747,7 +45748,7 @@
       </c>
       <c r="S939"/>
     </row>
-    <row r="940" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>139</v>
       </c>
@@ -45789,7 +45790,7 @@
       </c>
       <c r="S940"/>
     </row>
-    <row r="941" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>139</v>
       </c>
@@ -45821,7 +45822,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="942" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>139</v>
       </c>
@@ -45871,7 +45872,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="943" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>139</v>
       </c>
@@ -45903,7 +45904,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="944" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>139</v>
       </c>
@@ -45935,7 +45936,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="945" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>139</v>
       </c>
@@ -45976,7 +45977,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="946" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>139</v>
       </c>
@@ -46017,7 +46018,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="947" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>139</v>
       </c>
@@ -46059,7 +46060,7 @@
       </c>
       <c r="S947"/>
     </row>
-    <row r="948" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>139</v>
       </c>
@@ -46134,7 +46135,7 @@
       </c>
       <c r="S949"/>
     </row>
-    <row r="950" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>139</v>
       </c>
@@ -46176,7 +46177,7 @@
       </c>
       <c r="S950"/>
     </row>
-    <row r="951" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>139</v>
       </c>
@@ -46209,7 +46210,7 @@
       </c>
       <c r="S951"/>
     </row>
-    <row r="952" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>139</v>
       </c>
@@ -46251,7 +46252,7 @@
       </c>
       <c r="S952"/>
     </row>
-    <row r="953" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>139</v>
       </c>
@@ -46293,7 +46294,7 @@
       </c>
       <c r="S953"/>
     </row>
-    <row r="954" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>139</v>
       </c>
@@ -46344,7 +46345,7 @@
       </c>
       <c r="S954"/>
     </row>
-    <row r="955" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>139</v>
       </c>
@@ -46386,7 +46387,7 @@
       </c>
       <c r="S955"/>
     </row>
-    <row r="956" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>139</v>
       </c>
@@ -46428,7 +46429,7 @@
       </c>
       <c r="S956"/>
     </row>
-    <row r="957" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>139</v>
       </c>
@@ -46470,7 +46471,7 @@
       </c>
       <c r="S957"/>
     </row>
-    <row r="958" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>139</v>
       </c>
@@ -46512,7 +46513,7 @@
       </c>
       <c r="S958"/>
     </row>
-    <row r="959" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>139</v>
       </c>
@@ -46554,7 +46555,7 @@
       </c>
       <c r="S959"/>
     </row>
-    <row r="960" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>139</v>
       </c>
@@ -46596,7 +46597,7 @@
       </c>
       <c r="S960"/>
     </row>
-    <row r="961" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>139</v>
       </c>
@@ -46638,7 +46639,7 @@
       </c>
       <c r="S961"/>
     </row>
-    <row r="962" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>139</v>
       </c>
@@ -46722,7 +46723,7 @@
       </c>
       <c r="S963"/>
     </row>
-    <row r="964" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>139</v>
       </c>
@@ -46764,7 +46765,7 @@
       </c>
       <c r="S964"/>
     </row>
-    <row r="965" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>139</v>
       </c>
@@ -46797,7 +46798,7 @@
       </c>
       <c r="S965"/>
     </row>
-    <row r="966" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>139</v>
       </c>
@@ -46838,7 +46839,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="967" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>139</v>
       </c>
@@ -46879,7 +46880,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="968" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>139</v>
       </c>
@@ -46920,7 +46921,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="969" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>139</v>
       </c>
@@ -46952,7 +46953,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="970" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>139</v>
       </c>
@@ -46993,7 +46994,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="971" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>139</v>
       </c>
@@ -47025,7 +47026,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="972" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>139</v>
       </c>
@@ -47057,7 +47058,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="973" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>139</v>
       </c>
@@ -47089,7 +47090,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="974" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>139</v>
       </c>
@@ -47121,7 +47122,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="975" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>139</v>
       </c>
@@ -47153,7 +47154,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="976" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>139</v>
       </c>
@@ -47185,7 +47186,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="977" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>139</v>
       </c>
@@ -47217,7 +47218,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="978" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>139</v>
       </c>
@@ -47249,7 +47250,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="979" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>139</v>
       </c>
@@ -47281,7 +47282,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="980" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>139</v>
       </c>
@@ -47305,7 +47306,7 @@
       </c>
       <c r="S980"/>
     </row>
-    <row r="981" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>139</v>
       </c>
@@ -47337,7 +47338,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="982" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>139</v>
       </c>
@@ -47361,7 +47362,7 @@
       </c>
       <c r="S982"/>
     </row>
-    <row r="983" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>139</v>
       </c>
@@ -47385,7 +47386,7 @@
       </c>
       <c r="S983"/>
     </row>
-    <row r="984" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>139</v>
       </c>
@@ -47427,7 +47428,7 @@
       </c>
       <c r="S984"/>
     </row>
-    <row r="985" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>139</v>
       </c>
@@ -47460,7 +47461,7 @@
       </c>
       <c r="S985"/>
     </row>
-    <row r="986" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>139</v>
       </c>
@@ -47493,7 +47494,7 @@
       </c>
       <c r="S986"/>
     </row>
-    <row r="987" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>139</v>
       </c>
@@ -47526,7 +47527,7 @@
       </c>
       <c r="S987"/>
     </row>
-    <row r="988" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>139</v>
       </c>
@@ -47559,7 +47560,7 @@
       </c>
       <c r="S988"/>
     </row>
-    <row r="989" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>139</v>
       </c>
@@ -47592,7 +47593,7 @@
       </c>
       <c r="S989"/>
     </row>
-    <row r="990" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>139</v>
       </c>
@@ -47625,7 +47626,7 @@
       </c>
       <c r="S990"/>
     </row>
-    <row r="991" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>139</v>
       </c>
@@ -47658,7 +47659,7 @@
       </c>
       <c r="S991"/>
     </row>
-    <row r="992" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>139</v>
       </c>
@@ -47691,7 +47692,7 @@
       </c>
       <c r="S992"/>
     </row>
-    <row r="993" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>139</v>
       </c>
@@ -47723,7 +47724,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="994" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>139</v>
       </c>
@@ -47764,7 +47765,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="995" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>139</v>
       </c>
@@ -47805,7 +47806,7 @@
         <v>1.0569999999999999</v>
       </c>
     </row>
-    <row r="996" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>139</v>
       </c>
@@ -47837,7 +47838,7 @@
         <v>1.0109999999999999</v>
       </c>
     </row>
-    <row r="997" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>139</v>
       </c>
@@ -47878,7 +47879,7 @@
         <v>0.99199999999999999</v>
       </c>
     </row>
-    <row r="998" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>139</v>
       </c>
@@ -47919,7 +47920,7 @@
         <v>1.073</v>
       </c>
     </row>
-    <row r="999" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>139</v>
       </c>
@@ -47951,7 +47952,7 @@
         <v>1.0669999999999999</v>
       </c>
     </row>
-    <row r="1000" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>139</v>
       </c>
@@ -47992,7 +47993,7 @@
         <v>1.1419999999999999</v>
       </c>
     </row>
-    <row r="1001" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>139</v>
       </c>
@@ -48024,7 +48025,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="1002" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>139</v>
       </c>
@@ -48065,7 +48066,7 @@
         <v>1.1739999999999999</v>
       </c>
     </row>
-    <row r="1003" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>139</v>
       </c>
@@ -48097,7 +48098,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="1004" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>139</v>
       </c>
@@ -48129,7 +48130,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="1005" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>139</v>
       </c>
@@ -48170,7 +48171,7 @@
         <v>1.0880000000000001</v>
       </c>
     </row>
-    <row r="1006" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>139</v>
       </c>
@@ -48202,7 +48203,7 @@
         <v>1.1259999999999999</v>
       </c>
     </row>
-    <row r="1007" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>139</v>
       </c>
@@ -48266,7 +48267,7 @@
         <v>0.51800000000000002</v>
       </c>
     </row>
-    <row r="1009" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>139</v>
       </c>
@@ -48289,7 +48290,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="1010" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>139</v>
       </c>
@@ -48312,7 +48313,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="1011" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>139</v>
       </c>
@@ -48335,7 +48336,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1012" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>139</v>
       </c>
@@ -48358,7 +48359,7 @@
         <v>1.1950000000000001</v>
       </c>
     </row>
-    <row r="1013" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>139</v>
       </c>
@@ -48381,7 +48382,7 @@
         <v>1.0980000000000001</v>
       </c>
     </row>
-    <row r="1014" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>139</v>
       </c>
@@ -48404,7 +48405,7 @@
         <v>1.159</v>
       </c>
     </row>
-    <row r="1015" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>139</v>
       </c>
@@ -48427,7 +48428,7 @@
         <v>0.877</v>
       </c>
     </row>
-    <row r="1016" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>139</v>
       </c>
@@ -48450,7 +48451,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="1017" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>139</v>
       </c>
@@ -48482,7 +48483,7 @@
         <v>1.123</v>
       </c>
     </row>
-    <row r="1018" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>139</v>
       </c>
@@ -48514,7 +48515,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1019" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>139</v>
       </c>
@@ -48537,7 +48538,7 @@
         <v>1.109</v>
       </c>
     </row>
-    <row r="1020" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>139</v>
       </c>
@@ -48569,7 +48570,7 @@
         <v>0.95699999999999996</v>
       </c>
     </row>
-    <row r="1021" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>139</v>
       </c>
@@ -48601,7 +48602,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="1022" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>139</v>
       </c>
@@ -48683,7 +48684,7 @@
         <v>2.1589999999999998</v>
       </c>
     </row>
-    <row r="1024" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>139</v>
       </c>
@@ -48766,7 +48767,7 @@
       </c>
       <c r="S1025"/>
     </row>
-    <row r="1026" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>139</v>
       </c>
@@ -48799,7 +48800,7 @@
       </c>
       <c r="S1026"/>
     </row>
-    <row r="1027" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>139</v>
       </c>
@@ -48841,7 +48842,7 @@
       </c>
       <c r="S1027"/>
     </row>
-    <row r="1028" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>139</v>
       </c>
@@ -48883,7 +48884,7 @@
       </c>
       <c r="S1028"/>
     </row>
-    <row r="1029" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>139</v>
       </c>
@@ -48925,7 +48926,7 @@
       </c>
       <c r="S1029"/>
     </row>
-    <row r="1030" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>139</v>
       </c>
@@ -48967,7 +48968,7 @@
       </c>
       <c r="S1030"/>
     </row>
-    <row r="1031" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>139</v>
       </c>
@@ -49009,7 +49010,7 @@
       </c>
       <c r="S1031"/>
     </row>
-    <row r="1032" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>139</v>
       </c>
@@ -49051,7 +49052,7 @@
       </c>
       <c r="S1032"/>
     </row>
-    <row r="1033" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>139</v>
       </c>
@@ -49093,7 +49094,7 @@
       </c>
       <c r="S1033"/>
     </row>
-    <row r="1034" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>139</v>
       </c>
@@ -49135,7 +49136,7 @@
       </c>
       <c r="S1034"/>
     </row>
-    <row r="1035" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>139</v>
       </c>
@@ -49177,7 +49178,7 @@
       </c>
       <c r="S1035"/>
     </row>
-    <row r="1036" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>139</v>
       </c>
@@ -49219,7 +49220,7 @@
       </c>
       <c r="S1036"/>
     </row>
-    <row r="1037" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>139</v>
       </c>
@@ -49270,7 +49271,18 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}"/>
+  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="e"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="16">
+      <filters>
+        <filter val="0.5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LineClass/levels_pub.xlsx
+++ b/LineClass/levels_pub.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A526BD-E163-4603-8974-96EC9BBEB39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF016F6-7F02-423B-B40B-A694DD697E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="47115" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="47115" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
   </bookViews>
   <sheets>
     <sheet name="levels_pub" sheetId="1" r:id="rId1"/>
@@ -3592,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
-  <sheetPr filterMode="1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S1037"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3676,7 +3676,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="S42"/>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="S57"/>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="S73"/>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -7995,7 +7995,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -8236,7 +8236,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="S103"/>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="S111"/>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="S115"/>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="S117"/>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="S118"/>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -9446,7 +9446,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="S127"/>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="S129"/>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="S131"/>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -9972,7 +9972,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="S138"/>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="S139"/>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="S142"/>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -10675,7 +10675,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -11575,7 +11575,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -11625,7 +11625,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="S169"/>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -11817,7 +11817,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="S173"/>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="S175"/>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="S180"/>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -12452,7 +12452,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="S184"/>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>16</v>
       </c>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="S187"/>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>16</v>
       </c>
@@ -12677,7 +12677,7 @@
         <v>1.1559999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>16</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>16</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -12968,7 +12968,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="S196"/>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -13110,7 +13110,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -13201,7 +13201,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="S200"/>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="S202"/>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="S203"/>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="S205"/>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>1.1870000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="S209"/>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="S210"/>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>1.282</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="S214"/>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="S216"/>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="S218"/>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -14085,7 +14085,7 @@
       </c>
       <c r="S219"/>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="S221"/>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="S223"/>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="S224"/>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -14353,7 +14353,7 @@
       </c>
       <c r="S225"/>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="S228"/>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="S229"/>
     </row>
-    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="S230"/>
     </row>
-    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -14620,7 +14620,7 @@
         <v>1.143</v>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="S232"/>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -14753,7 +14753,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -14944,7 +14944,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -15144,7 +15144,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -15194,7 +15194,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -15244,7 +15244,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -15344,7 +15344,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -15444,7 +15444,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="S249"/>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -15527,7 +15527,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -15627,7 +15627,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -15677,7 +15677,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -15918,7 +15918,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -15968,7 +15968,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -16018,7 +16018,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -16168,7 +16168,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -16327,7 +16327,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -16427,7 +16427,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -16486,7 +16486,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -16650,7 +16650,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -16750,7 +16750,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -16859,7 +16859,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -16959,7 +16959,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -17159,7 +17159,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="S290"/>
     </row>
-    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="S296"/>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -17820,7 +17820,7 @@
       </c>
       <c r="S297"/>
     </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -17920,7 +17920,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="S301"/>
     </row>
-    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -18112,7 +18112,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -18212,7 +18212,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>16</v>
       </c>
@@ -18253,7 +18253,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -18303,7 +18303,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -18344,7 +18344,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -18394,7 +18394,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>16</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="S315"/>
     </row>
-    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -18719,7 +18719,7 @@
       </c>
       <c r="S316"/>
     </row>
-    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -18751,7 +18751,7 @@
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="S318"/>
     </row>
-    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -18843,7 +18843,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="S320"/>
     </row>
-    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="S321"/>
     </row>
-    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>16</v>
       </c>
@@ -18959,7 +18959,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>16</v>
       </c>
@@ -19009,7 +19009,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>16</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>16</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>16</v>
       </c>
@@ -19150,7 +19150,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>16</v>
       </c>
@@ -19200,7 +19200,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>16</v>
       </c>
@@ -19250,7 +19250,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>16</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>16</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>16</v>
       </c>
@@ -19409,7 +19409,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>16</v>
       </c>
@@ -19450,7 +19450,7 @@
         <v>1.252</v>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>16</v>
       </c>
@@ -19492,7 +19492,7 @@
       </c>
       <c r="S333"/>
     </row>
-    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>16</v>
       </c>
@@ -19542,7 +19542,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>16</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>16</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>16</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>16</v>
       </c>
@@ -19751,7 +19751,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>16</v>
       </c>
@@ -19801,7 +19801,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>16</v>
       </c>
@@ -19851,7 +19851,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>16</v>
       </c>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="S341"/>
     </row>
-    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>16</v>
       </c>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="S342"/>
     </row>
-    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>16</v>
       </c>
@@ -19941,7 +19941,7 @@
       </c>
       <c r="S343"/>
     </row>
-    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>16</v>
       </c>
@@ -19964,7 +19964,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>16</v>
       </c>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="S345"/>
     </row>
-    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>16</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>1.1319999999999999</v>
       </c>
     </row>
-    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -20071,7 +20071,7 @@
       </c>
       <c r="S347"/>
     </row>
-    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>16</v>
       </c>
@@ -20104,7 +20104,7 @@
       </c>
       <c r="S348"/>
     </row>
-    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>16</v>
       </c>
@@ -20154,7 +20154,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>16</v>
       </c>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="S350"/>
     </row>
-    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>16</v>
       </c>
@@ -20246,7 +20246,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>16</v>
       </c>
@@ -20296,7 +20296,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>16</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>16</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>16</v>
       </c>
@@ -20446,7 +20446,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>16</v>
       </c>
@@ -20496,7 +20496,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>16</v>
       </c>
@@ -20546,7 +20546,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>16</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>16</v>
       </c>
@@ -20637,7 +20637,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>16</v>
       </c>
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S360"/>
     </row>
-    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>16</v>
       </c>
@@ -20720,7 +20720,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>16</v>
       </c>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S362"/>
     </row>
-    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>16</v>
       </c>
@@ -20812,7 +20812,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>16</v>
       </c>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="S364"/>
     </row>
-    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>16</v>
       </c>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="S365"/>
     </row>
-    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>16</v>
       </c>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="S366"/>
     </row>
-    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>16</v>
       </c>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="S367"/>
     </row>
-    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>16</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>1.075</v>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>16</v>
       </c>
@@ -21035,7 +21035,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>16</v>
       </c>
@@ -21085,7 +21085,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>16</v>
       </c>
@@ -21127,7 +21127,7 @@
       </c>
       <c r="S371"/>
     </row>
-    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>16</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>16</v>
       </c>
@@ -21227,7 +21227,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>16</v>
       </c>
@@ -21277,7 +21277,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>16</v>
       </c>
@@ -21327,7 +21327,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>16</v>
       </c>
@@ -21377,7 +21377,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>16</v>
       </c>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="S377"/>
     </row>
-    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>16</v>
       </c>
@@ -21469,7 +21469,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>16</v>
       </c>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="S379"/>
     </row>
-    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>16</v>
       </c>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="S380"/>
     </row>
-    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>16</v>
       </c>
@@ -21595,7 +21595,7 @@
       </c>
       <c r="S381"/>
     </row>
-    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>16</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>1.161</v>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>16</v>
       </c>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="S383"/>
     </row>
-    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>16</v>
       </c>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="S384"/>
     </row>
-    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>16</v>
       </c>
@@ -21762,7 +21762,7 @@
       </c>
       <c r="S385"/>
     </row>
-    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>16</v>
       </c>
@@ -21812,7 +21812,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>16</v>
       </c>
@@ -21862,7 +21862,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>16</v>
       </c>
@@ -21912,7 +21912,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>16</v>
       </c>
@@ -21962,7 +21962,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>16</v>
       </c>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="S390"/>
     </row>
-    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>16</v>
       </c>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="S391"/>
     </row>
-    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>16</v>
       </c>
@@ -22096,7 +22096,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>16</v>
       </c>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="S393"/>
     </row>
-    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -22171,7 +22171,7 @@
       </c>
       <c r="S394"/>
     </row>
-    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>16</v>
       </c>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="S395"/>
     </row>
-    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>16</v>
       </c>
@@ -22263,7 +22263,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>16</v>
       </c>
@@ -22307,7 +22307,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>16</v>
       </c>
@@ -22357,7 +22357,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>16</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>16</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>16</v>
       </c>
@@ -22471,7 +22471,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>16</v>
       </c>
@@ -22521,7 +22521,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>16</v>
       </c>
@@ -22571,7 +22571,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>16</v>
       </c>
@@ -22612,7 +22612,7 @@
         <v>1.1060000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>16</v>
       </c>
@@ -22662,7 +22662,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>16</v>
       </c>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="S406"/>
     </row>
-    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>16</v>
       </c>
@@ -22746,7 +22746,7 @@
       </c>
       <c r="S407"/>
     </row>
-    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>16</v>
       </c>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="S408"/>
     </row>
-    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>16</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -22880,7 +22880,7 @@
       </c>
       <c r="S410"/>
     </row>
-    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>16</v>
       </c>
@@ -22930,7 +22930,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>16</v>
       </c>
@@ -22971,7 +22971,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="S413"/>
     </row>
-    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>16</v>
       </c>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="S414"/>
     </row>
-    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>16</v>
       </c>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="S415"/>
     </row>
-    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>16</v>
       </c>
@@ -23148,7 +23148,7 @@
       </c>
       <c r="S416"/>
     </row>
-    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>16</v>
       </c>
@@ -23198,7 +23198,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -23248,7 +23248,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -23289,7 +23289,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>16</v>
       </c>
@@ -23331,7 +23331,7 @@
       </c>
       <c r="S420"/>
     </row>
-    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>16</v>
       </c>
@@ -23381,7 +23381,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>16</v>
       </c>
@@ -23431,7 +23431,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -23473,7 +23473,7 @@
       </c>
       <c r="S423"/>
     </row>
-    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -23523,7 +23523,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -23565,7 +23565,7 @@
       </c>
       <c r="S425"/>
     </row>
-    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -23615,7 +23615,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="S427"/>
     </row>
-    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -23699,7 +23699,7 @@
       </c>
       <c r="S428"/>
     </row>
-    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -23749,7 +23749,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -23791,7 +23791,7 @@
       </c>
       <c r="S430"/>
     </row>
-    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="S431"/>
     </row>
-    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -23866,7 +23866,7 @@
       </c>
       <c r="S432"/>
     </row>
-    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -23908,7 +23908,7 @@
       </c>
       <c r="S433"/>
     </row>
-    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -23958,7 +23958,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -24009,7 +24009,7 @@
       </c>
       <c r="S435"/>
     </row>
-    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -24059,7 +24059,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -24092,7 +24092,7 @@
       </c>
       <c r="S437"/>
     </row>
-    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="S438"/>
     </row>
-    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="S439"/>
     </row>
-    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="S440"/>
     </row>
-    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="S441"/>
     </row>
-    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -24284,7 +24284,7 @@
       </c>
       <c r="S442"/>
     </row>
-    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -24308,7 +24308,7 @@
       </c>
       <c r="S443"/>
     </row>
-    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -24349,7 +24349,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -24399,7 +24399,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -24449,7 +24449,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="S447"/>
     </row>
-    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -24541,7 +24541,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -24582,7 +24582,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -24623,7 +24623,7 @@
         <v>1.3280000000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -24665,7 +24665,7 @@
       </c>
       <c r="S451"/>
     </row>
-    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -24707,7 +24707,7 @@
       </c>
       <c r="S452"/>
     </row>
-    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -24740,7 +24740,7 @@
       </c>
       <c r="S453"/>
     </row>
-    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -24790,7 +24790,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -24831,7 +24831,7 @@
         <v>1.046</v>
       </c>
     </row>
-    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -24873,7 +24873,7 @@
       </c>
       <c r="S456"/>
     </row>
-    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -24923,7 +24923,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -24973,7 +24973,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -25023,7 +25023,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="S460"/>
     </row>
-    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -25107,7 +25107,7 @@
       </c>
       <c r="S461"/>
     </row>
-    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="S462"/>
     </row>
-    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -25199,7 +25199,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -25240,7 +25240,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -25281,7 +25281,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -25313,7 +25313,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -25355,7 +25355,7 @@
       </c>
       <c r="S467"/>
     </row>
-    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -25405,7 +25405,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -25446,7 +25446,7 @@
         <v>1.254</v>
       </c>
     </row>
-    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -25546,7 +25546,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -25588,7 +25588,7 @@
       </c>
       <c r="S472"/>
     </row>
-    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -25629,7 +25629,7 @@
         <v>0.73399999999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="S474"/>
     </row>
-    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -25704,7 +25704,7 @@
       </c>
       <c r="S475"/>
     </row>
-    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="S476"/>
     </row>
-    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -25796,7 +25796,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -25837,7 +25837,7 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -25878,7 +25878,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -25920,7 +25920,7 @@
       </c>
       <c r="S480"/>
     </row>
-    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -25962,7 +25962,7 @@
       </c>
       <c r="S481"/>
     </row>
-    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -26012,7 +26012,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>139</v>
       </c>
@@ -26071,7 +26071,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>139</v>
       </c>
@@ -26121,7 +26121,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>139</v>
       </c>
@@ -26171,7 +26171,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>139</v>
       </c>
@@ -26221,7 +26221,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>139</v>
       </c>
@@ -26280,7 +26280,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>139</v>
       </c>
@@ -26330,7 +26330,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>139</v>
       </c>
@@ -26380,7 +26380,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>139</v>
       </c>
@@ -26439,7 +26439,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>139</v>
       </c>
@@ -26489,7 +26489,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>139</v>
       </c>
@@ -26521,7 +26521,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>139</v>
       </c>
@@ -26580,7 +26580,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>139</v>
       </c>
@@ -26612,7 +26612,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>139</v>
       </c>
@@ -26662,7 +26662,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>139</v>
       </c>
@@ -26712,7 +26712,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>139</v>
       </c>
@@ -26762,7 +26762,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>139</v>
       </c>
@@ -26803,7 +26803,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>139</v>
       </c>
@@ -26853,7 +26853,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>139</v>
       </c>
@@ -26903,7 +26903,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>139</v>
       </c>
@@ -26953,7 +26953,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>139</v>
       </c>
@@ -27003,7 +27003,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>139</v>
       </c>
@@ -27035,7 +27035,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>139</v>
       </c>
@@ -27085,7 +27085,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>139</v>
       </c>
@@ -27185,7 +27185,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>139</v>
       </c>
@@ -27235,7 +27235,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>139</v>
       </c>
@@ -27285,7 +27285,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>139</v>
       </c>
@@ -27335,7 +27335,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>139</v>
       </c>
@@ -27385,7 +27385,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>139</v>
       </c>
@@ -27435,7 +27435,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>139</v>
       </c>
@@ -27535,7 +27535,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>139</v>
       </c>
@@ -27585,7 +27585,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>139</v>
       </c>
@@ -27635,7 +27635,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>139</v>
       </c>
@@ -27685,7 +27685,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>139</v>
       </c>
@@ -27735,7 +27735,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>139</v>
       </c>
@@ -27785,7 +27785,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>139</v>
       </c>
@@ -27835,7 +27835,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>139</v>
       </c>
@@ -27885,7 +27885,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>139</v>
       </c>
@@ -27944,7 +27944,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>139</v>
       </c>
@@ -27994,7 +27994,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>139</v>
       </c>
@@ -28044,7 +28044,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>139</v>
       </c>
@@ -28094,7 +28094,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>139</v>
       </c>
@@ -28144,7 +28144,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>139</v>
       </c>
@@ -28194,7 +28194,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>139</v>
       </c>
@@ -28244,7 +28244,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>139</v>
       </c>
@@ -28344,7 +28344,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>139</v>
       </c>
@@ -28394,7 +28394,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>139</v>
       </c>
@@ -28444,7 +28444,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>139</v>
       </c>
@@ -28503,7 +28503,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>139</v>
       </c>
@@ -28553,7 +28553,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>139</v>
       </c>
@@ -28603,7 +28603,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>139</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>139</v>
       </c>
@@ -28703,7 +28703,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>139</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>139</v>
       </c>
@@ -28803,7 +28803,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>139</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>139</v>
       </c>
@@ -28903,7 +28903,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>139</v>
       </c>
@@ -28953,7 +28953,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>139</v>
       </c>
@@ -29003,7 +29003,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>139</v>
       </c>
@@ -29053,7 +29053,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>139</v>
       </c>
@@ -29103,7 +29103,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>139</v>
       </c>
@@ -29144,7 +29144,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>139</v>
       </c>
@@ -29194,7 +29194,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>139</v>
       </c>
@@ -29244,7 +29244,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>139</v>
       </c>
@@ -29294,7 +29294,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>139</v>
       </c>
@@ -29344,7 +29344,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>139</v>
       </c>
@@ -29394,7 +29394,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>139</v>
       </c>
@@ -29444,7 +29444,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>139</v>
       </c>
@@ -29494,7 +29494,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>139</v>
       </c>
@@ -29544,7 +29544,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>139</v>
       </c>
@@ -29594,7 +29594,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>139</v>
       </c>
@@ -29685,7 +29685,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>139</v>
       </c>
@@ -29735,7 +29735,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>139</v>
       </c>
@@ -29767,7 +29767,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>139</v>
       </c>
@@ -29808,7 +29808,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>139</v>
       </c>
@@ -29858,7 +29858,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>139</v>
       </c>
@@ -29940,7 +29940,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>139</v>
       </c>
@@ -29990,7 +29990,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>139</v>
       </c>
@@ -30040,7 +30040,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>139</v>
       </c>
@@ -30090,7 +30090,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>139</v>
       </c>
@@ -30140,7 +30140,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>139</v>
       </c>
@@ -30190,7 +30190,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>139</v>
       </c>
@@ -30240,7 +30240,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>139</v>
       </c>
@@ -30290,7 +30290,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>139</v>
       </c>
@@ -30340,7 +30340,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>139</v>
       </c>
@@ -30390,7 +30390,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>139</v>
       </c>
@@ -30431,7 +30431,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>139</v>
       </c>
@@ -30531,7 +30531,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>139</v>
       </c>
@@ -30581,7 +30581,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>139</v>
       </c>
@@ -30631,7 +30631,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>139</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>139</v>
       </c>
@@ -30740,7 +30740,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>139</v>
       </c>
@@ -30840,7 +30840,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>139</v>
       </c>
@@ -30890,7 +30890,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>139</v>
       </c>
@@ -30940,7 +30940,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>139</v>
       </c>
@@ -30981,7 +30981,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>139</v>
       </c>
@@ -31031,7 +31031,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>139</v>
       </c>
@@ -31081,7 +31081,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>139</v>
       </c>
@@ -31131,7 +31131,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>139</v>
       </c>
@@ -31231,7 +31231,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>139</v>
       </c>
@@ -31281,7 +31281,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>139</v>
       </c>
@@ -31331,7 +31331,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>139</v>
       </c>
@@ -31381,7 +31381,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>139</v>
       </c>
@@ -31431,7 +31431,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>139</v>
       </c>
@@ -31481,7 +31481,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>139</v>
       </c>
@@ -31513,7 +31513,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>139</v>
       </c>
@@ -31554,7 +31554,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>139</v>
       </c>
@@ -31604,7 +31604,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>139</v>
       </c>
@@ -31654,7 +31654,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>139</v>
       </c>
@@ -31695,7 +31695,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>139</v>
       </c>
@@ -31745,7 +31745,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>139</v>
       </c>
@@ -31795,7 +31795,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>139</v>
       </c>
@@ -31827,7 +31827,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>139</v>
       </c>
@@ -31877,7 +31877,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>139</v>
       </c>
@@ -31960,7 +31960,7 @@
       </c>
       <c r="S604"/>
     </row>
-    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>139</v>
       </c>
@@ -32001,7 +32001,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>139</v>
       </c>
@@ -32033,7 +32033,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>139</v>
       </c>
@@ -32106,7 +32106,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>139</v>
       </c>
@@ -32147,7 +32147,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>139</v>
       </c>
@@ -32197,7 +32197,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>139</v>
       </c>
@@ -32239,7 +32239,7 @@
       </c>
       <c r="S611"/>
     </row>
-    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>139</v>
       </c>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="S613"/>
     </row>
-    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>139</v>
       </c>
@@ -32328,7 +32328,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>139</v>
       </c>
@@ -32369,7 +32369,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>139</v>
       </c>
@@ -32410,7 +32410,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>139</v>
       </c>
@@ -32460,7 +32460,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>139</v>
       </c>
@@ -32501,7 +32501,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>139</v>
       </c>
@@ -32542,7 +32542,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>139</v>
       </c>
@@ -32592,7 +32592,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>139</v>
       </c>
@@ -32633,7 +32633,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>139</v>
       </c>
@@ -32683,7 +32683,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>139</v>
       </c>
@@ -32733,7 +32733,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>139</v>
       </c>
@@ -32774,7 +32774,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>139</v>
       </c>
@@ -32824,7 +32824,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>139</v>
       </c>
@@ -32856,7 +32856,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>139</v>
       </c>
@@ -32888,7 +32888,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>139</v>
       </c>
@@ -32929,7 +32929,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>139</v>
       </c>
@@ -32970,7 +32970,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>139</v>
       </c>
@@ -33011,7 +33011,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>139</v>
       </c>
@@ -33052,7 +33052,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>139</v>
       </c>
@@ -33093,7 +33093,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>139</v>
       </c>
@@ -33134,7 +33134,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>139</v>
       </c>
@@ -33184,7 +33184,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>139</v>
       </c>
@@ -33225,7 +33225,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>139</v>
       </c>
@@ -33275,7 +33275,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>139</v>
       </c>
@@ -33307,7 +33307,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>139</v>
       </c>
@@ -33339,7 +33339,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>139</v>
       </c>
@@ -33371,7 +33371,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>139</v>
       </c>
@@ -33412,7 +33412,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>139</v>
       </c>
@@ -33453,7 +33453,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>139</v>
       </c>
@@ -33494,7 +33494,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>139</v>
       </c>
@@ -33535,7 +33535,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>139</v>
       </c>
@@ -33576,7 +33576,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>139</v>
       </c>
@@ -33626,7 +33626,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>139</v>
       </c>
@@ -33667,7 +33667,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>139</v>
       </c>
@@ -33708,7 +33708,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>139</v>
       </c>
@@ -33740,7 +33740,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>139</v>
       </c>
@@ -33832,7 +33832,7 @@
       </c>
       <c r="S650"/>
     </row>
-    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>139</v>
       </c>
@@ -33916,7 +33916,7 @@
       </c>
       <c r="S652"/>
     </row>
-    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>139</v>
       </c>
@@ -33958,7 +33958,7 @@
       </c>
       <c r="S653"/>
     </row>
-    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>139</v>
       </c>
@@ -34008,7 +34008,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>139</v>
       </c>
@@ -34050,7 +34050,7 @@
       </c>
       <c r="S655"/>
     </row>
-    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>139</v>
       </c>
@@ -34100,7 +34100,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>139</v>
       </c>
@@ -34150,7 +34150,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>139</v>
       </c>
@@ -34200,7 +34200,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>139</v>
       </c>
@@ -34250,7 +34250,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>139</v>
       </c>
@@ -34300,7 +34300,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>139</v>
       </c>
@@ -34341,7 +34341,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>139</v>
       </c>
@@ -34373,7 +34373,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>139</v>
       </c>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="S663"/>
     </row>
-    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>139</v>
       </c>
@@ -34447,7 +34447,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>139</v>
       </c>
@@ -34497,7 +34497,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>139</v>
       </c>
@@ -34547,7 +34547,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>139</v>
       </c>
@@ -34597,7 +34597,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>139</v>
       </c>
@@ -34647,7 +34647,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>139</v>
       </c>
@@ -34721,7 +34721,7 @@
       </c>
       <c r="S670"/>
     </row>
-    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>139</v>
       </c>
@@ -34763,7 +34763,7 @@
       </c>
       <c r="S671"/>
     </row>
-    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>139</v>
       </c>
@@ -34805,7 +34805,7 @@
       </c>
       <c r="S672"/>
     </row>
-    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>139</v>
       </c>
@@ -34847,7 +34847,7 @@
       </c>
       <c r="S673"/>
     </row>
-    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>139</v>
       </c>
@@ -34897,7 +34897,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>139</v>
       </c>
@@ -34939,7 +34939,7 @@
       </c>
       <c r="S675"/>
     </row>
-    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>139</v>
       </c>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="S676"/>
     </row>
-    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>139</v>
       </c>
@@ -35031,7 +35031,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>139</v>
       </c>
@@ -35072,7 +35072,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>139</v>
       </c>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="S679"/>
     </row>
-    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>139</v>
       </c>
@@ -35156,7 +35156,7 @@
       </c>
       <c r="S680"/>
     </row>
-    <row r="681" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>139</v>
       </c>
@@ -35198,7 +35198,7 @@
       </c>
       <c r="S681"/>
     </row>
-    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>139</v>
       </c>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="S682"/>
     </row>
-    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>139</v>
       </c>
@@ -35290,7 +35290,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>139</v>
       </c>
@@ -35340,7 +35340,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>139</v>
       </c>
@@ -35373,7 +35373,7 @@
       </c>
       <c r="S685"/>
     </row>
-    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>139</v>
       </c>
@@ -35406,7 +35406,7 @@
       </c>
       <c r="S686"/>
     </row>
-    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>139</v>
       </c>
@@ -35439,7 +35439,7 @@
       </c>
       <c r="S687"/>
     </row>
-    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>139</v>
       </c>
@@ -35481,7 +35481,7 @@
       </c>
       <c r="S688"/>
     </row>
-    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>139</v>
       </c>
@@ -35523,7 +35523,7 @@
       </c>
       <c r="S689"/>
     </row>
-    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>139</v>
       </c>
@@ -35564,7 +35564,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>139</v>
       </c>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="S691"/>
     </row>
-    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>139</v>
       </c>
@@ -35639,7 +35639,7 @@
       </c>
       <c r="S692"/>
     </row>
-    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>139</v>
       </c>
@@ -35689,7 +35689,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>139</v>
       </c>
@@ -35722,7 +35722,7 @@
       </c>
       <c r="S694"/>
     </row>
-    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>139</v>
       </c>
@@ -35764,7 +35764,7 @@
       </c>
       <c r="S695"/>
     </row>
-    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>139</v>
       </c>
@@ -35797,7 +35797,7 @@
       </c>
       <c r="S696"/>
     </row>
-    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>139</v>
       </c>
@@ -35856,7 +35856,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>139</v>
       </c>
@@ -35898,7 +35898,7 @@
       </c>
       <c r="S698"/>
     </row>
-    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>139</v>
       </c>
@@ -35957,7 +35957,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>139</v>
       </c>
@@ -35999,7 +35999,7 @@
       </c>
       <c r="S700"/>
     </row>
-    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>139</v>
       </c>
@@ -36041,7 +36041,7 @@
       </c>
       <c r="S701"/>
     </row>
-    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>139</v>
       </c>
@@ -36083,7 +36083,7 @@
       </c>
       <c r="S702"/>
     </row>
-    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>139</v>
       </c>
@@ -36125,7 +36125,7 @@
       </c>
       <c r="S703"/>
     </row>
-    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>139</v>
       </c>
@@ -36167,7 +36167,7 @@
       </c>
       <c r="S704"/>
     </row>
-    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>139</v>
       </c>
@@ -36209,7 +36209,7 @@
       </c>
       <c r="S705"/>
     </row>
-    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>139</v>
       </c>
@@ -36260,7 +36260,7 @@
       </c>
       <c r="S706"/>
     </row>
-    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>139</v>
       </c>
@@ -36344,7 +36344,7 @@
       </c>
       <c r="S708"/>
     </row>
-    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>139</v>
       </c>
@@ -36386,7 +36386,7 @@
       </c>
       <c r="S709"/>
     </row>
-    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>139</v>
       </c>
@@ -36428,7 +36428,7 @@
       </c>
       <c r="S710"/>
     </row>
-    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>139</v>
       </c>
@@ -36470,7 +36470,7 @@
       </c>
       <c r="S711"/>
     </row>
-    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>139</v>
       </c>
@@ -36554,7 +36554,7 @@
       </c>
       <c r="S713"/>
     </row>
-    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>139</v>
       </c>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S714"/>
     </row>
-    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>139</v>
       </c>
@@ -36638,7 +36638,7 @@
       </c>
       <c r="S715"/>
     </row>
-    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>139</v>
       </c>
@@ -36680,7 +36680,7 @@
       </c>
       <c r="S716"/>
     </row>
-    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>139</v>
       </c>
@@ -36722,7 +36722,7 @@
       </c>
       <c r="S717"/>
     </row>
-    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>139</v>
       </c>
@@ -36772,7 +36772,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>139</v>
       </c>
@@ -36856,7 +36856,7 @@
       </c>
       <c r="S720"/>
     </row>
-    <row r="721" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>139</v>
       </c>
@@ -36897,7 +36897,7 @@
         <v>0.88600000000000001</v>
       </c>
     </row>
-    <row r="722" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>139</v>
       </c>
@@ -36938,7 +36938,7 @@
         <v>1.175</v>
       </c>
     </row>
-    <row r="723" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>139</v>
       </c>
@@ -36979,7 +36979,7 @@
         <v>1.115</v>
       </c>
     </row>
-    <row r="724" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>139</v>
       </c>
@@ -37020,7 +37020,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="725" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>139</v>
       </c>
@@ -37061,7 +37061,7 @@
         <v>1.119</v>
       </c>
     </row>
-    <row r="726" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>139</v>
       </c>
@@ -37111,7 +37111,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="727" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>139</v>
       </c>
@@ -37152,7 +37152,7 @@
         <v>1.079</v>
       </c>
     </row>
-    <row r="728" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>139</v>
       </c>
@@ -37193,7 +37193,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="729" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>139</v>
       </c>
@@ -37234,7 +37234,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="730" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>139</v>
       </c>
@@ -37275,7 +37275,7 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="731" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>139</v>
       </c>
@@ -37316,7 +37316,7 @@
         <v>1.022</v>
       </c>
     </row>
-    <row r="732" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>139</v>
       </c>
@@ -37398,7 +37398,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="734" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>139</v>
       </c>
@@ -37439,7 +37439,7 @@
         <v>1.133</v>
       </c>
     </row>
-    <row r="735" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>139</v>
       </c>
@@ -37480,7 +37480,7 @@
         <v>0.92400000000000004</v>
       </c>
     </row>
-    <row r="736" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>139</v>
       </c>
@@ -37521,7 +37521,7 @@
         <v>0.746</v>
       </c>
     </row>
-    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>139</v>
       </c>
@@ -37571,7 +37571,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="738" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>139</v>
       </c>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="S738"/>
     </row>
-    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>139</v>
       </c>
@@ -37655,7 +37655,7 @@
       </c>
       <c r="S739"/>
     </row>
-    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>139</v>
       </c>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="S740"/>
     </row>
-    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>139</v>
       </c>
@@ -37739,7 +37739,7 @@
       </c>
       <c r="S741"/>
     </row>
-    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>139</v>
       </c>
@@ -37772,7 +37772,7 @@
       </c>
       <c r="S742"/>
     </row>
-    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>139</v>
       </c>
@@ -37814,7 +37814,7 @@
       </c>
       <c r="S743"/>
     </row>
-    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>139</v>
       </c>
@@ -37856,7 +37856,7 @@
       </c>
       <c r="S744"/>
     </row>
-    <row r="745" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>139</v>
       </c>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="S745"/>
     </row>
-    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>139</v>
       </c>
@@ -37940,7 +37940,7 @@
       </c>
       <c r="S746"/>
     </row>
-    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>139</v>
       </c>
@@ -38024,7 +38024,7 @@
       </c>
       <c r="S748"/>
     </row>
-    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>139</v>
       </c>
@@ -38074,7 +38074,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>139</v>
       </c>
@@ -38116,7 +38116,7 @@
       </c>
       <c r="S750"/>
     </row>
-    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>139</v>
       </c>
@@ -38158,7 +38158,7 @@
       </c>
       <c r="S751"/>
     </row>
-    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>139</v>
       </c>
@@ -38241,7 +38241,7 @@
         <v>0.95099999999999996</v>
       </c>
     </row>
-    <row r="754" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>139</v>
       </c>
@@ -38282,7 +38282,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="755" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>139</v>
       </c>
@@ -38323,7 +38323,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="756" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>139</v>
       </c>
@@ -38364,7 +38364,7 @@
         <v>1.169</v>
       </c>
     </row>
-    <row r="757" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>139</v>
       </c>
@@ -38405,7 +38405,7 @@
         <v>1.0489999999999999</v>
       </c>
     </row>
-    <row r="758" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>139</v>
       </c>
@@ -38446,7 +38446,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="759" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>139</v>
       </c>
@@ -38487,7 +38487,7 @@
         <v>1.022</v>
       </c>
     </row>
-    <row r="760" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>139</v>
       </c>
@@ -38528,7 +38528,7 @@
         <v>1.419</v>
       </c>
     </row>
-    <row r="761" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>139</v>
       </c>
@@ -38569,7 +38569,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="762" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>139</v>
       </c>
@@ -38610,7 +38610,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="763" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>139</v>
       </c>
@@ -38651,7 +38651,7 @@
         <v>1.028</v>
       </c>
     </row>
-    <row r="764" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>139</v>
       </c>
@@ -38692,7 +38692,7 @@
         <v>1.613</v>
       </c>
     </row>
-    <row r="765" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>139</v>
       </c>
@@ -38733,7 +38733,7 @@
         <v>0.93500000000000005</v>
       </c>
     </row>
-    <row r="766" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>139</v>
       </c>
@@ -38774,7 +38774,7 @@
         <v>1.042</v>
       </c>
     </row>
-    <row r="767" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>139</v>
       </c>
@@ -38815,7 +38815,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="768" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>139</v>
       </c>
@@ -38847,7 +38847,7 @@
         <v>1.0640000000000001</v>
       </c>
     </row>
-    <row r="769" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>139</v>
       </c>
@@ -39011,7 +39011,7 @@
         <v>0.96299999999999997</v>
       </c>
     </row>
-    <row r="773" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>139</v>
       </c>
@@ -39052,7 +39052,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="774" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>139</v>
       </c>
@@ -39093,7 +39093,7 @@
         <v>1.2450000000000001</v>
       </c>
     </row>
-    <row r="775" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>139</v>
       </c>
@@ -39134,7 +39134,7 @@
         <v>1.2250000000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>139</v>
       </c>
@@ -39184,7 +39184,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="777" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>139</v>
       </c>
@@ -39225,7 +39225,7 @@
         <v>1.2150000000000001</v>
       </c>
     </row>
-    <row r="778" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>139</v>
       </c>
@@ -39266,7 +39266,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="779" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>139</v>
       </c>
@@ -39298,7 +39298,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="780" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>139</v>
       </c>
@@ -39339,7 +39339,7 @@
         <v>1.264</v>
       </c>
     </row>
-    <row r="781" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>139</v>
       </c>
@@ -39380,7 +39380,7 @@
         <v>1.157</v>
       </c>
     </row>
-    <row r="782" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>139</v>
       </c>
@@ -39421,7 +39421,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="783" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>139</v>
       </c>
@@ -39462,7 +39462,7 @@
         <v>1.0609999999999999</v>
       </c>
     </row>
-    <row r="784" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>139</v>
       </c>
@@ -39512,7 +39512,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="785" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>139</v>
       </c>
@@ -39554,7 +39554,7 @@
       </c>
       <c r="S785"/>
     </row>
-    <row r="786" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>139</v>
       </c>
@@ -39578,7 +39578,7 @@
       </c>
       <c r="S786"/>
     </row>
-    <row r="787" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>139</v>
       </c>
@@ -39620,7 +39620,7 @@
       </c>
       <c r="S787"/>
     </row>
-    <row r="788" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>139</v>
       </c>
@@ -39704,7 +39704,7 @@
       </c>
       <c r="S789"/>
     </row>
-    <row r="790" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>139</v>
       </c>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="S790"/>
     </row>
-    <row r="791" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>139</v>
       </c>
@@ -39839,7 +39839,7 @@
       </c>
       <c r="S792"/>
     </row>
-    <row r="793" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>139</v>
       </c>
@@ -39871,7 +39871,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="794" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>139</v>
       </c>
@@ -39913,7 +39913,7 @@
       </c>
       <c r="S794"/>
     </row>
-    <row r="795" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>139</v>
       </c>
@@ -39955,7 +39955,7 @@
       </c>
       <c r="S795"/>
     </row>
-    <row r="796" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>139</v>
       </c>
@@ -39997,7 +39997,7 @@
       </c>
       <c r="S796"/>
     </row>
-    <row r="797" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>139</v>
       </c>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="S797"/>
     </row>
-    <row r="798" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>139</v>
       </c>
@@ -40081,7 +40081,7 @@
       </c>
       <c r="S798"/>
     </row>
-    <row r="799" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>139</v>
       </c>
@@ -40123,7 +40123,7 @@
       </c>
       <c r="S799"/>
     </row>
-    <row r="800" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>139</v>
       </c>
@@ -40165,7 +40165,7 @@
       </c>
       <c r="S800"/>
     </row>
-    <row r="801" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>139</v>
       </c>
@@ -40207,7 +40207,7 @@
       </c>
       <c r="S801"/>
     </row>
-    <row r="802" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>139</v>
       </c>
@@ -40249,7 +40249,7 @@
       </c>
       <c r="S802"/>
     </row>
-    <row r="803" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>139</v>
       </c>
@@ -40300,7 +40300,7 @@
       </c>
       <c r="S803"/>
     </row>
-    <row r="804" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>139</v>
       </c>
@@ -40332,7 +40332,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="805" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>139</v>
       </c>
@@ -40374,7 +40374,7 @@
       </c>
       <c r="S805"/>
     </row>
-    <row r="806" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>139</v>
       </c>
@@ -40416,7 +40416,7 @@
       </c>
       <c r="S806"/>
     </row>
-    <row r="807" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>139</v>
       </c>
@@ -40500,7 +40500,7 @@
       </c>
       <c r="S808"/>
     </row>
-    <row r="809" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>139</v>
       </c>
@@ -40542,7 +40542,7 @@
       </c>
       <c r="S809"/>
     </row>
-    <row r="810" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>139</v>
       </c>
@@ -40584,7 +40584,7 @@
       </c>
       <c r="S810"/>
     </row>
-    <row r="811" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>139</v>
       </c>
@@ -40668,7 +40668,7 @@
       </c>
       <c r="S812"/>
     </row>
-    <row r="813" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>139</v>
       </c>
@@ -40710,7 +40710,7 @@
       </c>
       <c r="S813"/>
     </row>
-    <row r="814" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>139</v>
       </c>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="S814"/>
     </row>
-    <row r="815" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>139</v>
       </c>
@@ -40802,7 +40802,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="816" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>139</v>
       </c>
@@ -40844,7 +40844,7 @@
       </c>
       <c r="S816"/>
     </row>
-    <row r="817" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>139</v>
       </c>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="S817"/>
     </row>
-    <row r="818" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>139</v>
       </c>
@@ -40928,7 +40928,7 @@
       </c>
       <c r="S818"/>
     </row>
-    <row r="819" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>139</v>
       </c>
@@ -40970,7 +40970,7 @@
       </c>
       <c r="S819"/>
     </row>
-    <row r="820" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>139</v>
       </c>
@@ -41012,7 +41012,7 @@
       </c>
       <c r="S820"/>
     </row>
-    <row r="821" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>139</v>
       </c>
@@ -41054,7 +41054,7 @@
       </c>
       <c r="S821"/>
     </row>
-    <row r="822" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>139</v>
       </c>
@@ -41096,7 +41096,7 @@
       </c>
       <c r="S822"/>
     </row>
-    <row r="823" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>139</v>
       </c>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="S823"/>
     </row>
-    <row r="824" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>139</v>
       </c>
@@ -41180,7 +41180,7 @@
       </c>
       <c r="S824"/>
     </row>
-    <row r="825" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>139</v>
       </c>
@@ -41222,7 +41222,7 @@
       </c>
       <c r="S825"/>
     </row>
-    <row r="826" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>139</v>
       </c>
@@ -41306,7 +41306,7 @@
       </c>
       <c r="S827"/>
     </row>
-    <row r="828" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>139</v>
       </c>
@@ -41347,7 +41347,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="829" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>139</v>
       </c>
@@ -41389,7 +41389,7 @@
       </c>
       <c r="S829"/>
     </row>
-    <row r="830" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>139</v>
       </c>
@@ -41430,7 +41430,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="831" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>139</v>
       </c>
@@ -41472,7 +41472,7 @@
       </c>
       <c r="S831"/>
     </row>
-    <row r="832" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>139</v>
       </c>
@@ -41522,7 +41522,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="833" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>139</v>
       </c>
@@ -41564,7 +41564,7 @@
       </c>
       <c r="S833"/>
     </row>
-    <row r="834" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>139</v>
       </c>
@@ -41606,7 +41606,7 @@
       </c>
       <c r="S834"/>
     </row>
-    <row r="835" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>139</v>
       </c>
@@ -41639,7 +41639,7 @@
       </c>
       <c r="S835"/>
     </row>
-    <row r="836" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>139</v>
       </c>
@@ -41681,7 +41681,7 @@
       </c>
       <c r="S836"/>
     </row>
-    <row r="837" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>139</v>
       </c>
@@ -41722,7 +41722,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="838" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>139</v>
       </c>
@@ -41772,7 +41772,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="839" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>139</v>
       </c>
@@ -41814,7 +41814,7 @@
       </c>
       <c r="S839"/>
     </row>
-    <row r="840" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>139</v>
       </c>
@@ -41855,7 +41855,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="841" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>139</v>
       </c>
@@ -41897,7 +41897,7 @@
       </c>
       <c r="S841"/>
     </row>
-    <row r="842" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>139</v>
       </c>
@@ -41939,7 +41939,7 @@
       </c>
       <c r="S842"/>
     </row>
-    <row r="843" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>139</v>
       </c>
@@ -41981,7 +41981,7 @@
       </c>
       <c r="S843"/>
     </row>
-    <row r="844" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>139</v>
       </c>
@@ -42023,7 +42023,7 @@
       </c>
       <c r="S844"/>
     </row>
-    <row r="845" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>139</v>
       </c>
@@ -42065,7 +42065,7 @@
       </c>
       <c r="S845"/>
     </row>
-    <row r="846" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>139</v>
       </c>
@@ -42107,7 +42107,7 @@
       </c>
       <c r="S846"/>
     </row>
-    <row r="847" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>139</v>
       </c>
@@ -42149,7 +42149,7 @@
       </c>
       <c r="S847"/>
     </row>
-    <row r="848" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>139</v>
       </c>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="S849"/>
     </row>
-    <row r="850" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>139</v>
       </c>
@@ -42291,7 +42291,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="851" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>139</v>
       </c>
@@ -42333,7 +42333,7 @@
       </c>
       <c r="S851"/>
     </row>
-    <row r="852" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>139</v>
       </c>
@@ -42384,7 +42384,7 @@
       </c>
       <c r="S852"/>
     </row>
-    <row r="853" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>139</v>
       </c>
@@ -42426,7 +42426,7 @@
       </c>
       <c r="S853"/>
     </row>
-    <row r="854" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>139</v>
       </c>
@@ -42468,7 +42468,7 @@
       </c>
       <c r="S854"/>
     </row>
-    <row r="855" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>139</v>
       </c>
@@ -42509,7 +42509,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="856" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>139</v>
       </c>
@@ -42551,7 +42551,7 @@
       </c>
       <c r="S856"/>
     </row>
-    <row r="857" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>139</v>
       </c>
@@ -42575,7 +42575,7 @@
       </c>
       <c r="S857"/>
     </row>
-    <row r="858" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>139</v>
       </c>
@@ -42599,7 +42599,7 @@
       </c>
       <c r="S858"/>
     </row>
-    <row r="859" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>139</v>
       </c>
@@ -42649,7 +42649,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="860" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>139</v>
       </c>
@@ -42691,7 +42691,7 @@
       </c>
       <c r="S860"/>
     </row>
-    <row r="861" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>139</v>
       </c>
@@ -42733,7 +42733,7 @@
       </c>
       <c r="S861"/>
     </row>
-    <row r="862" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>139</v>
       </c>
@@ -42775,7 +42775,7 @@
       </c>
       <c r="S862"/>
     </row>
-    <row r="863" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>139</v>
       </c>
@@ -42817,7 +42817,7 @@
       </c>
       <c r="S863"/>
     </row>
-    <row r="864" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>139</v>
       </c>
@@ -42859,7 +42859,7 @@
       </c>
       <c r="S864"/>
     </row>
-    <row r="865" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>139</v>
       </c>
@@ -42901,7 +42901,7 @@
       </c>
       <c r="S865"/>
     </row>
-    <row r="866" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>139</v>
       </c>
@@ -42985,7 +42985,7 @@
       </c>
       <c r="S867"/>
     </row>
-    <row r="868" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>139</v>
       </c>
@@ -43017,7 +43017,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="869" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>139</v>
       </c>
@@ -43049,7 +43049,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="870" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>139</v>
       </c>
@@ -43091,7 +43091,7 @@
       </c>
       <c r="S870"/>
     </row>
-    <row r="871" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>139</v>
       </c>
@@ -43142,7 +43142,7 @@
       </c>
       <c r="S871"/>
     </row>
-    <row r="872" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>139</v>
       </c>
@@ -43184,7 +43184,7 @@
       </c>
       <c r="S872"/>
     </row>
-    <row r="873" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>139</v>
       </c>
@@ -43217,7 +43217,7 @@
       </c>
       <c r="S873"/>
     </row>
-    <row r="874" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>139</v>
       </c>
@@ -43250,7 +43250,7 @@
       </c>
       <c r="S874"/>
     </row>
-    <row r="875" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>139</v>
       </c>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="S875"/>
     </row>
-    <row r="876" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>139</v>
       </c>
@@ -43325,7 +43325,7 @@
       </c>
       <c r="S876"/>
     </row>
-    <row r="877" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>139</v>
       </c>
@@ -43358,7 +43358,7 @@
       </c>
       <c r="S877"/>
     </row>
-    <row r="878" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>139</v>
       </c>
@@ -43382,7 +43382,7 @@
       </c>
       <c r="S878"/>
     </row>
-    <row r="879" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>139</v>
       </c>
@@ -43424,7 +43424,7 @@
       </c>
       <c r="S879"/>
     </row>
-    <row r="880" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>139</v>
       </c>
@@ -43457,7 +43457,7 @@
       </c>
       <c r="S880"/>
     </row>
-    <row r="881" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>139</v>
       </c>
@@ -43507,7 +43507,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="882" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>139</v>
       </c>
@@ -43548,7 +43548,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="883" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>139</v>
       </c>
@@ -43589,7 +43589,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="884" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>139</v>
       </c>
@@ -43639,7 +43639,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="885" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>139</v>
       </c>
@@ -43680,7 +43680,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="886" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>139</v>
       </c>
@@ -43721,7 +43721,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="887" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>139</v>
       </c>
@@ -43762,7 +43762,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="888" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>139</v>
       </c>
@@ -43795,7 +43795,7 @@
       </c>
       <c r="S888"/>
     </row>
-    <row r="889" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>139</v>
       </c>
@@ -43828,7 +43828,7 @@
       </c>
       <c r="S889"/>
     </row>
-    <row r="890" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>139</v>
       </c>
@@ -43869,7 +43869,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="891" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>139</v>
       </c>
@@ -43910,7 +43910,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="892" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>139</v>
       </c>
@@ -43943,7 +43943,7 @@
       </c>
       <c r="S892"/>
     </row>
-    <row r="893" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>139</v>
       </c>
@@ -43984,7 +43984,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="894" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>139</v>
       </c>
@@ -44025,7 +44025,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="895" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>139</v>
       </c>
@@ -44066,7 +44066,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="896" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>139</v>
       </c>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S897"/>
     </row>
-    <row r="898" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>139</v>
       </c>
@@ -44232,7 +44232,7 @@
       </c>
       <c r="S899"/>
     </row>
-    <row r="900" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>139</v>
       </c>
@@ -44274,7 +44274,7 @@
       </c>
       <c r="S900"/>
     </row>
-    <row r="901" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>139</v>
       </c>
@@ -44358,7 +44358,7 @@
       </c>
       <c r="S902"/>
     </row>
-    <row r="903" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>139</v>
       </c>
@@ -44400,7 +44400,7 @@
       </c>
       <c r="S903"/>
     </row>
-    <row r="904" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>139</v>
       </c>
@@ -44475,7 +44475,7 @@
       </c>
       <c r="S905"/>
     </row>
-    <row r="906" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>139</v>
       </c>
@@ -44517,7 +44517,7 @@
       </c>
       <c r="S906"/>
     </row>
-    <row r="907" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>139</v>
       </c>
@@ -44559,7 +44559,7 @@
       </c>
       <c r="S907"/>
     </row>
-    <row r="908" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>139</v>
       </c>
@@ -44601,7 +44601,7 @@
       </c>
       <c r="S908"/>
     </row>
-    <row r="909" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>139</v>
       </c>
@@ -44643,7 +44643,7 @@
       </c>
       <c r="S909"/>
     </row>
-    <row r="910" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>139</v>
       </c>
@@ -44685,7 +44685,7 @@
       </c>
       <c r="S910"/>
     </row>
-    <row r="911" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>139</v>
       </c>
@@ -44727,7 +44727,7 @@
       </c>
       <c r="S911"/>
     </row>
-    <row r="912" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>139</v>
       </c>
@@ -44759,7 +44759,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="913" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>139</v>
       </c>
@@ -44801,7 +44801,7 @@
       </c>
       <c r="S913"/>
     </row>
-    <row r="914" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>139</v>
       </c>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="S915"/>
     </row>
-    <row r="916" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>139</v>
       </c>
@@ -44909,7 +44909,7 @@
       </c>
       <c r="S916"/>
     </row>
-    <row r="917" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>139</v>
       </c>
@@ -44942,7 +44942,7 @@
       </c>
       <c r="S917"/>
     </row>
-    <row r="918" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>139</v>
       </c>
@@ -44983,7 +44983,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="919" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>139</v>
       </c>
@@ -45025,7 +45025,7 @@
       </c>
       <c r="S919"/>
     </row>
-    <row r="920" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>139</v>
       </c>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="S920"/>
     </row>
-    <row r="921" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>139</v>
       </c>
@@ -45100,7 +45100,7 @@
       </c>
       <c r="S921"/>
     </row>
-    <row r="922" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>139</v>
       </c>
@@ -45142,7 +45142,7 @@
       </c>
       <c r="S922"/>
     </row>
-    <row r="923" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>139</v>
       </c>
@@ -45184,7 +45184,7 @@
       </c>
       <c r="S923"/>
     </row>
-    <row r="924" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>139</v>
       </c>
@@ -45226,7 +45226,7 @@
       </c>
       <c r="S924"/>
     </row>
-    <row r="925" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>139</v>
       </c>
@@ -45268,7 +45268,7 @@
       </c>
       <c r="S925"/>
     </row>
-    <row r="926" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>139</v>
       </c>
@@ -45301,7 +45301,7 @@
       </c>
       <c r="S926"/>
     </row>
-    <row r="927" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>139</v>
       </c>
@@ -45333,7 +45333,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="928" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>139</v>
       </c>
@@ -45365,7 +45365,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="929" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>139</v>
       </c>
@@ -45397,7 +45397,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="930" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>139</v>
       </c>
@@ -45429,7 +45429,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="931" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>139</v>
       </c>
@@ -45461,7 +45461,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="932" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>139</v>
       </c>
@@ -45493,7 +45493,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="933" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>139</v>
       </c>
@@ -45525,7 +45525,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="934" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>139</v>
       </c>
@@ -45557,7 +45557,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="935" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>139</v>
       </c>
@@ -45599,7 +45599,7 @@
       </c>
       <c r="S935"/>
     </row>
-    <row r="936" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>139</v>
       </c>
@@ -45632,7 +45632,7 @@
       </c>
       <c r="S936"/>
     </row>
-    <row r="937" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>139</v>
       </c>
@@ -45706,7 +45706,7 @@
       </c>
       <c r="S938"/>
     </row>
-    <row r="939" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>139</v>
       </c>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="S939"/>
     </row>
-    <row r="940" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>139</v>
       </c>
@@ -45790,7 +45790,7 @@
       </c>
       <c r="S940"/>
     </row>
-    <row r="941" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>139</v>
       </c>
@@ -45822,7 +45822,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="942" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>139</v>
       </c>
@@ -45872,7 +45872,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="943" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>139</v>
       </c>
@@ -45904,7 +45904,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="944" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>139</v>
       </c>
@@ -45936,7 +45936,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="945" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>139</v>
       </c>
@@ -45977,7 +45977,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="946" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>139</v>
       </c>
@@ -46018,7 +46018,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="947" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>139</v>
       </c>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S947"/>
     </row>
-    <row r="948" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>139</v>
       </c>
@@ -46135,7 +46135,7 @@
       </c>
       <c r="S949"/>
     </row>
-    <row r="950" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>139</v>
       </c>
@@ -46177,7 +46177,7 @@
       </c>
       <c r="S950"/>
     </row>
-    <row r="951" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>139</v>
       </c>
@@ -46210,7 +46210,7 @@
       </c>
       <c r="S951"/>
     </row>
-    <row r="952" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>139</v>
       </c>
@@ -46252,7 +46252,7 @@
       </c>
       <c r="S952"/>
     </row>
-    <row r="953" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>139</v>
       </c>
@@ -46294,7 +46294,7 @@
       </c>
       <c r="S953"/>
     </row>
-    <row r="954" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>139</v>
       </c>
@@ -46345,7 +46345,7 @@
       </c>
       <c r="S954"/>
     </row>
-    <row r="955" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>139</v>
       </c>
@@ -46387,7 +46387,7 @@
       </c>
       <c r="S955"/>
     </row>
-    <row r="956" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>139</v>
       </c>
@@ -46429,7 +46429,7 @@
       </c>
       <c r="S956"/>
     </row>
-    <row r="957" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>139</v>
       </c>
@@ -46471,7 +46471,7 @@
       </c>
       <c r="S957"/>
     </row>
-    <row r="958" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>139</v>
       </c>
@@ -46513,7 +46513,7 @@
       </c>
       <c r="S958"/>
     </row>
-    <row r="959" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>139</v>
       </c>
@@ -46555,7 +46555,7 @@
       </c>
       <c r="S959"/>
     </row>
-    <row r="960" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>139</v>
       </c>
@@ -46597,7 +46597,7 @@
       </c>
       <c r="S960"/>
     </row>
-    <row r="961" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>139</v>
       </c>
@@ -46639,7 +46639,7 @@
       </c>
       <c r="S961"/>
     </row>
-    <row r="962" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>139</v>
       </c>
@@ -46723,7 +46723,7 @@
       </c>
       <c r="S963"/>
     </row>
-    <row r="964" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>139</v>
       </c>
@@ -46765,7 +46765,7 @@
       </c>
       <c r="S964"/>
     </row>
-    <row r="965" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>139</v>
       </c>
@@ -46798,7 +46798,7 @@
       </c>
       <c r="S965"/>
     </row>
-    <row r="966" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>139</v>
       </c>
@@ -46839,7 +46839,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="967" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>139</v>
       </c>
@@ -46880,7 +46880,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="968" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>139</v>
       </c>
@@ -46921,7 +46921,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="969" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>139</v>
       </c>
@@ -46953,7 +46953,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="970" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>139</v>
       </c>
@@ -46994,7 +46994,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="971" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>139</v>
       </c>
@@ -47026,7 +47026,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="972" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>139</v>
       </c>
@@ -47058,7 +47058,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="973" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>139</v>
       </c>
@@ -47090,7 +47090,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="974" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>139</v>
       </c>
@@ -47122,7 +47122,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="975" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>139</v>
       </c>
@@ -47154,7 +47154,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="976" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>139</v>
       </c>
@@ -47186,7 +47186,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="977" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>139</v>
       </c>
@@ -47218,7 +47218,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="978" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>139</v>
       </c>
@@ -47250,7 +47250,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="979" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>139</v>
       </c>
@@ -47282,7 +47282,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="980" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>139</v>
       </c>
@@ -47306,7 +47306,7 @@
       </c>
       <c r="S980"/>
     </row>
-    <row r="981" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>139</v>
       </c>
@@ -47338,7 +47338,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="982" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>139</v>
       </c>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="S982"/>
     </row>
-    <row r="983" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>139</v>
       </c>
@@ -47386,7 +47386,7 @@
       </c>
       <c r="S983"/>
     </row>
-    <row r="984" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>139</v>
       </c>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="S984"/>
     </row>
-    <row r="985" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>139</v>
       </c>
@@ -47461,7 +47461,7 @@
       </c>
       <c r="S985"/>
     </row>
-    <row r="986" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>139</v>
       </c>
@@ -47494,7 +47494,7 @@
       </c>
       <c r="S986"/>
     </row>
-    <row r="987" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>139</v>
       </c>
@@ -47527,7 +47527,7 @@
       </c>
       <c r="S987"/>
     </row>
-    <row r="988" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>139</v>
       </c>
@@ -47560,7 +47560,7 @@
       </c>
       <c r="S988"/>
     </row>
-    <row r="989" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>139</v>
       </c>
@@ -47593,7 +47593,7 @@
       </c>
       <c r="S989"/>
     </row>
-    <row r="990" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>139</v>
       </c>
@@ -47626,7 +47626,7 @@
       </c>
       <c r="S990"/>
     </row>
-    <row r="991" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>139</v>
       </c>
@@ -47659,7 +47659,7 @@
       </c>
       <c r="S991"/>
     </row>
-    <row r="992" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>139</v>
       </c>
@@ -47692,7 +47692,7 @@
       </c>
       <c r="S992"/>
     </row>
-    <row r="993" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>139</v>
       </c>
@@ -47724,7 +47724,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="994" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>139</v>
       </c>
@@ -47765,7 +47765,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="995" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>139</v>
       </c>
@@ -47806,7 +47806,7 @@
         <v>1.0569999999999999</v>
       </c>
     </row>
-    <row r="996" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>139</v>
       </c>
@@ -47838,7 +47838,7 @@
         <v>1.0109999999999999</v>
       </c>
     </row>
-    <row r="997" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>139</v>
       </c>
@@ -47879,7 +47879,7 @@
         <v>0.99199999999999999</v>
       </c>
     </row>
-    <row r="998" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>139</v>
       </c>
@@ -47920,7 +47920,7 @@
         <v>1.073</v>
       </c>
     </row>
-    <row r="999" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>139</v>
       </c>
@@ -47952,7 +47952,7 @@
         <v>1.0669999999999999</v>
       </c>
     </row>
-    <row r="1000" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>139</v>
       </c>
@@ -47993,7 +47993,7 @@
         <v>1.1419999999999999</v>
       </c>
     </row>
-    <row r="1001" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>139</v>
       </c>
@@ -48025,7 +48025,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="1002" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>139</v>
       </c>
@@ -48066,7 +48066,7 @@
         <v>1.1739999999999999</v>
       </c>
     </row>
-    <row r="1003" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>139</v>
       </c>
@@ -48098,7 +48098,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="1004" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>139</v>
       </c>
@@ -48130,7 +48130,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="1005" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>139</v>
       </c>
@@ -48171,7 +48171,7 @@
         <v>1.0880000000000001</v>
       </c>
     </row>
-    <row r="1006" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>139</v>
       </c>
@@ -48203,7 +48203,7 @@
         <v>1.1259999999999999</v>
       </c>
     </row>
-    <row r="1007" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>139</v>
       </c>
@@ -48267,7 +48267,7 @@
         <v>0.51800000000000002</v>
       </c>
     </row>
-    <row r="1009" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>139</v>
       </c>
@@ -48290,7 +48290,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="1010" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>139</v>
       </c>
@@ -48313,7 +48313,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="1011" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>139</v>
       </c>
@@ -48336,7 +48336,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1012" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>139</v>
       </c>
@@ -48359,7 +48359,7 @@
         <v>1.1950000000000001</v>
       </c>
     </row>
-    <row r="1013" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>139</v>
       </c>
@@ -48382,7 +48382,7 @@
         <v>1.0980000000000001</v>
       </c>
     </row>
-    <row r="1014" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>139</v>
       </c>
@@ -48405,7 +48405,7 @@
         <v>1.159</v>
       </c>
     </row>
-    <row r="1015" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>139</v>
       </c>
@@ -48428,7 +48428,7 @@
         <v>0.877</v>
       </c>
     </row>
-    <row r="1016" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>139</v>
       </c>
@@ -48451,7 +48451,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="1017" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>139</v>
       </c>
@@ -48483,7 +48483,7 @@
         <v>1.123</v>
       </c>
     </row>
-    <row r="1018" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>139</v>
       </c>
@@ -48515,7 +48515,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1019" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>139</v>
       </c>
@@ -48538,7 +48538,7 @@
         <v>1.109</v>
       </c>
     </row>
-    <row r="1020" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>139</v>
       </c>
@@ -48570,7 +48570,7 @@
         <v>0.95699999999999996</v>
       </c>
     </row>
-    <row r="1021" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>139</v>
       </c>
@@ -48602,7 +48602,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="1022" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>139</v>
       </c>
@@ -48684,7 +48684,7 @@
         <v>2.1589999999999998</v>
       </c>
     </row>
-    <row r="1024" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>139</v>
       </c>
@@ -48767,7 +48767,7 @@
       </c>
       <c r="S1025"/>
     </row>
-    <row r="1026" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>139</v>
       </c>
@@ -48800,7 +48800,7 @@
       </c>
       <c r="S1026"/>
     </row>
-    <row r="1027" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>139</v>
       </c>
@@ -48842,7 +48842,7 @@
       </c>
       <c r="S1027"/>
     </row>
-    <row r="1028" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>139</v>
       </c>
@@ -48884,7 +48884,7 @@
       </c>
       <c r="S1028"/>
     </row>
-    <row r="1029" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>139</v>
       </c>
@@ -48926,7 +48926,7 @@
       </c>
       <c r="S1029"/>
     </row>
-    <row r="1030" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>139</v>
       </c>
@@ -48968,7 +48968,7 @@
       </c>
       <c r="S1030"/>
     </row>
-    <row r="1031" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>139</v>
       </c>
@@ -49010,7 +49010,7 @@
       </c>
       <c r="S1031"/>
     </row>
-    <row r="1032" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>139</v>
       </c>
@@ -49052,7 +49052,7 @@
       </c>
       <c r="S1032"/>
     </row>
-    <row r="1033" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>139</v>
       </c>
@@ -49094,7 +49094,7 @@
       </c>
       <c r="S1033"/>
     </row>
-    <row r="1034" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>139</v>
       </c>
@@ -49136,7 +49136,7 @@
       </c>
       <c r="S1034"/>
     </row>
-    <row r="1035" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>139</v>
       </c>
@@ -49178,7 +49178,7 @@
       </c>
       <c r="S1035"/>
     </row>
-    <row r="1036" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>139</v>
       </c>
@@ -49220,7 +49220,7 @@
       </c>
       <c r="S1036"/>
     </row>
-    <row r="1037" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>139</v>
       </c>
@@ -49271,18 +49271,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="e"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="16">
-      <filters>
-        <filter val="0.5"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LineClass/levels_pub.xlsx
+++ b/LineClass/levels_pub.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF016F6-7F02-423B-B40B-A694DD697E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F47FBE-A511-4912-A02C-3CC743A5B83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="47115" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="43920" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
   </bookViews>
   <sheets>
     <sheet name="levels_pub" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7296" uniqueCount="896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7303" uniqueCount="903">
   <si>
     <t>conf</t>
   </si>
@@ -2724,6 +2724,27 @@
   </si>
   <si>
     <t>059003.000624</t>
+  </si>
+  <si>
+    <t>059003.000642</t>
+  </si>
+  <si>
+    <t>059003.000676</t>
+  </si>
+  <si>
+    <t>059003.000652</t>
+  </si>
+  <si>
+    <t>059003.000680</t>
+  </si>
+  <si>
+    <t>059003.000678</t>
+  </si>
+  <si>
+    <t>059003.000673</t>
+  </si>
+  <si>
+    <t>059003.000625</t>
   </si>
 </sst>
 </file>
@@ -3592,7 +3613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A1:S1037"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3676,7 +3697,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3717,7 +3738,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3749,7 +3770,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3781,7 +3802,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3813,7 +3834,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3854,7 +3875,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3904,7 +3925,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3945,7 +3966,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3995,7 +4016,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4036,7 +4057,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4086,7 +4107,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4136,7 +4157,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4186,7 +4207,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4218,7 +4239,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4268,7 +4289,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4327,7 +4348,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4359,7 +4380,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4409,7 +4430,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4459,7 +4480,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -4509,7 +4530,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -4550,7 +4571,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -4591,7 +4612,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -4632,7 +4653,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4682,7 +4703,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4732,7 +4753,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -4782,7 +4803,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -4832,7 +4853,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -4873,7 +4894,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -4914,7 +4935,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -4955,7 +4976,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -4987,7 +5008,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -5019,7 +5040,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -5069,7 +5090,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -5110,7 +5131,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -5160,7 +5181,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -5210,7 +5231,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -5260,7 +5281,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -5310,7 +5331,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -5360,7 +5381,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -5410,7 +5431,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -5460,7 +5481,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -5502,7 +5523,7 @@
       </c>
       <c r="S42"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -5552,7 +5573,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -5602,7 +5623,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -5652,7 +5673,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -5702,7 +5723,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -5752,7 +5773,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -5802,7 +5823,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -5852,7 +5873,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -5902,7 +5923,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -5952,7 +5973,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -6002,7 +6023,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>16</v>
       </c>
@@ -6052,7 +6073,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -6093,7 +6114,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -6143,7 +6164,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -6193,7 +6214,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -6235,7 +6256,7 @@
       </c>
       <c r="S57"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -6294,7 +6315,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -6344,7 +6365,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -6394,7 +6415,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -6444,7 +6465,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -6503,7 +6524,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -6553,7 +6574,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -6603,7 +6624,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -6662,7 +6683,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -6712,7 +6733,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -6762,7 +6783,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -6812,7 +6833,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -6862,7 +6883,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -6912,7 +6933,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -6962,7 +6983,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -7012,7 +7033,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -7054,7 +7075,7 @@
       </c>
       <c r="S73"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -7104,7 +7125,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -7154,7 +7175,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -7204,7 +7225,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -7254,7 +7275,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -7304,7 +7325,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -7354,7 +7375,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -7404,7 +7425,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -7445,7 +7466,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -7504,7 +7525,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -7554,7 +7575,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -7604,7 +7625,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -7654,7 +7675,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -7704,7 +7725,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -7754,7 +7775,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -7804,7 +7825,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -7854,7 +7875,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -7904,7 +7925,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -7954,7 +7975,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -7995,7 +8016,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -8045,7 +8066,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -8095,7 +8116,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -8145,7 +8166,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -8195,7 +8216,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -8236,7 +8257,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -8286,7 +8307,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -8336,7 +8357,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -8386,7 +8407,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -8436,7 +8457,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -8495,7 +8516,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -8537,7 +8558,7 @@
       </c>
       <c r="S103"/>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -8587,7 +8608,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -8637,7 +8658,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -8687,7 +8708,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -8737,7 +8758,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -8787,7 +8808,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -8837,7 +8858,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -8887,7 +8908,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -8938,7 +8959,7 @@
       </c>
       <c r="S111"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -8970,7 +8991,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -9020,7 +9041,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -9070,7 +9091,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -9112,7 +9133,7 @@
       </c>
       <c r="S115"/>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -9162,7 +9183,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -9204,7 +9225,7 @@
       </c>
       <c r="S117"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -9246,7 +9267,7 @@
       </c>
       <c r="S118"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -9296,7 +9317,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -9346,7 +9367,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -9396,7 +9417,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -9446,7 +9467,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -9496,7 +9517,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -9546,7 +9567,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -9596,7 +9617,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -9646,7 +9667,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -9688,7 +9709,7 @@
       </c>
       <c r="S127"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -9738,7 +9759,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -9780,7 +9801,7 @@
       </c>
       <c r="S129"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -9830,7 +9851,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -9872,7 +9893,7 @@
       </c>
       <c r="S131"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -9922,7 +9943,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -9972,7 +9993,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -10031,7 +10052,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -10081,7 +10102,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -10131,7 +10152,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -10190,7 +10211,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -10232,7 +10253,7 @@
       </c>
       <c r="S138"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -10274,7 +10295,7 @@
       </c>
       <c r="S139"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -10324,7 +10345,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -10374,7 +10395,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -10425,7 +10446,7 @@
       </c>
       <c r="S142"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -10475,7 +10496,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -10525,7 +10546,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -10575,7 +10596,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -10625,7 +10646,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -10675,7 +10696,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -10725,7 +10746,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -10775,7 +10796,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -10825,7 +10846,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -10884,7 +10905,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -10934,7 +10955,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -10984,7 +11005,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -11034,7 +11055,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -11084,7 +11105,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -11134,7 +11155,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -11184,7 +11205,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -11234,7 +11255,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -11275,7 +11296,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -11325,7 +11346,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -11375,7 +11396,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -11425,7 +11446,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -11475,7 +11496,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -11525,7 +11546,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -11575,7 +11596,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -11625,7 +11646,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -11675,7 +11696,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -11725,7 +11746,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -11767,7 +11788,7 @@
       </c>
       <c r="S169"/>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -11817,7 +11838,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -11867,7 +11888,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -11917,7 +11938,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -11959,7 +11980,7 @@
       </c>
       <c r="S173"/>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -12009,7 +12030,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -12051,7 +12072,7 @@
       </c>
       <c r="S175"/>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -12101,7 +12122,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -12151,7 +12172,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -12201,7 +12222,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -12251,7 +12272,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -12293,7 +12314,7 @@
       </c>
       <c r="S180"/>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -12352,7 +12373,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -12402,7 +12423,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -12452,7 +12473,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -12494,7 +12515,7 @@
       </c>
       <c r="S184"/>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -12544,7 +12565,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -12594,7 +12615,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>16</v>
       </c>
@@ -12636,7 +12657,7 @@
       </c>
       <c r="S187"/>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>16</v>
       </c>
@@ -12677,7 +12698,7 @@
         <v>1.1559999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -12718,7 +12739,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -12768,7 +12789,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>16</v>
       </c>
@@ -12818,7 +12839,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -12867,8 +12888,11 @@
       <c r="R192">
         <v>0.88200000000000001</v>
       </c>
-    </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S192" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>16</v>
       </c>
@@ -12918,7 +12942,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -12968,7 +12992,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -13018,7 +13042,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -13060,7 +13084,7 @@
       </c>
       <c r="S196"/>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -13110,7 +13134,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -13151,7 +13175,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -13201,7 +13225,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -13243,7 +13267,7 @@
       </c>
       <c r="S200"/>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -13293,7 +13317,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -13335,7 +13359,7 @@
       </c>
       <c r="S202"/>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -13377,7 +13401,7 @@
       </c>
       <c r="S203"/>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -13409,7 +13433,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -13460,7 +13484,7 @@
       </c>
       <c r="S205"/>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -13510,7 +13534,7 @@
         <v>1.1870000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -13542,7 +13566,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -13592,7 +13616,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -13634,7 +13658,7 @@
       </c>
       <c r="S209"/>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -13676,7 +13700,7 @@
       </c>
       <c r="S210"/>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -13717,7 +13741,7 @@
         <v>1.282</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -13767,7 +13791,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -13817,7 +13841,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -13859,7 +13883,7 @@
       </c>
       <c r="S214"/>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -13909,7 +13933,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -13951,7 +13975,7 @@
       </c>
       <c r="S216"/>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -14001,7 +14025,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -14043,7 +14067,7 @@
       </c>
       <c r="S218"/>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -14085,7 +14109,7 @@
       </c>
       <c r="S219"/>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -14135,7 +14159,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -14177,7 +14201,7 @@
       </c>
       <c r="S221"/>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -14227,7 +14251,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -14269,7 +14293,7 @@
       </c>
       <c r="S223"/>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -14311,7 +14335,7 @@
       </c>
       <c r="S224"/>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -14353,7 +14377,7 @@
       </c>
       <c r="S225"/>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -14403,7 +14427,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -14453,7 +14477,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -14495,7 +14519,7 @@
       </c>
       <c r="S228"/>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -14537,7 +14561,7 @@
       </c>
       <c r="S229"/>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -14579,7 +14603,7 @@
       </c>
       <c r="S230"/>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -14620,7 +14644,7 @@
         <v>1.143</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -14653,7 +14677,7 @@
       </c>
       <c r="S232"/>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -14703,7 +14727,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -14753,7 +14777,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -14794,7 +14818,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -14844,7 +14868,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -14894,7 +14918,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -14944,7 +14968,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -14994,7 +15018,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -15044,7 +15068,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -15094,7 +15118,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -15144,7 +15168,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -15194,7 +15218,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -15244,7 +15268,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -15294,7 +15318,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -15344,7 +15368,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -15394,7 +15418,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -15444,7 +15468,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -15477,7 +15501,7 @@
       </c>
       <c r="S249"/>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -15527,7 +15551,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -15577,7 +15601,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -15627,7 +15651,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -15677,7 +15701,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -15727,7 +15751,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -15768,7 +15792,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -15818,7 +15842,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -15868,7 +15892,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -15918,7 +15942,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -15968,7 +15992,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -16018,7 +16042,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -16068,7 +16092,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -16118,7 +16142,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -16168,7 +16192,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -16218,7 +16242,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -16277,7 +16301,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -16327,7 +16351,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -16377,7 +16401,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -16427,7 +16451,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -16486,7 +16510,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -16527,7 +16551,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -16577,7 +16601,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -16618,7 +16642,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -16650,7 +16674,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -16700,7 +16724,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -16750,7 +16774,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -16800,7 +16824,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -16859,7 +16883,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -16909,7 +16933,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -16959,7 +16983,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -17009,7 +17033,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -17059,7 +17083,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -17109,7 +17133,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -17159,7 +17183,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -17209,7 +17233,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -17259,7 +17283,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -17309,7 +17333,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -17359,7 +17383,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -17409,7 +17433,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -17459,7 +17483,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -17492,7 +17516,7 @@
       </c>
       <c r="S290"/>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -17542,7 +17566,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -17592,7 +17616,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -17642,7 +17666,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -17692,7 +17716,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -17736,7 +17760,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -17778,7 +17802,7 @@
       </c>
       <c r="S296"/>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -17820,7 +17844,7 @@
       </c>
       <c r="S297"/>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -17870,7 +17894,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -17920,7 +17944,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -17970,7 +17994,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -18012,7 +18036,7 @@
       </c>
       <c r="S301"/>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -18062,7 +18086,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -18112,7 +18136,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -18162,7 +18186,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -18212,7 +18236,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>16</v>
       </c>
@@ -18253,7 +18277,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -18303,7 +18327,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -18344,7 +18368,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -18394,7 +18418,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -18444,7 +18468,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>16</v>
       </c>
@@ -18494,7 +18518,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -18544,7 +18568,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -18594,7 +18618,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -18644,7 +18668,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -18686,7 +18710,7 @@
       </c>
       <c r="S315"/>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -18719,7 +18743,7 @@
       </c>
       <c r="S316"/>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -18751,7 +18775,7 @@
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -18793,7 +18817,7 @@
       </c>
       <c r="S318"/>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -18843,7 +18867,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -18867,7 +18891,7 @@
       </c>
       <c r="S320"/>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -18900,7 +18924,7 @@
       </c>
       <c r="S321"/>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>16</v>
       </c>
@@ -18959,7 +18983,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>16</v>
       </c>
@@ -19009,7 +19033,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>16</v>
       </c>
@@ -19059,7 +19083,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>16</v>
       </c>
@@ -19100,7 +19124,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>16</v>
       </c>
@@ -19150,7 +19174,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>16</v>
       </c>
@@ -19200,7 +19224,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>16</v>
       </c>
@@ -19250,7 +19274,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>16</v>
       </c>
@@ -19300,7 +19324,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>16</v>
       </c>
@@ -19350,7 +19374,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>16</v>
       </c>
@@ -19409,7 +19433,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>16</v>
       </c>
@@ -19450,7 +19474,7 @@
         <v>1.252</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>16</v>
       </c>
@@ -19492,7 +19516,7 @@
       </c>
       <c r="S333"/>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>16</v>
       </c>
@@ -19542,7 +19566,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>16</v>
       </c>
@@ -19592,7 +19616,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>16</v>
       </c>
@@ -19642,7 +19666,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>16</v>
       </c>
@@ -19692,7 +19716,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>16</v>
       </c>
@@ -19751,7 +19775,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>16</v>
       </c>
@@ -19801,7 +19825,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>16</v>
       </c>
@@ -19851,7 +19875,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>16</v>
       </c>
@@ -19884,7 +19908,7 @@
       </c>
       <c r="S341"/>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>16</v>
       </c>
@@ -19908,7 +19932,7 @@
       </c>
       <c r="S342"/>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>16</v>
       </c>
@@ -19941,7 +19965,7 @@
       </c>
       <c r="S343"/>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>16</v>
       </c>
@@ -19964,7 +19988,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>16</v>
       </c>
@@ -19997,7 +20021,7 @@
       </c>
       <c r="S345"/>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>16</v>
       </c>
@@ -20029,7 +20053,7 @@
         <v>1.1319999999999999</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>16</v>
       </c>
@@ -20071,7 +20095,7 @@
       </c>
       <c r="S347"/>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>16</v>
       </c>
@@ -20104,7 +20128,7 @@
       </c>
       <c r="S348"/>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>16</v>
       </c>
@@ -20154,7 +20178,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>16</v>
       </c>
@@ -20196,7 +20220,7 @@
       </c>
       <c r="S350"/>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>16</v>
       </c>
@@ -20246,7 +20270,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>16</v>
       </c>
@@ -20296,7 +20320,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>16</v>
       </c>
@@ -20346,7 +20370,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>16</v>
       </c>
@@ -20396,7 +20420,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>16</v>
       </c>
@@ -20446,7 +20470,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>16</v>
       </c>
@@ -20496,7 +20520,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>16</v>
       </c>
@@ -20546,7 +20570,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>16</v>
       </c>
@@ -20578,7 +20602,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>16</v>
       </c>
@@ -20637,7 +20661,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>16</v>
       </c>
@@ -20670,7 +20694,7 @@
       </c>
       <c r="S360"/>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>16</v>
       </c>
@@ -20720,7 +20744,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>16</v>
       </c>
@@ -20762,7 +20786,7 @@
       </c>
       <c r="S362"/>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>16</v>
       </c>
@@ -20812,7 +20836,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>16</v>
       </c>
@@ -20854,7 +20878,7 @@
       </c>
       <c r="S364"/>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>16</v>
       </c>
@@ -20887,7 +20911,7 @@
       </c>
       <c r="S365"/>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>16</v>
       </c>
@@ -20920,7 +20944,7 @@
       </c>
       <c r="S366"/>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>16</v>
       </c>
@@ -20953,7 +20977,7 @@
       </c>
       <c r="S367"/>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>16</v>
       </c>
@@ -20985,7 +21009,7 @@
         <v>1.075</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>16</v>
       </c>
@@ -21035,7 +21059,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>16</v>
       </c>
@@ -21085,7 +21109,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>16</v>
       </c>
@@ -21127,7 +21151,7 @@
       </c>
       <c r="S371"/>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>16</v>
       </c>
@@ -21177,7 +21201,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>16</v>
       </c>
@@ -21227,7 +21251,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>16</v>
       </c>
@@ -21277,7 +21301,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>16</v>
       </c>
@@ -21327,7 +21351,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>16</v>
       </c>
@@ -21377,7 +21401,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>16</v>
       </c>
@@ -21419,7 +21443,7 @@
       </c>
       <c r="S377"/>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>16</v>
       </c>
@@ -21469,7 +21493,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>16</v>
       </c>
@@ -21511,7 +21535,7 @@
       </c>
       <c r="S379"/>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>16</v>
       </c>
@@ -21553,7 +21577,7 @@
       </c>
       <c r="S380"/>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>16</v>
       </c>
@@ -21595,7 +21619,7 @@
       </c>
       <c r="S381"/>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>16</v>
       </c>
@@ -21636,7 +21660,7 @@
         <v>1.161</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>16</v>
       </c>
@@ -21678,7 +21702,7 @@
       </c>
       <c r="S383"/>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>16</v>
       </c>
@@ -21720,7 +21744,7 @@
       </c>
       <c r="S384"/>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>16</v>
       </c>
@@ -21762,7 +21786,7 @@
       </c>
       <c r="S385"/>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>16</v>
       </c>
@@ -21812,7 +21836,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>16</v>
       </c>
@@ -21862,7 +21886,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>16</v>
       </c>
@@ -21912,7 +21936,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>16</v>
       </c>
@@ -21962,7 +21986,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>16</v>
       </c>
@@ -22004,7 +22028,7 @@
       </c>
       <c r="S390"/>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>16</v>
       </c>
@@ -22046,7 +22070,7 @@
       </c>
       <c r="S391"/>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>16</v>
       </c>
@@ -22096,7 +22120,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>16</v>
       </c>
@@ -22138,7 +22162,7 @@
       </c>
       <c r="S393"/>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -22171,7 +22195,7 @@
       </c>
       <c r="S394"/>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>16</v>
       </c>
@@ -22213,7 +22237,7 @@
       </c>
       <c r="S395"/>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>16</v>
       </c>
@@ -22263,7 +22287,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>16</v>
       </c>
@@ -22307,7 +22331,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>16</v>
       </c>
@@ -22357,7 +22381,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>16</v>
       </c>
@@ -22389,7 +22413,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>16</v>
       </c>
@@ -22421,7 +22445,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>16</v>
       </c>
@@ -22471,7 +22495,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>16</v>
       </c>
@@ -22521,7 +22545,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>16</v>
       </c>
@@ -22571,7 +22595,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>16</v>
       </c>
@@ -22612,7 +22636,7 @@
         <v>1.1060000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>16</v>
       </c>
@@ -22662,7 +22686,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>16</v>
       </c>
@@ -22704,7 +22728,7 @@
       </c>
       <c r="S406"/>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>16</v>
       </c>
@@ -22746,7 +22770,7 @@
       </c>
       <c r="S407"/>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>16</v>
       </c>
@@ -22788,7 +22812,7 @@
       </c>
       <c r="S408"/>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>16</v>
       </c>
@@ -22838,7 +22862,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -22880,7 +22904,7 @@
       </c>
       <c r="S410"/>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>16</v>
       </c>
@@ -22930,7 +22954,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>16</v>
       </c>
@@ -22971,7 +22995,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>16</v>
       </c>
@@ -23013,7 +23037,7 @@
       </c>
       <c r="S413"/>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>16</v>
       </c>
@@ -23064,7 +23088,7 @@
       </c>
       <c r="S414"/>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>16</v>
       </c>
@@ -23106,7 +23130,7 @@
       </c>
       <c r="S415"/>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>16</v>
       </c>
@@ -23148,7 +23172,7 @@
       </c>
       <c r="S416"/>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>16</v>
       </c>
@@ -23198,7 +23222,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>16</v>
       </c>
@@ -23248,7 +23272,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>16</v>
       </c>
@@ -23289,7 +23313,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>16</v>
       </c>
@@ -23331,7 +23355,7 @@
       </c>
       <c r="S420"/>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>16</v>
       </c>
@@ -23381,7 +23405,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>16</v>
       </c>
@@ -23431,7 +23455,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>16</v>
       </c>
@@ -23473,7 +23497,7 @@
       </c>
       <c r="S423"/>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>16</v>
       </c>
@@ -23523,7 +23547,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>16</v>
       </c>
@@ -23565,7 +23589,7 @@
       </c>
       <c r="S425"/>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>16</v>
       </c>
@@ -23615,7 +23639,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>16</v>
       </c>
@@ -23657,7 +23681,7 @@
       </c>
       <c r="S427"/>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -23699,7 +23723,7 @@
       </c>
       <c r="S428"/>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>16</v>
       </c>
@@ -23749,7 +23773,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>16</v>
       </c>
@@ -23791,7 +23815,7 @@
       </c>
       <c r="S430"/>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>16</v>
       </c>
@@ -23824,7 +23848,7 @@
       </c>
       <c r="S431"/>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -23866,7 +23890,7 @@
       </c>
       <c r="S432"/>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>16</v>
       </c>
@@ -23908,7 +23932,7 @@
       </c>
       <c r="S433"/>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>16</v>
       </c>
@@ -23958,7 +23982,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>16</v>
       </c>
@@ -24009,7 +24033,7 @@
       </c>
       <c r="S435"/>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>16</v>
       </c>
@@ -24059,7 +24083,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>16</v>
       </c>
@@ -24092,7 +24116,7 @@
       </c>
       <c r="S437"/>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>16</v>
       </c>
@@ -24134,7 +24158,7 @@
       </c>
       <c r="S438"/>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>16</v>
       </c>
@@ -24176,7 +24200,7 @@
       </c>
       <c r="S439"/>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>16</v>
       </c>
@@ -24218,7 +24242,7 @@
       </c>
       <c r="S440"/>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>16</v>
       </c>
@@ -24242,7 +24266,7 @@
       </c>
       <c r="S441"/>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>16</v>
       </c>
@@ -24284,7 +24308,7 @@
       </c>
       <c r="S442"/>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>16</v>
       </c>
@@ -24308,7 +24332,7 @@
       </c>
       <c r="S443"/>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>16</v>
       </c>
@@ -24349,7 +24373,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>16</v>
       </c>
@@ -24399,7 +24423,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -24449,7 +24473,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>16</v>
       </c>
@@ -24491,7 +24515,7 @@
       </c>
       <c r="S447"/>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>16</v>
       </c>
@@ -24541,7 +24565,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>16</v>
       </c>
@@ -24582,7 +24606,7 @@
         <v>1.147</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>16</v>
       </c>
@@ -24623,7 +24647,7 @@
         <v>1.3280000000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>16</v>
       </c>
@@ -24665,7 +24689,7 @@
       </c>
       <c r="S451"/>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>16</v>
       </c>
@@ -24707,7 +24731,7 @@
       </c>
       <c r="S452"/>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -24740,7 +24764,7 @@
       </c>
       <c r="S453"/>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>16</v>
       </c>
@@ -24790,7 +24814,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>16</v>
       </c>
@@ -24831,7 +24855,7 @@
         <v>1.046</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>16</v>
       </c>
@@ -24873,7 +24897,7 @@
       </c>
       <c r="S456"/>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>16</v>
       </c>
@@ -24923,7 +24947,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>16</v>
       </c>
@@ -24973,7 +24997,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>16</v>
       </c>
@@ -25023,7 +25047,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>16</v>
       </c>
@@ -25065,7 +25089,7 @@
       </c>
       <c r="S460"/>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>16</v>
       </c>
@@ -25107,7 +25131,7 @@
       </c>
       <c r="S461"/>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>16</v>
       </c>
@@ -25149,7 +25173,7 @@
       </c>
       <c r="S462"/>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>16</v>
       </c>
@@ -25199,7 +25223,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>16</v>
       </c>
@@ -25240,7 +25264,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>16</v>
       </c>
@@ -25281,7 +25305,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>16</v>
       </c>
@@ -25313,7 +25337,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>16</v>
       </c>
@@ -25355,7 +25379,7 @@
       </c>
       <c r="S467"/>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>16</v>
       </c>
@@ -25405,7 +25429,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>16</v>
       </c>
@@ -25446,7 +25470,7 @@
         <v>1.254</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>16</v>
       </c>
@@ -25496,7 +25520,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>16</v>
       </c>
@@ -25546,7 +25570,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>16</v>
       </c>
@@ -25588,7 +25612,7 @@
       </c>
       <c r="S472"/>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>16</v>
       </c>
@@ -25629,7 +25653,7 @@
         <v>0.73399999999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>16</v>
       </c>
@@ -25662,7 +25686,7 @@
       </c>
       <c r="S474"/>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>16</v>
       </c>
@@ -25704,7 +25728,7 @@
       </c>
       <c r="S475"/>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>16</v>
       </c>
@@ -25746,7 +25770,7 @@
       </c>
       <c r="S476"/>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>16</v>
       </c>
@@ -25796,7 +25820,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>16</v>
       </c>
@@ -25837,7 +25861,7 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>16</v>
       </c>
@@ -25878,7 +25902,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>16</v>
       </c>
@@ -25920,7 +25944,7 @@
       </c>
       <c r="S480"/>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>16</v>
       </c>
@@ -25962,7 +25986,7 @@
       </c>
       <c r="S481"/>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>16</v>
       </c>
@@ -31958,7 +31982,9 @@
       <c r="R604">
         <v>2.5640000000000001</v>
       </c>
-      <c r="S604"/>
+      <c r="S604" t="s">
+        <v>896</v>
+      </c>
     </row>
     <row r="605" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
@@ -35112,7 +35138,9 @@
       <c r="R679">
         <v>1.0449999999999999</v>
       </c>
-      <c r="S679"/>
+      <c r="S679" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="680" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
@@ -35604,7 +35632,9 @@
       <c r="R691">
         <v>1.0049999999999999</v>
       </c>
-      <c r="S691"/>
+      <c r="S691" t="s">
+        <v>901</v>
+      </c>
     </row>
     <row r="692" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
@@ -36594,7 +36624,9 @@
       <c r="R714">
         <v>0.93200000000000005</v>
       </c>
-      <c r="S714"/>
+      <c r="S714" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="715" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
@@ -38200,7 +38232,7 @@
       </c>
       <c r="S752"/>
     </row>
-    <row r="753" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>139</v>
       </c>
@@ -38240,8 +38272,9 @@
       <c r="R753">
         <v>0.95099999999999996</v>
       </c>
-    </row>
-    <row r="754" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S753"/>
+    </row>
+    <row r="754" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>139</v>
       </c>
@@ -38281,8 +38314,9 @@
       <c r="R754">
         <v>0.86499999999999999</v>
       </c>
-    </row>
-    <row r="755" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S754"/>
+    </row>
+    <row r="755" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>139</v>
       </c>
@@ -38322,8 +38356,9 @@
       <c r="R755">
         <v>1.07</v>
       </c>
-    </row>
-    <row r="756" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S755"/>
+    </row>
+    <row r="756" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>139</v>
       </c>
@@ -38363,8 +38398,9 @@
       <c r="R756">
         <v>1.169</v>
       </c>
-    </row>
-    <row r="757" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S756"/>
+    </row>
+    <row r="757" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>139</v>
       </c>
@@ -38404,8 +38440,9 @@
       <c r="R757">
         <v>1.0489999999999999</v>
       </c>
-    </row>
-    <row r="758" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S757"/>
+    </row>
+    <row r="758" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>139</v>
       </c>
@@ -38445,8 +38482,11 @@
       <c r="R758">
         <v>0.998</v>
       </c>
-    </row>
-    <row r="759" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S758" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="759" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>139</v>
       </c>
@@ -38486,8 +38526,9 @@
       <c r="R759">
         <v>1.022</v>
       </c>
-    </row>
-    <row r="760" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S759"/>
+    </row>
+    <row r="760" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>139</v>
       </c>
@@ -38527,8 +38568,9 @@
       <c r="R760">
         <v>1.419</v>
       </c>
-    </row>
-    <row r="761" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S760"/>
+    </row>
+    <row r="761" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>139</v>
       </c>
@@ -38568,8 +38610,9 @@
       <c r="R761">
         <v>1.117</v>
       </c>
-    </row>
-    <row r="762" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S761"/>
+    </row>
+    <row r="762" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>139</v>
       </c>
@@ -38609,8 +38652,9 @@
       <c r="R762">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="763" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S762"/>
+    </row>
+    <row r="763" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>139</v>
       </c>
@@ -38650,8 +38694,9 @@
       <c r="R763">
         <v>1.028</v>
       </c>
-    </row>
-    <row r="764" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S763"/>
+    </row>
+    <row r="764" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>139</v>
       </c>
@@ -38691,8 +38736,9 @@
       <c r="R764">
         <v>1.613</v>
       </c>
-    </row>
-    <row r="765" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S764"/>
+    </row>
+    <row r="765" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>139</v>
       </c>
@@ -38732,8 +38778,9 @@
       <c r="R765">
         <v>0.93500000000000005</v>
       </c>
-    </row>
-    <row r="766" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S765"/>
+    </row>
+    <row r="766" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>139</v>
       </c>
@@ -38773,8 +38820,9 @@
       <c r="R766">
         <v>1.042</v>
       </c>
-    </row>
-    <row r="767" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S766"/>
+    </row>
+    <row r="767" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>139</v>
       </c>
@@ -38814,8 +38862,9 @@
       <c r="R767">
         <v>0.999</v>
       </c>
-    </row>
-    <row r="768" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S767"/>
+    </row>
+    <row r="768" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>139</v>
       </c>
@@ -38846,6 +38895,7 @@
       <c r="R768">
         <v>1.0640000000000001</v>
       </c>
+      <c r="S768"/>
     </row>
     <row r="769" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
@@ -41812,7 +41862,9 @@
       <c r="R839">
         <v>0.63800000000000001</v>
       </c>
-      <c r="S839"/>
+      <c r="S839" t="s">
+        <v>898</v>
+      </c>
     </row>
     <row r="840" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
@@ -49271,7 +49323,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}"/>
+  <autoFilter ref="A1:S1037" xr:uid="{29751ECF-5867-4DFC-949B-BE61CEB11EBC}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="e"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LineClass/levels_pub.xlsx
+++ b/LineClass/levels_pub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F47FBE-A511-4912-A02C-3CC743A5B83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3102C0B-7C35-4A08-982D-F07DF06DD445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="43920" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
+    <workbookView xWindow="525" yWindow="3510" windowWidth="51075" windowHeight="17505" xr2:uid="{68E62A3F-E4FB-447B-97FA-80FE60CCF832}"/>
   </bookViews>
   <sheets>
     <sheet name="levels_pub" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7303" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7307" uniqueCount="907">
   <si>
     <t>conf</t>
   </si>
@@ -2745,6 +2745,18 @@
   </si>
   <si>
     <t>059003.000625</t>
+  </si>
+  <si>
+    <t>059003.000677</t>
+  </si>
+  <si>
+    <t>059003.000684</t>
+  </si>
+  <si>
+    <t>059003.000649</t>
+  </si>
+  <si>
+    <t>059003.000672</t>
   </si>
 </sst>
 </file>
@@ -2887,7 +2899,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3073,6 +3085,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -3234,10 +3252,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3632,7 +3653,7 @@
     <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3684,7 +3705,7 @@
       <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="Q1" t="s">
@@ -5515,6 +5536,7 @@
       <c r="O42">
         <v>54158.400000000001</v>
       </c>
+      <c r="P42"/>
       <c r="Q42">
         <v>2.5</v>
       </c>
@@ -6248,6 +6270,7 @@
       <c r="O57">
         <v>63128.5</v>
       </c>
+      <c r="P57"/>
       <c r="Q57">
         <v>0.5</v>
       </c>
@@ -7067,6 +7090,7 @@
       <c r="O73">
         <v>65631</v>
       </c>
+      <c r="P73"/>
       <c r="Q73">
         <v>0.5</v>
       </c>
@@ -8550,6 +8574,7 @@
       <c r="O103">
         <v>68762.3</v>
       </c>
+      <c r="P103"/>
       <c r="Q103">
         <v>0.5</v>
       </c>
@@ -8951,6 +8976,7 @@
       <c r="O111">
         <v>69366.399999999994</v>
       </c>
+      <c r="P111"/>
       <c r="Q111">
         <v>1.5</v>
       </c>
@@ -9125,6 +9151,7 @@
       <c r="O115">
         <v>70304.2</v>
       </c>
+      <c r="P115"/>
       <c r="Q115">
         <v>2.5</v>
       </c>
@@ -9217,6 +9244,7 @@
       <c r="O117">
         <v>70478</v>
       </c>
+      <c r="P117"/>
       <c r="Q117">
         <v>0.5</v>
       </c>
@@ -9259,6 +9287,7 @@
       <c r="O118">
         <v>70577.899999999994</v>
       </c>
+      <c r="P118"/>
       <c r="Q118">
         <v>1.5</v>
       </c>
@@ -9701,6 +9730,7 @@
       <c r="O127">
         <v>72363.600000000006</v>
       </c>
+      <c r="P127"/>
       <c r="Q127">
         <v>1.5</v>
       </c>
@@ -9793,6 +9823,7 @@
       <c r="O129">
         <v>72944.7</v>
       </c>
+      <c r="P129"/>
       <c r="Q129">
         <v>0.5</v>
       </c>
@@ -9885,6 +9916,7 @@
       <c r="O131">
         <v>73369.899999999994</v>
       </c>
+      <c r="P131"/>
       <c r="Q131">
         <v>1.5</v>
       </c>
@@ -10245,6 +10277,7 @@
       <c r="O138">
         <v>74670.600000000006</v>
       </c>
+      <c r="P138"/>
       <c r="Q138">
         <v>2.5</v>
       </c>
@@ -10287,6 +10320,7 @@
       <c r="O139">
         <v>75159.899999999994</v>
       </c>
+      <c r="P139"/>
       <c r="Q139">
         <v>1.5</v>
       </c>
@@ -10438,6 +10472,7 @@
       <c r="O142">
         <v>75420.7</v>
       </c>
+      <c r="P142"/>
       <c r="Q142">
         <v>0.5</v>
       </c>
@@ -11780,6 +11815,7 @@
       <c r="O169">
         <v>82034.3</v>
       </c>
+      <c r="P169"/>
       <c r="Q169">
         <v>4.5</v>
       </c>
@@ -11972,6 +12008,7 @@
       <c r="O173">
         <v>83140.800000000003</v>
       </c>
+      <c r="P173"/>
       <c r="Q173">
         <v>2.5</v>
       </c>
@@ -12064,6 +12101,7 @@
       <c r="O175">
         <v>83488.399999999994</v>
       </c>
+      <c r="P175"/>
       <c r="Q175">
         <v>0.5</v>
       </c>
@@ -12306,6 +12344,7 @@
       <c r="O180">
         <v>84315.7</v>
       </c>
+      <c r="P180"/>
       <c r="Q180">
         <v>2.5</v>
       </c>
@@ -12507,6 +12546,7 @@
       <c r="O184">
         <v>84630.8</v>
       </c>
+      <c r="P184"/>
       <c r="Q184">
         <v>0.5</v>
       </c>
@@ -12649,6 +12689,7 @@
       <c r="O187">
         <v>84871.5</v>
       </c>
+      <c r="P187"/>
       <c r="Q187">
         <v>2.5</v>
       </c>
@@ -12691,6 +12732,7 @@
       <c r="O188">
         <v>84887</v>
       </c>
+      <c r="P188"/>
       <c r="Q188">
         <v>3.5</v>
       </c>
@@ -12882,6 +12924,7 @@
       <c r="O192">
         <v>86015.9</v>
       </c>
+      <c r="P192"/>
       <c r="Q192">
         <v>3.5</v>
       </c>
@@ -13076,6 +13119,7 @@
       <c r="O196">
         <v>87291.5</v>
       </c>
+      <c r="P196"/>
       <c r="Q196">
         <v>0.5</v>
       </c>
@@ -13259,6 +13303,7 @@
       <c r="O200">
         <v>88538.4</v>
       </c>
+      <c r="P200"/>
       <c r="Q200">
         <v>2.5</v>
       </c>
@@ -13351,6 +13396,7 @@
       <c r="O202">
         <v>89509.8</v>
       </c>
+      <c r="P202"/>
       <c r="Q202">
         <v>1.5</v>
       </c>
@@ -13393,6 +13439,7 @@
       <c r="O203">
         <v>89672.3</v>
       </c>
+      <c r="P203"/>
       <c r="Q203">
         <v>0.5</v>
       </c>
@@ -13476,6 +13523,7 @@
       <c r="O205">
         <v>90091.7</v>
       </c>
+      <c r="P205"/>
       <c r="Q205">
         <v>2.5</v>
       </c>
@@ -13527,6 +13575,7 @@
       <c r="O206">
         <v>90172.3</v>
       </c>
+      <c r="P206"/>
       <c r="Q206">
         <v>3.5</v>
       </c>
@@ -13650,6 +13699,7 @@
       <c r="O209">
         <v>91039.2</v>
       </c>
+      <c r="P209"/>
       <c r="Q209">
         <v>1.5</v>
       </c>
@@ -13692,6 +13742,7 @@
       <c r="O210">
         <v>91642.6</v>
       </c>
+      <c r="P210"/>
       <c r="Q210">
         <v>2.5</v>
       </c>
@@ -13734,6 +13785,7 @@
       <c r="O211">
         <v>92210.7</v>
       </c>
+      <c r="P211"/>
       <c r="Q211">
         <v>3.5</v>
       </c>
@@ -13875,6 +13927,7 @@
       <c r="O214">
         <v>93427.9</v>
       </c>
+      <c r="P214"/>
       <c r="Q214">
         <v>1.5</v>
       </c>
@@ -13967,6 +14020,7 @@
       <c r="O216">
         <v>93597.1</v>
       </c>
+      <c r="P216"/>
       <c r="Q216">
         <v>0.5</v>
       </c>
@@ -14059,6 +14113,7 @@
       <c r="O218">
         <v>94239.8</v>
       </c>
+      <c r="P218"/>
       <c r="Q218">
         <v>2.5</v>
       </c>
@@ -14101,6 +14156,7 @@
       <c r="O219">
         <v>95006.9</v>
       </c>
+      <c r="P219"/>
       <c r="Q219">
         <v>2.5</v>
       </c>
@@ -14193,6 +14249,7 @@
       <c r="O221">
         <v>95551.5</v>
       </c>
+      <c r="P221"/>
       <c r="Q221">
         <v>1.5</v>
       </c>
@@ -14285,6 +14342,7 @@
       <c r="O223">
         <v>97374.399999999994</v>
       </c>
+      <c r="P223"/>
       <c r="Q223">
         <v>1.5</v>
       </c>
@@ -14327,6 +14385,7 @@
       <c r="O224">
         <v>98148.6</v>
       </c>
+      <c r="P224"/>
       <c r="Q224">
         <v>2.5</v>
       </c>
@@ -14369,6 +14428,7 @@
       <c r="O225">
         <v>98274.6</v>
       </c>
+      <c r="P225"/>
       <c r="Q225">
         <v>0.5</v>
       </c>
@@ -14511,6 +14571,7 @@
       <c r="O228">
         <v>100126.8</v>
       </c>
+      <c r="P228"/>
       <c r="Q228">
         <v>0.5</v>
       </c>
@@ -14553,6 +14614,7 @@
       <c r="O229">
         <v>102482.1</v>
       </c>
+      <c r="P229"/>
       <c r="Q229">
         <v>1.5</v>
       </c>
@@ -14595,6 +14657,7 @@
       <c r="O230">
         <v>105360.7</v>
       </c>
+      <c r="P230"/>
       <c r="Q230">
         <v>2.5</v>
       </c>
@@ -14637,6 +14700,7 @@
       <c r="O231">
         <v>108172.5</v>
       </c>
+      <c r="P231"/>
       <c r="Q231">
         <v>3.5</v>
       </c>
@@ -14669,6 +14733,7 @@
       <c r="O232">
         <v>108850.8</v>
       </c>
+      <c r="P232"/>
       <c r="Q232">
         <v>0.5</v>
       </c>
@@ -15493,6 +15558,7 @@
       <c r="O249">
         <v>112214.9</v>
       </c>
+      <c r="P249"/>
       <c r="Q249">
         <v>1.5</v>
       </c>
@@ -17508,6 +17574,7 @@
       <c r="O290">
         <v>116010</v>
       </c>
+      <c r="P290"/>
       <c r="Q290">
         <v>6.5</v>
       </c>
@@ -17750,6 +17817,7 @@
       <c r="O295">
         <v>116406.7</v>
       </c>
+      <c r="P295"/>
       <c r="Q295">
         <v>2.5</v>
       </c>
@@ -17794,6 +17862,7 @@
       <c r="O296">
         <v>116437.2</v>
       </c>
+      <c r="P296"/>
       <c r="Q296">
         <v>2.5</v>
       </c>
@@ -17836,6 +17905,7 @@
       <c r="O297">
         <v>116482.2</v>
       </c>
+      <c r="P297"/>
       <c r="Q297">
         <v>1.5</v>
       </c>
@@ -18028,6 +18098,7 @@
       <c r="O301">
         <v>116804.7</v>
       </c>
+      <c r="P301"/>
       <c r="Q301">
         <v>0.5</v>
       </c>
@@ -18702,6 +18773,7 @@
       <c r="O315">
         <v>117665.3</v>
       </c>
+      <c r="P315"/>
       <c r="Q315">
         <v>4.5</v>
       </c>
@@ -18735,6 +18807,7 @@
       <c r="O316">
         <v>117733.1</v>
       </c>
+      <c r="P316"/>
       <c r="Q316">
         <v>0.5</v>
       </c>
@@ -18768,6 +18841,7 @@
       <c r="O317">
         <v>117761</v>
       </c>
+      <c r="P317"/>
       <c r="Q317">
         <v>3.5</v>
       </c>
@@ -18809,6 +18883,7 @@
       <c r="O318">
         <v>117827.4</v>
       </c>
+      <c r="P318"/>
       <c r="Q318">
         <v>1.5</v>
       </c>
@@ -18883,6 +18958,7 @@
       <c r="O320">
         <v>117888.6</v>
       </c>
+      <c r="P320"/>
       <c r="Q320">
         <v>2.5</v>
       </c>
@@ -18916,6 +18992,7 @@
       <c r="O321">
         <v>117972.7</v>
       </c>
+      <c r="P321"/>
       <c r="Q321">
         <v>2.5</v>
       </c>
@@ -19117,6 +19194,7 @@
       <c r="O325">
         <v>118086.9</v>
       </c>
+      <c r="P325"/>
       <c r="Q325">
         <v>3.5</v>
       </c>
@@ -19467,6 +19545,7 @@
       <c r="O332">
         <v>118504.2</v>
       </c>
+      <c r="P332"/>
       <c r="Q332">
         <v>3.5</v>
       </c>
@@ -19508,6 +19587,7 @@
       <c r="O333">
         <v>118596.3</v>
       </c>
+      <c r="P333"/>
       <c r="Q333">
         <v>4.5</v>
       </c>
@@ -19900,6 +19980,7 @@
       <c r="O341">
         <v>119248.3</v>
       </c>
+      <c r="P341"/>
       <c r="Q341">
         <v>4.5</v>
       </c>
@@ -19924,6 +20005,7 @@
       <c r="O342">
         <v>119258.1</v>
       </c>
+      <c r="P342"/>
       <c r="Q342">
         <v>1.5</v>
       </c>
@@ -19957,6 +20039,7 @@
       <c r="O343">
         <v>119367.6</v>
       </c>
+      <c r="P343"/>
       <c r="Q343">
         <v>2.5</v>
       </c>
@@ -19981,6 +20064,7 @@
       <c r="O344">
         <v>119376.3</v>
       </c>
+      <c r="P344"/>
       <c r="Q344">
         <v>3.5</v>
       </c>
@@ -20013,6 +20097,7 @@
       <c r="O345">
         <v>119778.7</v>
       </c>
+      <c r="P345"/>
       <c r="Q345">
         <v>5.5</v>
       </c>
@@ -20046,6 +20131,7 @@
       <c r="O346">
         <v>119938</v>
       </c>
+      <c r="P346"/>
       <c r="Q346">
         <v>3.5</v>
       </c>
@@ -20087,6 +20173,7 @@
       <c r="O347">
         <v>119959.7</v>
       </c>
+      <c r="P347"/>
       <c r="Q347">
         <v>2.5</v>
       </c>
@@ -20120,6 +20207,7 @@
       <c r="O348">
         <v>119970.6</v>
       </c>
+      <c r="P348"/>
       <c r="Q348">
         <v>4.5</v>
       </c>
@@ -20212,6 +20300,7 @@
       <c r="O350">
         <v>120658.3</v>
       </c>
+      <c r="P350"/>
       <c r="Q350">
         <v>0.5</v>
       </c>
@@ -20595,6 +20684,7 @@
       <c r="O358">
         <v>121583.5</v>
       </c>
+      <c r="P358"/>
       <c r="Q358">
         <v>3.5</v>
       </c>
@@ -20686,6 +20776,7 @@
       <c r="O360">
         <v>121635</v>
       </c>
+      <c r="P360"/>
       <c r="Q360">
         <v>4.5</v>
       </c>
@@ -20778,6 +20869,7 @@
       <c r="O362">
         <v>121757.4</v>
       </c>
+      <c r="P362"/>
       <c r="Q362">
         <v>2.5</v>
       </c>
@@ -20870,6 +20962,7 @@
       <c r="O364">
         <v>122593.3</v>
       </c>
+      <c r="P364"/>
       <c r="Q364">
         <v>1.5</v>
       </c>
@@ -20903,6 +20996,7 @@
       <c r="O365">
         <v>122910.9</v>
       </c>
+      <c r="P365"/>
       <c r="Q365">
         <v>4.5</v>
       </c>
@@ -20936,6 +21030,7 @@
       <c r="O366">
         <v>122933.4</v>
       </c>
+      <c r="P366"/>
       <c r="Q366">
         <v>5.5</v>
       </c>
@@ -20969,6 +21064,7 @@
       <c r="O367">
         <v>123038.1</v>
       </c>
+      <c r="P367"/>
       <c r="Q367">
         <v>2.5</v>
       </c>
@@ -21002,6 +21098,7 @@
       <c r="O368">
         <v>123086.8</v>
       </c>
+      <c r="P368"/>
       <c r="Q368">
         <v>3.5</v>
       </c>
@@ -21143,6 +21240,7 @@
       <c r="O371">
         <v>128448.6</v>
       </c>
+      <c r="P371"/>
       <c r="Q371">
         <v>0.5</v>
       </c>
@@ -21435,6 +21533,7 @@
       <c r="O377">
         <v>128883.3</v>
       </c>
+      <c r="P377"/>
       <c r="Q377">
         <v>1.5</v>
       </c>
@@ -21527,6 +21626,7 @@
       <c r="O379">
         <v>128957.5</v>
       </c>
+      <c r="P379"/>
       <c r="Q379">
         <v>1.5</v>
       </c>
@@ -21569,6 +21669,7 @@
       <c r="O380">
         <v>129013.3</v>
       </c>
+      <c r="P380"/>
       <c r="Q380">
         <v>2.5</v>
       </c>
@@ -21611,6 +21712,7 @@
       <c r="O381">
         <v>130099.6</v>
       </c>
+      <c r="P381"/>
       <c r="Q381">
         <v>0.5</v>
       </c>
@@ -21653,6 +21755,7 @@
       <c r="O382">
         <v>130293</v>
       </c>
+      <c r="P382"/>
       <c r="Q382">
         <v>3.5</v>
       </c>
@@ -21694,6 +21797,7 @@
       <c r="O383">
         <v>130441.60000000001</v>
       </c>
+      <c r="P383"/>
       <c r="Q383">
         <v>1.5</v>
       </c>
@@ -21736,6 +21840,7 @@
       <c r="O384">
         <v>130629.1</v>
       </c>
+      <c r="P384"/>
       <c r="Q384">
         <v>2.5</v>
       </c>
@@ -21778,6 +21883,7 @@
       <c r="O385">
         <v>132356.79999999999</v>
       </c>
+      <c r="P385"/>
       <c r="Q385">
         <v>2.5</v>
       </c>
@@ -22020,6 +22126,7 @@
       <c r="O390">
         <v>132865.20000000001</v>
       </c>
+      <c r="P390"/>
       <c r="Q390">
         <v>2.5</v>
       </c>
@@ -22062,6 +22169,7 @@
       <c r="O391">
         <v>132902.6</v>
       </c>
+      <c r="P391"/>
       <c r="Q391">
         <v>1.5</v>
       </c>
@@ -22154,6 +22262,7 @@
       <c r="O393">
         <v>132959.20000000001</v>
       </c>
+      <c r="P393"/>
       <c r="Q393">
         <v>4.5</v>
       </c>
@@ -22187,6 +22296,7 @@
       <c r="O394">
         <v>133036.5</v>
       </c>
+      <c r="P394"/>
       <c r="Q394">
         <v>2.5</v>
       </c>
@@ -22229,6 +22339,7 @@
       <c r="O395">
         <v>133047.79999999999</v>
       </c>
+      <c r="P395"/>
       <c r="Q395">
         <v>0.5</v>
       </c>
@@ -22321,6 +22432,7 @@
       <c r="O397">
         <v>133050.4</v>
       </c>
+      <c r="P397"/>
       <c r="Q397">
         <v>3.5</v>
       </c>
@@ -22629,6 +22741,7 @@
       <c r="O404">
         <v>133412.29999999999</v>
       </c>
+      <c r="P404"/>
       <c r="Q404">
         <v>3.5</v>
       </c>
@@ -22720,6 +22833,7 @@
       <c r="O406">
         <v>133493.70000000001</v>
       </c>
+      <c r="P406"/>
       <c r="Q406">
         <v>0.5</v>
       </c>
@@ -22762,6 +22876,7 @@
       <c r="O407">
         <v>133508.9</v>
       </c>
+      <c r="P407"/>
       <c r="Q407">
         <v>5.5</v>
       </c>
@@ -22804,6 +22919,7 @@
       <c r="O408">
         <v>133556.1</v>
       </c>
+      <c r="P408"/>
       <c r="Q408">
         <v>6.5</v>
       </c>
@@ -22896,6 +23012,7 @@
       <c r="O410">
         <v>133636.70000000001</v>
       </c>
+      <c r="P410"/>
       <c r="Q410">
         <v>0.5</v>
       </c>
@@ -23029,6 +23146,7 @@
       <c r="O413">
         <v>133713.79999999999</v>
       </c>
+      <c r="P413"/>
       <c r="Q413">
         <v>1.5</v>
       </c>
@@ -23080,6 +23198,7 @@
       <c r="O414">
         <v>133794.4</v>
       </c>
+      <c r="P414"/>
       <c r="Q414">
         <v>2.5</v>
       </c>
@@ -23122,6 +23241,7 @@
       <c r="O415">
         <v>133965.79999999999</v>
       </c>
+      <c r="P415"/>
       <c r="Q415">
         <v>1.5</v>
       </c>
@@ -23164,6 +23284,7 @@
       <c r="O416">
         <v>133992.1</v>
       </c>
+      <c r="P416"/>
       <c r="Q416">
         <v>1.5</v>
       </c>
@@ -23306,6 +23427,7 @@
       <c r="O419">
         <v>134099</v>
       </c>
+      <c r="P419"/>
       <c r="Q419">
         <v>3.5</v>
       </c>
@@ -23347,6 +23469,7 @@
       <c r="O420">
         <v>134249.1</v>
       </c>
+      <c r="P420"/>
       <c r="Q420">
         <v>1.5</v>
       </c>
@@ -23489,6 +23612,7 @@
       <c r="O423">
         <v>134301.4</v>
       </c>
+      <c r="P423"/>
       <c r="Q423">
         <v>2.5</v>
       </c>
@@ -23581,6 +23705,7 @@
       <c r="O425">
         <v>134345.1</v>
       </c>
+      <c r="P425"/>
       <c r="Q425">
         <v>1.5</v>
       </c>
@@ -23673,6 +23798,7 @@
       <c r="O427">
         <v>134417.9</v>
       </c>
+      <c r="P427"/>
       <c r="Q427">
         <v>2.5</v>
       </c>
@@ -23715,6 +23841,7 @@
       <c r="O428">
         <v>134514.1</v>
       </c>
+      <c r="P428"/>
       <c r="Q428">
         <v>4.5</v>
       </c>
@@ -23807,6 +23934,7 @@
       <c r="O430">
         <v>134697.20000000001</v>
       </c>
+      <c r="P430"/>
       <c r="Q430">
         <v>2.5</v>
       </c>
@@ -23840,6 +23968,7 @@
       <c r="O431">
         <v>134829.4</v>
       </c>
+      <c r="P431"/>
       <c r="Q431">
         <v>6.5</v>
       </c>
@@ -23882,6 +24011,7 @@
       <c r="O432">
         <v>134831.6</v>
       </c>
+      <c r="P432"/>
       <c r="Q432">
         <v>1.5</v>
       </c>
@@ -23924,6 +24054,7 @@
       <c r="O433">
         <v>134931.4</v>
       </c>
+      <c r="P433"/>
       <c r="Q433">
         <v>2.5</v>
       </c>
@@ -24025,6 +24156,7 @@
       <c r="O435">
         <v>134975.5</v>
       </c>
+      <c r="P435"/>
       <c r="Q435">
         <v>1.5</v>
       </c>
@@ -24108,6 +24240,7 @@
       <c r="O437">
         <v>135138.79999999999</v>
       </c>
+      <c r="P437"/>
       <c r="Q437">
         <v>5.5</v>
       </c>
@@ -24150,6 +24283,7 @@
       <c r="O438">
         <v>135252.29999999999</v>
       </c>
+      <c r="P438"/>
       <c r="Q438">
         <v>0.5</v>
       </c>
@@ -24192,6 +24326,7 @@
       <c r="O439">
         <v>135275.5</v>
       </c>
+      <c r="P439"/>
       <c r="Q439">
         <v>2.5</v>
       </c>
@@ -24234,6 +24369,7 @@
       <c r="O440">
         <v>135296.20000000001</v>
       </c>
+      <c r="P440"/>
       <c r="Q440">
         <v>1.5</v>
       </c>
@@ -24258,6 +24394,7 @@
       <c r="O441">
         <v>135347.9</v>
       </c>
+      <c r="P441"/>
       <c r="Q441">
         <v>7.5</v>
       </c>
@@ -24300,6 +24437,7 @@
       <c r="O442">
         <v>135358.9</v>
       </c>
+      <c r="P442"/>
       <c r="Q442">
         <v>0.5</v>
       </c>
@@ -24324,6 +24462,7 @@
       <c r="O443">
         <v>135618.20000000001</v>
       </c>
+      <c r="P443"/>
       <c r="Q443">
         <v>4.5</v>
       </c>
@@ -24507,6 +24646,7 @@
       <c r="O447">
         <v>136100.29999999999</v>
       </c>
+      <c r="P447"/>
       <c r="Q447">
         <v>4.5</v>
       </c>
@@ -24599,6 +24739,7 @@
       <c r="O449">
         <v>136185.79999999999</v>
       </c>
+      <c r="P449"/>
       <c r="Q449">
         <v>3.5</v>
       </c>
@@ -24640,6 +24781,7 @@
       <c r="O450">
         <v>136211.79999999999</v>
       </c>
+      <c r="P450"/>
       <c r="Q450">
         <v>3.5</v>
       </c>
@@ -24681,6 +24823,7 @@
       <c r="O451">
         <v>136351.4</v>
       </c>
+      <c r="P451"/>
       <c r="Q451">
         <v>0.5</v>
       </c>
@@ -24723,6 +24866,7 @@
       <c r="O452">
         <v>136362.4</v>
       </c>
+      <c r="P452"/>
       <c r="Q452">
         <v>2.5</v>
       </c>
@@ -24756,6 +24900,7 @@
       <c r="O453">
         <v>136396.1</v>
       </c>
+      <c r="P453"/>
       <c r="Q453">
         <v>5.5</v>
       </c>
@@ -24848,6 +24993,7 @@
       <c r="O455">
         <v>136439.6</v>
       </c>
+      <c r="P455"/>
       <c r="Q455">
         <v>3.5</v>
       </c>
@@ -24889,6 +25035,7 @@
       <c r="O456">
         <v>136564.6</v>
       </c>
+      <c r="P456"/>
       <c r="Q456">
         <v>2.5</v>
       </c>
@@ -25081,6 +25228,7 @@
       <c r="O460">
         <v>136642.5</v>
       </c>
+      <c r="P460"/>
       <c r="Q460">
         <v>2.5</v>
       </c>
@@ -25123,6 +25271,7 @@
       <c r="O461">
         <v>136668.6</v>
       </c>
+      <c r="P461"/>
       <c r="Q461">
         <v>1.5</v>
       </c>
@@ -25165,6 +25314,7 @@
       <c r="O462">
         <v>136743.70000000001</v>
       </c>
+      <c r="P462"/>
       <c r="Q462">
         <v>1.5</v>
       </c>
@@ -25371,6 +25521,7 @@
       <c r="O467">
         <v>138285.5</v>
       </c>
+      <c r="P467"/>
       <c r="Q467">
         <v>4.5</v>
       </c>
@@ -25463,6 +25614,7 @@
       <c r="O469">
         <v>138365.20000000001</v>
       </c>
+      <c r="P469"/>
       <c r="Q469">
         <v>3.5</v>
       </c>
@@ -25604,6 +25756,7 @@
       <c r="O472">
         <v>138498</v>
       </c>
+      <c r="P472"/>
       <c r="Q472">
         <v>7.5</v>
       </c>
@@ -25646,6 +25799,7 @@
       <c r="O473">
         <v>138554.79999999999</v>
       </c>
+      <c r="P473"/>
       <c r="Q473">
         <v>3.5</v>
       </c>
@@ -25678,6 +25832,7 @@
       <c r="O474">
         <v>138621.5</v>
       </c>
+      <c r="P474"/>
       <c r="Q474">
         <v>2.5</v>
       </c>
@@ -25720,6 +25875,7 @@
       <c r="O475">
         <v>138631.79999999999</v>
       </c>
+      <c r="P475"/>
       <c r="Q475">
         <v>0.5</v>
       </c>
@@ -25762,6 +25918,7 @@
       <c r="O476">
         <v>138652.29999999999</v>
       </c>
+      <c r="P476"/>
       <c r="Q476">
         <v>4.5</v>
       </c>
@@ -25854,6 +26011,7 @@
       <c r="O478">
         <v>138780.5</v>
       </c>
+      <c r="P478"/>
       <c r="Q478">
         <v>3.5</v>
       </c>
@@ -25936,6 +26094,7 @@
       <c r="O480">
         <v>138811.4</v>
       </c>
+      <c r="P480"/>
       <c r="Q480">
         <v>1.5</v>
       </c>
@@ -25978,6 +26137,7 @@
       <c r="O481">
         <v>138967.6</v>
       </c>
+      <c r="P481"/>
       <c r="Q481">
         <v>5.5</v>
       </c>
@@ -26036,7 +26196,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>139</v>
       </c>
@@ -26095,7 +26255,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>139</v>
       </c>
@@ -26132,7 +26292,7 @@
       <c r="O484">
         <v>13355.5</v>
       </c>
-      <c r="P484">
+      <c r="P484" s="4">
         <v>-3.4</v>
       </c>
       <c r="Q484">
@@ -26145,7 +26305,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>139</v>
       </c>
@@ -26195,7 +26355,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>139</v>
       </c>
@@ -26245,7 +26405,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>139</v>
       </c>
@@ -26291,7 +26451,7 @@
       <c r="O487">
         <v>15009.5</v>
       </c>
-      <c r="P487">
+      <c r="P487" s="4">
         <v>-149.54</v>
       </c>
       <c r="Q487">
@@ -26304,7 +26464,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>139</v>
       </c>
@@ -26354,7 +26514,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>139</v>
       </c>
@@ -26391,7 +26551,7 @@
       <c r="O489">
         <v>15508.9</v>
       </c>
-      <c r="P489">
+      <c r="P489" s="4">
         <v>16.600000000000001</v>
       </c>
       <c r="Q489">
@@ -26513,7 +26673,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>139</v>
       </c>
@@ -26545,7 +26705,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>139</v>
       </c>
@@ -26604,7 +26764,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>139</v>
       </c>
@@ -26636,7 +26796,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>139</v>
       </c>
@@ -26686,7 +26846,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>139</v>
       </c>
@@ -26723,7 +26883,7 @@
       <c r="O496">
         <v>18256.7</v>
       </c>
-      <c r="P496">
+      <c r="P496" s="4">
         <v>-15.16</v>
       </c>
       <c r="Q496">
@@ -26736,7 +26896,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>139</v>
       </c>
@@ -26786,7 +26946,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>139</v>
       </c>
@@ -26877,7 +27037,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>139</v>
       </c>
@@ -26914,7 +27074,7 @@
       <c r="O500">
         <v>19272.2</v>
       </c>
-      <c r="P500">
+      <c r="P500" s="4">
         <v>36.729999999999997</v>
       </c>
       <c r="Q500">
@@ -26927,7 +27087,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>139</v>
       </c>
@@ -26977,7 +27137,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>139</v>
       </c>
@@ -27014,7 +27174,7 @@
       <c r="O502">
         <v>19567.2</v>
       </c>
-      <c r="P502">
+      <c r="P502" s="4">
         <v>133.69999999999999</v>
       </c>
       <c r="Q502">
@@ -27027,7 +27187,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>139</v>
       </c>
@@ -27059,7 +27219,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>139</v>
       </c>
@@ -27109,7 +27269,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>139</v>
       </c>
@@ -27159,7 +27319,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>139</v>
       </c>
@@ -27259,7 +27419,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>139</v>
       </c>
@@ -27309,7 +27469,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>139</v>
       </c>
@@ -27359,7 +27519,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>139</v>
       </c>
@@ -27409,7 +27569,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>139</v>
       </c>
@@ -27509,7 +27669,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>139</v>
       </c>
@@ -27559,7 +27719,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>139</v>
       </c>
@@ -27609,7 +27769,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>139</v>
       </c>
@@ -27659,7 +27819,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>139</v>
       </c>
@@ -27696,7 +27856,7 @@
       <c r="O516">
         <v>21678</v>
       </c>
-      <c r="P516">
+      <c r="P516" s="4">
         <v>77.84</v>
       </c>
       <c r="Q516">
@@ -27759,7 +27919,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>139</v>
       </c>
@@ -27809,7 +27969,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>139</v>
       </c>
@@ -27909,7 +28069,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>139</v>
       </c>
@@ -27968,7 +28128,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>139</v>
       </c>
@@ -28018,7 +28178,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>139</v>
       </c>
@@ -28068,7 +28228,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>139</v>
       </c>
@@ -28105,7 +28265,7 @@
       <c r="O524">
         <v>23470.400000000001</v>
       </c>
-      <c r="P524">
+      <c r="P524" s="4">
         <v>-28.15</v>
       </c>
       <c r="Q524">
@@ -28168,7 +28328,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>139</v>
       </c>
@@ -28218,7 +28378,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>139</v>
       </c>
@@ -28268,7 +28428,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>139</v>
       </c>
@@ -28318,7 +28478,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>139</v>
       </c>
@@ -28418,7 +28578,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>139</v>
       </c>
@@ -28468,7 +28628,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>139</v>
       </c>
@@ -28527,7 +28687,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>139</v>
       </c>
@@ -28577,7 +28737,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>139</v>
       </c>
@@ -28627,7 +28787,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>139</v>
       </c>
@@ -28727,7 +28887,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>139</v>
       </c>
@@ -28764,7 +28924,7 @@
       <c r="O537">
         <v>26070.6</v>
       </c>
-      <c r="P537">
+      <c r="P537" s="4">
         <v>24.63</v>
       </c>
       <c r="Q537">
@@ -28777,7 +28937,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>139</v>
       </c>
@@ -28827,7 +28987,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>139</v>
       </c>
@@ -28977,7 +29137,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>139</v>
       </c>
@@ -29027,7 +29187,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>139</v>
       </c>
@@ -29064,7 +29224,7 @@
       <c r="O543">
         <v>27342.799999999999</v>
       </c>
-      <c r="P543">
+      <c r="P543" s="4">
         <v>37.51</v>
       </c>
       <c r="Q543">
@@ -29077,7 +29237,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>139</v>
       </c>
@@ -29168,7 +29328,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>139</v>
       </c>
@@ -29218,7 +29378,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>139</v>
       </c>
@@ -29268,7 +29428,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>139</v>
       </c>
@@ -29318,7 +29478,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>139</v>
       </c>
@@ -29368,7 +29528,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>139</v>
       </c>
@@ -29418,7 +29578,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>139</v>
       </c>
@@ -29468,7 +29628,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>139</v>
       </c>
@@ -29505,7 +29665,7 @@
       <c r="O552">
         <v>30426.1</v>
       </c>
-      <c r="P552">
+      <c r="P552" s="4">
         <v>79.62</v>
       </c>
       <c r="Q552">
@@ -29518,7 +29678,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>139</v>
       </c>
@@ -29555,7 +29715,7 @@
       <c r="O553">
         <v>30759.8</v>
       </c>
-      <c r="P553">
+      <c r="P553" s="4">
         <v>-26.27</v>
       </c>
       <c r="Q553">
@@ -29618,7 +29778,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>139</v>
       </c>
@@ -29659,7 +29819,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>139</v>
       </c>
@@ -29709,7 +29869,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>139</v>
       </c>
@@ -29759,7 +29919,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>139</v>
       </c>
@@ -29791,7 +29951,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>139</v>
       </c>
@@ -29832,7 +29992,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>139</v>
       </c>
@@ -29882,7 +30042,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>139</v>
       </c>
@@ -29910,7 +30070,7 @@
       <c r="O561">
         <v>33558.699999999997</v>
       </c>
-      <c r="P561">
+      <c r="P561" s="4">
         <v>-92.29</v>
       </c>
       <c r="Q561">
@@ -29923,7 +30083,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="562" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>139</v>
       </c>
@@ -29964,7 +30124,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>139</v>
       </c>
@@ -30114,7 +30274,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>139</v>
       </c>
@@ -30164,7 +30324,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>139</v>
       </c>
@@ -30214,7 +30374,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>139</v>
       </c>
@@ -30264,7 +30424,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>139</v>
       </c>
@@ -30364,7 +30524,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>139</v>
       </c>
@@ -30414,7 +30574,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>139</v>
       </c>
@@ -30442,7 +30602,7 @@
       <c r="O572">
         <v>36309.4</v>
       </c>
-      <c r="P572">
+      <c r="P572" s="4">
         <v>361.17</v>
       </c>
       <c r="Q572">
@@ -30455,7 +30615,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>139</v>
       </c>
@@ -30505,7 +30665,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="574" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>139</v>
       </c>
@@ -30555,7 +30715,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>139</v>
       </c>
@@ -30655,7 +30815,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>139</v>
       </c>
@@ -30714,7 +30874,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>139</v>
       </c>
@@ -30814,7 +30974,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="580" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>139</v>
       </c>
@@ -30864,7 +31024,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>139</v>
       </c>
@@ -30914,7 +31074,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>139</v>
       </c>
@@ -31005,7 +31165,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>139</v>
       </c>
@@ -31055,7 +31215,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>139</v>
       </c>
@@ -31105,7 +31265,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>139</v>
       </c>
@@ -31155,7 +31315,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>139</v>
       </c>
@@ -31205,7 +31365,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="588" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>139</v>
       </c>
@@ -31255,7 +31415,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>139</v>
       </c>
@@ -31305,7 +31465,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>139</v>
       </c>
@@ -31342,7 +31502,7 @@
       <c r="O590">
         <v>39939.5</v>
       </c>
-      <c r="P590">
+      <c r="P590" s="4">
         <v>-206.51</v>
       </c>
       <c r="Q590">
@@ -31355,7 +31515,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>139</v>
       </c>
@@ -31405,7 +31565,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>139</v>
       </c>
@@ -31455,7 +31615,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>139</v>
       </c>
@@ -31505,7 +31665,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>139</v>
       </c>
@@ -31628,7 +31788,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>139</v>
       </c>
@@ -31678,7 +31838,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>139</v>
       </c>
@@ -31719,7 +31879,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>139</v>
       </c>
@@ -31769,7 +31929,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>139</v>
       </c>
@@ -31851,7 +32011,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>139</v>
       </c>
@@ -31901,7 +32061,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>139</v>
       </c>
@@ -31951,7 +32111,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="604" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>139</v>
       </c>
@@ -31976,6 +32136,7 @@
       <c r="O604">
         <v>49610.2</v>
       </c>
+      <c r="P604"/>
       <c r="Q604">
         <v>0.5</v>
       </c>
@@ -31986,7 +32147,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>139</v>
       </c>
@@ -32027,7 +32188,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>139</v>
       </c>
@@ -32046,7 +32207,7 @@
       <c r="O606">
         <v>50666.8</v>
       </c>
-      <c r="P606">
+      <c r="P606" s="4">
         <v>-19.45</v>
       </c>
       <c r="Q606">
@@ -32059,7 +32220,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>139</v>
       </c>
@@ -32091,7 +32252,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="608" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>139</v>
       </c>
@@ -32132,7 +32293,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>139</v>
       </c>
@@ -32173,7 +32334,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>139</v>
       </c>
@@ -32223,7 +32384,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>139</v>
       </c>
@@ -32257,6 +32418,7 @@
       <c r="O611">
         <v>67211.8</v>
       </c>
+      <c r="P611"/>
       <c r="Q611">
         <v>1.5</v>
       </c>
@@ -32265,7 +32427,7 @@
       </c>
       <c r="S611"/>
     </row>
-    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>139</v>
       </c>
@@ -32281,6 +32443,7 @@
       <c r="O612">
         <v>68729.5</v>
       </c>
+      <c r="P612"/>
       <c r="Q612">
         <v>2.5</v>
       </c>
@@ -32289,7 +32452,7 @@
       </c>
       <c r="S612"/>
     </row>
-    <row r="613" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>139</v>
       </c>
@@ -32305,6 +32468,7 @@
       <c r="O613">
         <v>79157.399999999994</v>
       </c>
+      <c r="P613"/>
       <c r="Q613">
         <v>0.5</v>
       </c>
@@ -32354,7 +32518,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>139</v>
       </c>
@@ -32395,7 +32559,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>139</v>
       </c>
@@ -32486,7 +32650,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>139</v>
       </c>
@@ -32514,7 +32678,7 @@
       <c r="O618">
         <v>100777.60000000001</v>
       </c>
-      <c r="P618">
+      <c r="P618" s="4">
         <v>-152.56</v>
       </c>
       <c r="Q618">
@@ -32527,7 +32691,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>139</v>
       </c>
@@ -32568,7 +32732,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>139</v>
       </c>
@@ -32618,7 +32782,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>139</v>
       </c>
@@ -32646,7 +32810,7 @@
       <c r="O621">
         <v>101135.4</v>
       </c>
-      <c r="P621">
+      <c r="P621" s="4">
         <v>29.93</v>
       </c>
       <c r="Q621">
@@ -32709,7 +32873,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>139</v>
       </c>
@@ -32759,7 +32923,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="624" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>139</v>
       </c>
@@ -32800,7 +32964,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="625" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>139</v>
       </c>
@@ -32850,7 +33014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="626" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>139</v>
       </c>
@@ -32869,7 +33033,7 @@
       <c r="O626">
         <v>102363.2</v>
       </c>
-      <c r="P626">
+      <c r="P626" s="4">
         <v>72.47</v>
       </c>
       <c r="Q626">
@@ -32882,7 +33046,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="627" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>139</v>
       </c>
@@ -32914,7 +33078,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="628" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>139</v>
       </c>
@@ -32942,7 +33106,7 @@
       <c r="O628">
         <v>102666.2</v>
       </c>
-      <c r="P628">
+      <c r="P628" s="4">
         <v>-48.96</v>
       </c>
       <c r="Q628">
@@ -32955,7 +33119,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="629" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>139</v>
       </c>
@@ -32996,7 +33160,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="630" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>139</v>
       </c>
@@ -33037,7 +33201,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="631" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>139</v>
       </c>
@@ -33078,7 +33242,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>139</v>
       </c>
@@ -33106,7 +33270,7 @@
       <c r="O632">
         <v>103269.7</v>
       </c>
-      <c r="P632">
+      <c r="P632" s="4">
         <v>74.650000000000006</v>
       </c>
       <c r="Q632">
@@ -33160,7 +33324,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>139</v>
       </c>
@@ -33251,7 +33415,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>139</v>
       </c>
@@ -33301,7 +33465,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>139</v>
       </c>
@@ -33333,7 +33497,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="638" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>139</v>
       </c>
@@ -33365,7 +33529,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>139</v>
       </c>
@@ -33384,7 +33548,7 @@
       <c r="O639">
         <v>104756.5</v>
       </c>
-      <c r="P639">
+      <c r="P639" s="4">
         <v>32.18</v>
       </c>
       <c r="Q639">
@@ -33397,7 +33561,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>139</v>
       </c>
@@ -33425,7 +33589,7 @@
       <c r="O640">
         <v>104921.3</v>
       </c>
-      <c r="P640">
+      <c r="P640" s="4">
         <v>-16.75</v>
       </c>
       <c r="Q640">
@@ -33438,7 +33602,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="641" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>139</v>
       </c>
@@ -33479,7 +33643,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="642" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>139</v>
       </c>
@@ -33520,7 +33684,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>139</v>
       </c>
@@ -33561,7 +33725,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>139</v>
       </c>
@@ -33602,7 +33766,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>139</v>
       </c>
@@ -33639,7 +33803,7 @@
       <c r="O645">
         <v>105397.3</v>
       </c>
-      <c r="P645">
+      <c r="P645" s="4">
         <v>52.88</v>
       </c>
       <c r="Q645">
@@ -33652,7 +33816,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="646" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>139</v>
       </c>
@@ -33693,7 +33857,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="647" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>139</v>
       </c>
@@ -33734,7 +33898,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>139</v>
       </c>
@@ -33816,7 +33980,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="650" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>139</v>
       </c>
@@ -33850,6 +34014,7 @@
       <c r="O650">
         <v>105664.6</v>
       </c>
+      <c r="P650"/>
       <c r="Q650">
         <v>0.5</v>
       </c>
@@ -33858,7 +34023,7 @@
       </c>
       <c r="S650"/>
     </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>139</v>
       </c>
@@ -33892,6 +34057,7 @@
       <c r="O651">
         <v>105790.1</v>
       </c>
+      <c r="P651"/>
       <c r="Q651">
         <v>2.5</v>
       </c>
@@ -33900,7 +34066,7 @@
       </c>
       <c r="S651"/>
     </row>
-    <row r="652" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>139</v>
       </c>
@@ -33934,6 +34100,7 @@
       <c r="O652">
         <v>105979.2</v>
       </c>
+      <c r="P652"/>
       <c r="Q652">
         <v>0.5</v>
       </c>
@@ -33942,7 +34109,7 @@
       </c>
       <c r="S652"/>
     </row>
-    <row r="653" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>139</v>
       </c>
@@ -33976,6 +34143,7 @@
       <c r="O653">
         <v>105993.3</v>
       </c>
+      <c r="P653"/>
       <c r="Q653">
         <v>1.5</v>
       </c>
@@ -33984,7 +34152,7 @@
       </c>
       <c r="S653"/>
     </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>139</v>
       </c>
@@ -34034,7 +34202,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="655" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>139</v>
       </c>
@@ -34068,6 +34236,7 @@
       <c r="O655">
         <v>106175</v>
       </c>
+      <c r="P655"/>
       <c r="Q655">
         <v>1.5</v>
       </c>
@@ -34126,7 +34295,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="657" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>139</v>
       </c>
@@ -34176,7 +34345,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="658" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>139</v>
       </c>
@@ -34226,7 +34395,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="659" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>139</v>
       </c>
@@ -34367,7 +34536,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="662" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>139</v>
       </c>
@@ -34399,7 +34568,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="663" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>139</v>
       </c>
@@ -34424,6 +34593,7 @@
       <c r="O663">
         <v>107103.6</v>
       </c>
+      <c r="P663"/>
       <c r="Q663">
         <v>1.5</v>
       </c>
@@ -34432,7 +34602,7 @@
       </c>
       <c r="S663"/>
     </row>
-    <row r="664" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>139</v>
       </c>
@@ -34473,7 +34643,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="665" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>139</v>
       </c>
@@ -34523,7 +34693,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="666" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>139</v>
       </c>
@@ -34673,7 +34843,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="669" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>139</v>
       </c>
@@ -34710,7 +34880,7 @@
       <c r="O669">
         <v>107472.3</v>
       </c>
-      <c r="P669">
+      <c r="P669" s="4">
         <v>-68.39</v>
       </c>
       <c r="Q669">
@@ -34723,7 +34893,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="670" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>139</v>
       </c>
@@ -34739,6 +34909,7 @@
       <c r="O670">
         <v>107529.8</v>
       </c>
+      <c r="P670"/>
       <c r="Q670">
         <v>0.5</v>
       </c>
@@ -34747,7 +34918,7 @@
       </c>
       <c r="S670"/>
     </row>
-    <row r="671" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>139</v>
       </c>
@@ -34781,6 +34952,7 @@
       <c r="O671">
         <v>107614.5</v>
       </c>
+      <c r="P671"/>
       <c r="Q671">
         <v>2.5</v>
       </c>
@@ -34789,7 +34961,7 @@
       </c>
       <c r="S671"/>
     </row>
-    <row r="672" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>139</v>
       </c>
@@ -34823,6 +34995,7 @@
       <c r="O672">
         <v>107689.9</v>
       </c>
+      <c r="P672"/>
       <c r="Q672">
         <v>1.5</v>
       </c>
@@ -34831,7 +35004,7 @@
       </c>
       <c r="S672"/>
     </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>139</v>
       </c>
@@ -34865,6 +35038,7 @@
       <c r="O673">
         <v>107743.5</v>
       </c>
+      <c r="P673"/>
       <c r="Q673">
         <v>2.5</v>
       </c>
@@ -34873,7 +35047,7 @@
       </c>
       <c r="S673"/>
     </row>
-    <row r="674" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>139</v>
       </c>
@@ -34910,7 +35084,7 @@
       <c r="O674">
         <v>107757.5</v>
       </c>
-      <c r="P674">
+      <c r="P674" s="4">
         <v>-60.43</v>
       </c>
       <c r="Q674">
@@ -34923,7 +35097,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="675" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>139</v>
       </c>
@@ -34957,6 +35131,7 @@
       <c r="O675">
         <v>107804.9</v>
       </c>
+      <c r="P675"/>
       <c r="Q675">
         <v>4.5</v>
       </c>
@@ -34999,6 +35174,7 @@
       <c r="O676">
         <v>107816.8</v>
       </c>
+      <c r="P676"/>
       <c r="Q676">
         <v>3.5</v>
       </c>
@@ -35007,7 +35183,7 @@
       </c>
       <c r="S676"/>
     </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>139</v>
       </c>
@@ -35057,7 +35233,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="678" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>139</v>
       </c>
@@ -35132,6 +35308,7 @@
       <c r="O679">
         <v>108099.1</v>
       </c>
+      <c r="P679"/>
       <c r="Q679">
         <v>3.5</v>
       </c>
@@ -35142,7 +35319,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="680" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>139</v>
       </c>
@@ -35176,6 +35353,7 @@
       <c r="O680">
         <v>108125.7</v>
       </c>
+      <c r="P680"/>
       <c r="Q680">
         <v>1.5</v>
       </c>
@@ -35218,6 +35396,7 @@
       <c r="O681">
         <v>108201.7</v>
       </c>
+      <c r="P681"/>
       <c r="Q681">
         <v>3.5</v>
       </c>
@@ -35226,7 +35405,7 @@
       </c>
       <c r="S681"/>
     </row>
-    <row r="682" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>139</v>
       </c>
@@ -35260,6 +35439,7 @@
       <c r="O682">
         <v>108488.4</v>
       </c>
+      <c r="P682"/>
       <c r="Q682">
         <v>2.5</v>
       </c>
@@ -35268,7 +35448,7 @@
       </c>
       <c r="S682"/>
     </row>
-    <row r="683" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>139</v>
       </c>
@@ -35318,7 +35498,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>139</v>
       </c>
@@ -35355,7 +35535,7 @@
       <c r="O684">
         <v>108568.2</v>
       </c>
-      <c r="P684">
+      <c r="P684" s="4">
         <v>-8.8000000000000007</v>
       </c>
       <c r="Q684">
@@ -35368,7 +35548,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="685" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>139</v>
       </c>
@@ -35393,6 +35573,7 @@
       <c r="O685">
         <v>110201.1</v>
       </c>
+      <c r="P685"/>
       <c r="Q685">
         <v>4.5</v>
       </c>
@@ -35426,6 +35607,7 @@
       <c r="O686">
         <v>110276.6</v>
       </c>
+      <c r="P686"/>
       <c r="Q686">
         <v>3.5</v>
       </c>
@@ -35459,6 +35641,7 @@
       <c r="O687">
         <v>110670.39999999999</v>
       </c>
+      <c r="P687"/>
       <c r="Q687">
         <v>3.5</v>
       </c>
@@ -35467,7 +35650,7 @@
       </c>
       <c r="S687"/>
     </row>
-    <row r="688" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>139</v>
       </c>
@@ -35501,6 +35684,7 @@
       <c r="O688">
         <v>110697.60000000001</v>
       </c>
+      <c r="P688"/>
       <c r="Q688">
         <v>2.5</v>
       </c>
@@ -35509,7 +35693,7 @@
       </c>
       <c r="S688"/>
     </row>
-    <row r="689" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>139</v>
       </c>
@@ -35543,6 +35727,7 @@
       <c r="O689">
         <v>110828</v>
       </c>
+      <c r="P689"/>
       <c r="Q689">
         <v>4.5</v>
       </c>
@@ -35551,7 +35736,7 @@
       </c>
       <c r="S689"/>
     </row>
-    <row r="690" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>139</v>
       </c>
@@ -35579,7 +35764,7 @@
       <c r="O690">
         <v>110903.8</v>
       </c>
-      <c r="P690">
+      <c r="P690" s="4">
         <v>135.94999999999999</v>
       </c>
       <c r="Q690">
@@ -35592,7 +35777,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="691" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>139</v>
       </c>
@@ -35636,7 +35821,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="692" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>139</v>
       </c>
@@ -35661,6 +35846,7 @@
       <c r="O692">
         <v>111175.1</v>
       </c>
+      <c r="P692"/>
       <c r="Q692">
         <v>2.5</v>
       </c>
@@ -35669,7 +35855,7 @@
       </c>
       <c r="S692"/>
     </row>
-    <row r="693" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>139</v>
       </c>
@@ -35719,7 +35905,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="694" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>139</v>
       </c>
@@ -35744,6 +35930,7 @@
       <c r="O694">
         <v>111182.3</v>
       </c>
+      <c r="P694"/>
       <c r="Q694">
         <v>1.5</v>
       </c>
@@ -35752,7 +35939,7 @@
       </c>
       <c r="S694"/>
     </row>
-    <row r="695" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>139</v>
       </c>
@@ -35786,6 +35973,7 @@
       <c r="O695">
         <v>111244.7</v>
       </c>
+      <c r="P695"/>
       <c r="Q695">
         <v>4.5</v>
       </c>
@@ -35819,6 +36007,7 @@
       <c r="O696">
         <v>111465.9</v>
       </c>
+      <c r="P696"/>
       <c r="Q696">
         <v>3.5</v>
       </c>
@@ -35827,7 +36016,7 @@
       </c>
       <c r="S696"/>
     </row>
-    <row r="697" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>139</v>
       </c>
@@ -35886,7 +36075,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="698" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>139</v>
       </c>
@@ -35920,6 +36109,7 @@
       <c r="O698">
         <v>115278.9</v>
       </c>
+      <c r="P698"/>
       <c r="Q698">
         <v>2.5</v>
       </c>
@@ -35987,7 +36177,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="700" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>139</v>
       </c>
@@ -36021,6 +36211,7 @@
       <c r="O700">
         <v>115992.5</v>
       </c>
+      <c r="P700"/>
       <c r="Q700">
         <v>1.5</v>
       </c>
@@ -36063,6 +36254,7 @@
       <c r="O701">
         <v>116763.1</v>
       </c>
+      <c r="P701"/>
       <c r="Q701">
         <v>3.5</v>
       </c>
@@ -36071,7 +36263,7 @@
       </c>
       <c r="S701"/>
     </row>
-    <row r="702" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>139</v>
       </c>
@@ -36105,6 +36297,7 @@
       <c r="O702">
         <v>117255.6</v>
       </c>
+      <c r="P702"/>
       <c r="Q702">
         <v>4.5</v>
       </c>
@@ -36147,6 +36340,7 @@
       <c r="O703">
         <v>117465.5</v>
       </c>
+      <c r="P703"/>
       <c r="Q703">
         <v>3.5</v>
       </c>
@@ -36189,6 +36383,7 @@
       <c r="O704">
         <v>117700</v>
       </c>
+      <c r="P704"/>
       <c r="Q704">
         <v>3.5</v>
       </c>
@@ -36197,7 +36392,7 @@
       </c>
       <c r="S704"/>
     </row>
-    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>139</v>
       </c>
@@ -36231,6 +36426,7 @@
       <c r="O705">
         <v>117908.7</v>
       </c>
+      <c r="P705"/>
       <c r="Q705">
         <v>2.5</v>
       </c>
@@ -36239,7 +36435,7 @@
       </c>
       <c r="S705"/>
     </row>
-    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>139</v>
       </c>
@@ -36290,7 +36486,7 @@
       </c>
       <c r="S706"/>
     </row>
-    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>139</v>
       </c>
@@ -36324,6 +36520,7 @@
       <c r="O707">
         <v>118051.5</v>
       </c>
+      <c r="P707"/>
       <c r="Q707">
         <v>4.5</v>
       </c>
@@ -36332,7 +36529,7 @@
       </c>
       <c r="S707"/>
     </row>
-    <row r="708" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>139</v>
       </c>
@@ -36366,6 +36563,7 @@
       <c r="O708">
         <v>118105.4</v>
       </c>
+      <c r="P708"/>
       <c r="Q708">
         <v>0.5</v>
       </c>
@@ -36374,7 +36572,7 @@
       </c>
       <c r="S708"/>
     </row>
-    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>139</v>
       </c>
@@ -36408,6 +36606,7 @@
       <c r="O709">
         <v>118208.1</v>
       </c>
+      <c r="P709"/>
       <c r="Q709">
         <v>1.5</v>
       </c>
@@ -36416,7 +36615,7 @@
       </c>
       <c r="S709"/>
     </row>
-    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>139</v>
       </c>
@@ -36450,6 +36649,7 @@
       <c r="O710">
         <v>118248.1</v>
       </c>
+      <c r="P710"/>
       <c r="Q710">
         <v>2.5</v>
       </c>
@@ -36458,7 +36658,7 @@
       </c>
       <c r="S710"/>
     </row>
-    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>139</v>
       </c>
@@ -36492,6 +36692,7 @@
       <c r="O711">
         <v>118358.6</v>
       </c>
+      <c r="P711"/>
       <c r="Q711">
         <v>1.5</v>
       </c>
@@ -36500,7 +36701,7 @@
       </c>
       <c r="S711"/>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>139</v>
       </c>
@@ -36534,6 +36735,7 @@
       <c r="O712">
         <v>118448.3</v>
       </c>
+      <c r="P712"/>
       <c r="Q712">
         <v>2.5</v>
       </c>
@@ -36542,7 +36744,7 @@
       </c>
       <c r="S712"/>
     </row>
-    <row r="713" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>139</v>
       </c>
@@ -36576,6 +36778,7 @@
       <c r="O713">
         <v>118485.4</v>
       </c>
+      <c r="P713"/>
       <c r="Q713">
         <v>0.5</v>
       </c>
@@ -36618,6 +36821,7 @@
       <c r="O714">
         <v>118600.8</v>
       </c>
+      <c r="P714"/>
       <c r="Q714">
         <v>3.5</v>
       </c>
@@ -36628,7 +36832,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>139</v>
       </c>
@@ -36662,6 +36866,7 @@
       <c r="O715">
         <v>118667.9</v>
       </c>
+      <c r="P715"/>
       <c r="Q715">
         <v>2.5</v>
       </c>
@@ -36704,6 +36909,7 @@
       <c r="O716">
         <v>118727.8</v>
       </c>
+      <c r="P716"/>
       <c r="Q716">
         <v>3.5</v>
       </c>
@@ -36712,7 +36918,7 @@
       </c>
       <c r="S716"/>
     </row>
-    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>139</v>
       </c>
@@ -36746,6 +36952,7 @@
       <c r="O717">
         <v>118792.5</v>
       </c>
+      <c r="P717"/>
       <c r="Q717">
         <v>1.5</v>
       </c>
@@ -36754,7 +36961,7 @@
       </c>
       <c r="S717"/>
     </row>
-    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>139</v>
       </c>
@@ -36804,7 +37011,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>139</v>
       </c>
@@ -36838,6 +37045,7 @@
       <c r="O719">
         <v>119027.7</v>
       </c>
+      <c r="P719"/>
       <c r="Q719">
         <v>4.5</v>
       </c>
@@ -36846,7 +37054,7 @@
       </c>
       <c r="S719"/>
     </row>
-    <row r="720" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>139</v>
       </c>
@@ -36880,6 +37088,7 @@
       <c r="O720">
         <v>119170.8</v>
       </c>
+      <c r="P720"/>
       <c r="Q720">
         <v>0.5</v>
       </c>
@@ -36888,7 +37097,7 @@
       </c>
       <c r="S720"/>
     </row>
-    <row r="721" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>139</v>
       </c>
@@ -36922,14 +37131,16 @@
       <c r="O721">
         <v>119178.9</v>
       </c>
+      <c r="P721"/>
       <c r="Q721">
         <v>1.5</v>
       </c>
       <c r="R721">
         <v>0.88600000000000001</v>
       </c>
-    </row>
-    <row r="722" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S721"/>
+    </row>
+    <row r="722" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>139</v>
       </c>
@@ -36963,14 +37174,16 @@
       <c r="O722">
         <v>119260.6</v>
       </c>
+      <c r="P722"/>
       <c r="Q722">
         <v>2.5</v>
       </c>
       <c r="R722">
         <v>1.175</v>
       </c>
-    </row>
-    <row r="723" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S722"/>
+    </row>
+    <row r="723" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>139</v>
       </c>
@@ -37010,8 +37223,9 @@
       <c r="R723">
         <v>1.115</v>
       </c>
-    </row>
-    <row r="724" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S723"/>
+    </row>
+    <row r="724" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>139</v>
       </c>
@@ -37045,14 +37259,16 @@
       <c r="O724">
         <v>119378.4</v>
       </c>
+      <c r="P724"/>
       <c r="Q724">
         <v>2.5</v>
       </c>
       <c r="R724">
         <v>0.88200000000000001</v>
       </c>
-    </row>
-    <row r="725" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S724"/>
+    </row>
+    <row r="725" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>139</v>
       </c>
@@ -37086,14 +37302,16 @@
       <c r="O725">
         <v>119407.2</v>
       </c>
+      <c r="P725"/>
       <c r="Q725">
         <v>3.5</v>
       </c>
       <c r="R725">
         <v>1.119</v>
       </c>
-    </row>
-    <row r="726" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S725"/>
+    </row>
+    <row r="726" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>139</v>
       </c>
@@ -37136,14 +37354,16 @@
       <c r="O726">
         <v>119593.4</v>
       </c>
+      <c r="P726"/>
       <c r="Q726">
         <v>4.5</v>
       </c>
       <c r="R726">
         <v>0.997</v>
       </c>
-    </row>
-    <row r="727" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S726"/>
+    </row>
+    <row r="727" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>139</v>
       </c>
@@ -37177,14 +37397,16 @@
       <c r="O727">
         <v>119851.8</v>
       </c>
+      <c r="P727"/>
       <c r="Q727">
         <v>4.5</v>
       </c>
       <c r="R727">
         <v>1.079</v>
       </c>
-    </row>
-    <row r="728" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S727"/>
+    </row>
+    <row r="728" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>139</v>
       </c>
@@ -37218,14 +37440,16 @@
       <c r="O728">
         <v>119878.1</v>
       </c>
+      <c r="P728"/>
       <c r="Q728">
         <v>2.5</v>
       </c>
       <c r="R728">
         <v>1.1399999999999999</v>
       </c>
-    </row>
-    <row r="729" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S728"/>
+    </row>
+    <row r="729" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>139</v>
       </c>
@@ -37256,8 +37480,15 @@
       <c r="M729" t="s">
         <v>157</v>
       </c>
-      <c r="O729">
+      <c r="N729" s="3">
+        <v>119498.5791</v>
+      </c>
+      <c r="O729" s="3">
         <v>120144.6</v>
+      </c>
+      <c r="P729" s="5">
+        <f>N729-O729</f>
+        <v>-646.02090000000317</v>
       </c>
       <c r="Q729">
         <v>3.5</v>
@@ -37265,8 +37496,11 @@
       <c r="R729">
         <v>1.1499999999999999</v>
       </c>
-    </row>
-    <row r="730" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S729" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="730" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>139</v>
       </c>
@@ -37300,14 +37534,16 @@
       <c r="O730">
         <v>120221</v>
       </c>
+      <c r="P730"/>
       <c r="Q730">
         <v>1.5</v>
       </c>
       <c r="R730">
         <v>0.83799999999999997</v>
       </c>
-    </row>
-    <row r="731" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S730"/>
+    </row>
+    <row r="731" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>139</v>
       </c>
@@ -37338,8 +37574,15 @@
       <c r="M731" t="s">
         <v>141</v>
       </c>
-      <c r="O731">
+      <c r="N731" s="3">
+        <v>120805.16959999999</v>
+      </c>
+      <c r="O731" s="3">
         <v>120416.4</v>
+      </c>
+      <c r="P731" s="5">
+        <f>N731-O731</f>
+        <v>388.76959999999963</v>
       </c>
       <c r="Q731">
         <v>5.5</v>
@@ -37347,8 +37590,11 @@
       <c r="R731">
         <v>1.022</v>
       </c>
-    </row>
-    <row r="732" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S731" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="732" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>139</v>
       </c>
@@ -37382,14 +37628,16 @@
       <c r="O732">
         <v>120572.1</v>
       </c>
+      <c r="P732"/>
       <c r="Q732">
         <v>4.5</v>
       </c>
       <c r="R732">
         <v>1.0660000000000001</v>
       </c>
-    </row>
-    <row r="733" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S732"/>
+    </row>
+    <row r="733" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>139</v>
       </c>
@@ -37423,14 +37671,16 @@
       <c r="O733">
         <v>120611</v>
       </c>
+      <c r="P733"/>
       <c r="Q733">
         <v>0.5</v>
       </c>
       <c r="R733">
         <v>0.53</v>
       </c>
-    </row>
-    <row r="734" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S733"/>
+    </row>
+    <row r="734" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>139</v>
       </c>
@@ -37464,14 +37714,16 @@
       <c r="O734">
         <v>120741.6</v>
       </c>
+      <c r="P734"/>
       <c r="Q734">
         <v>3.5</v>
       </c>
       <c r="R734">
         <v>1.133</v>
       </c>
-    </row>
-    <row r="735" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S734"/>
+    </row>
+    <row r="735" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>139</v>
       </c>
@@ -37505,14 +37757,16 @@
       <c r="O735">
         <v>120802.1</v>
       </c>
+      <c r="P735"/>
       <c r="Q735">
         <v>3.5</v>
       </c>
       <c r="R735">
         <v>0.92400000000000004</v>
       </c>
-    </row>
-    <row r="736" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S735"/>
+    </row>
+    <row r="736" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>139</v>
       </c>
@@ -37546,14 +37800,16 @@
       <c r="O736">
         <v>120808.7</v>
       </c>
+      <c r="P736"/>
       <c r="Q736">
         <v>1.5</v>
       </c>
       <c r="R736">
         <v>0.746</v>
       </c>
-    </row>
-    <row r="737" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S736"/>
+    </row>
+    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>139</v>
       </c>
@@ -37590,7 +37846,7 @@
       <c r="O737">
         <v>120998.7</v>
       </c>
-      <c r="P737">
+      <c r="P737" s="4">
         <v>144.6</v>
       </c>
       <c r="Q737">
@@ -37637,6 +37893,7 @@
       <c r="O738">
         <v>121073.4</v>
       </c>
+      <c r="P738"/>
       <c r="Q738">
         <v>3.5</v>
       </c>
@@ -37645,7 +37902,7 @@
       </c>
       <c r="S738"/>
     </row>
-    <row r="739" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>139</v>
       </c>
@@ -37679,6 +37936,7 @@
       <c r="O739">
         <v>121155.7</v>
       </c>
+      <c r="P739"/>
       <c r="Q739">
         <v>2.5</v>
       </c>
@@ -37687,7 +37945,7 @@
       </c>
       <c r="S739"/>
     </row>
-    <row r="740" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>139</v>
       </c>
@@ -37721,6 +37979,7 @@
       <c r="O740">
         <v>121458.2</v>
       </c>
+      <c r="P740"/>
       <c r="Q740">
         <v>1.5</v>
       </c>
@@ -37729,7 +37988,7 @@
       </c>
       <c r="S740"/>
     </row>
-    <row r="741" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>139</v>
       </c>
@@ -37763,6 +38022,7 @@
       <c r="O741">
         <v>121478.2</v>
       </c>
+      <c r="P741"/>
       <c r="Q741">
         <v>4.5</v>
       </c>
@@ -37771,7 +38031,7 @@
       </c>
       <c r="S741"/>
     </row>
-    <row r="742" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>139</v>
       </c>
@@ -37796,6 +38056,7 @@
       <c r="O742">
         <v>121582.6</v>
       </c>
+      <c r="P742"/>
       <c r="Q742">
         <v>6.5</v>
       </c>
@@ -37804,7 +38065,7 @@
       </c>
       <c r="S742"/>
     </row>
-    <row r="743" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>139</v>
       </c>
@@ -37838,6 +38099,7 @@
       <c r="O743">
         <v>121676.6</v>
       </c>
+      <c r="P743"/>
       <c r="Q743">
         <v>2.5</v>
       </c>
@@ -37846,7 +38108,7 @@
       </c>
       <c r="S743"/>
     </row>
-    <row r="744" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>139</v>
       </c>
@@ -37880,6 +38142,7 @@
       <c r="O744">
         <v>121861.1</v>
       </c>
+      <c r="P744"/>
       <c r="Q744">
         <v>2.5</v>
       </c>
@@ -37922,6 +38185,7 @@
       <c r="O745">
         <v>121889.2</v>
       </c>
+      <c r="P745"/>
       <c r="Q745">
         <v>3.5</v>
       </c>
@@ -37930,7 +38194,7 @@
       </c>
       <c r="S745"/>
     </row>
-    <row r="746" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>139</v>
       </c>
@@ -37964,6 +38228,7 @@
       <c r="O746">
         <v>122017.8</v>
       </c>
+      <c r="P746"/>
       <c r="Q746">
         <v>1.5</v>
       </c>
@@ -37972,7 +38237,7 @@
       </c>
       <c r="S746"/>
     </row>
-    <row r="747" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>139</v>
       </c>
@@ -38006,6 +38271,7 @@
       <c r="O747">
         <v>122337.9</v>
       </c>
+      <c r="P747"/>
       <c r="Q747">
         <v>4.5</v>
       </c>
@@ -38014,7 +38280,7 @@
       </c>
       <c r="S747"/>
     </row>
-    <row r="748" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>139</v>
       </c>
@@ -38048,6 +38314,7 @@
       <c r="O748">
         <v>122401.3</v>
       </c>
+      <c r="P748"/>
       <c r="Q748">
         <v>0.5</v>
       </c>
@@ -38056,7 +38323,7 @@
       </c>
       <c r="S748"/>
     </row>
-    <row r="749" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>139</v>
       </c>
@@ -38106,7 +38373,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="750" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>139</v>
       </c>
@@ -38148,7 +38415,7 @@
       </c>
       <c r="S750"/>
     </row>
-    <row r="751" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>139</v>
       </c>
@@ -38182,6 +38449,7 @@
       <c r="O751">
         <v>122553.9</v>
       </c>
+      <c r="P751"/>
       <c r="Q751">
         <v>4.5</v>
       </c>
@@ -38190,7 +38458,7 @@
       </c>
       <c r="S751"/>
     </row>
-    <row r="752" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>139</v>
       </c>
@@ -38232,7 +38500,7 @@
       </c>
       <c r="S752"/>
     </row>
-    <row r="753" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>139</v>
       </c>
@@ -38266,6 +38534,7 @@
       <c r="O753">
         <v>122612</v>
       </c>
+      <c r="P753"/>
       <c r="Q753">
         <v>0.5</v>
       </c>
@@ -38274,7 +38543,7 @@
       </c>
       <c r="S753"/>
     </row>
-    <row r="754" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>139</v>
       </c>
@@ -38308,6 +38577,7 @@
       <c r="O754">
         <v>122620.1</v>
       </c>
+      <c r="P754"/>
       <c r="Q754">
         <v>1.5</v>
       </c>
@@ -38316,7 +38586,7 @@
       </c>
       <c r="S754"/>
     </row>
-    <row r="755" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>139</v>
       </c>
@@ -38350,6 +38620,7 @@
       <c r="O755">
         <v>122636.7</v>
       </c>
+      <c r="P755"/>
       <c r="Q755">
         <v>6.5</v>
       </c>
@@ -38392,6 +38663,7 @@
       <c r="O756">
         <v>122648.9</v>
       </c>
+      <c r="P756"/>
       <c r="Q756">
         <v>3.5</v>
       </c>
@@ -38400,7 +38672,7 @@
       </c>
       <c r="S756"/>
     </row>
-    <row r="757" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>139</v>
       </c>
@@ -38434,6 +38706,7 @@
       <c r="O757">
         <v>122676.4</v>
       </c>
+      <c r="P757"/>
       <c r="Q757">
         <v>2.5</v>
       </c>
@@ -38442,7 +38715,7 @@
       </c>
       <c r="S757"/>
     </row>
-    <row r="758" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>139</v>
       </c>
@@ -38486,7 +38759,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="759" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>139</v>
       </c>
@@ -38520,6 +38793,7 @@
       <c r="O759">
         <v>122845.6</v>
       </c>
+      <c r="P759"/>
       <c r="Q759">
         <v>6.5</v>
       </c>
@@ -38528,7 +38802,7 @@
       </c>
       <c r="S759"/>
     </row>
-    <row r="760" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>139</v>
       </c>
@@ -38562,6 +38836,7 @@
       <c r="O760">
         <v>122869.2</v>
       </c>
+      <c r="P760"/>
       <c r="Q760">
         <v>2.5</v>
       </c>
@@ -38570,7 +38845,7 @@
       </c>
       <c r="S760"/>
     </row>
-    <row r="761" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>139</v>
       </c>
@@ -38604,6 +38879,7 @@
       <c r="O761">
         <v>122955</v>
       </c>
+      <c r="P761"/>
       <c r="Q761">
         <v>1.5</v>
       </c>
@@ -38612,7 +38888,7 @@
       </c>
       <c r="S761"/>
     </row>
-    <row r="762" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>139</v>
       </c>
@@ -38654,7 +38930,7 @@
       </c>
       <c r="S762"/>
     </row>
-    <row r="763" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>139</v>
       </c>
@@ -38688,6 +38964,7 @@
       <c r="O763">
         <v>123020.6</v>
       </c>
+      <c r="P763"/>
       <c r="Q763">
         <v>2.5</v>
       </c>
@@ -38696,7 +38973,7 @@
       </c>
       <c r="S763"/>
     </row>
-    <row r="764" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>139</v>
       </c>
@@ -38730,6 +39007,7 @@
       <c r="O764">
         <v>123031</v>
       </c>
+      <c r="P764"/>
       <c r="Q764">
         <v>1.5</v>
       </c>
@@ -38738,7 +39016,7 @@
       </c>
       <c r="S764"/>
     </row>
-    <row r="765" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>139</v>
       </c>
@@ -38772,6 +39050,7 @@
       <c r="O765">
         <v>123073.4</v>
       </c>
+      <c r="P765"/>
       <c r="Q765">
         <v>4.5</v>
       </c>
@@ -38814,6 +39093,7 @@
       <c r="O766">
         <v>123176.2</v>
       </c>
+      <c r="P766"/>
       <c r="Q766">
         <v>3.5</v>
       </c>
@@ -38822,7 +39102,7 @@
       </c>
       <c r="S766"/>
     </row>
-    <row r="767" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>139</v>
       </c>
@@ -38856,6 +39136,7 @@
       <c r="O767">
         <v>123203.3</v>
       </c>
+      <c r="P767"/>
       <c r="Q767">
         <v>6.5</v>
       </c>
@@ -38864,7 +39145,7 @@
       </c>
       <c r="S767"/>
     </row>
-    <row r="768" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>139</v>
       </c>
@@ -38889,6 +39170,7 @@
       <c r="O768">
         <v>123213.3</v>
       </c>
+      <c r="P768"/>
       <c r="Q768">
         <v>7.5</v>
       </c>
@@ -38897,7 +39179,7 @@
       </c>
       <c r="S768"/>
     </row>
-    <row r="769" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>139</v>
       </c>
@@ -38931,6 +39213,7 @@
       <c r="O769">
         <v>123219.5</v>
       </c>
+      <c r="P769" s="4"/>
       <c r="Q769">
         <v>5.5</v>
       </c>
@@ -38938,7 +39221,7 @@
         <v>1.0640000000000001</v>
       </c>
     </row>
-    <row r="770" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>139</v>
       </c>
@@ -38979,7 +39262,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>139</v>
       </c>
@@ -39020,7 +39303,7 @@
         <v>1.861</v>
       </c>
     </row>
-    <row r="772" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>139</v>
       </c>
@@ -39061,7 +39344,7 @@
         <v>0.96299999999999997</v>
       </c>
     </row>
-    <row r="773" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>139</v>
       </c>
@@ -39102,7 +39385,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="774" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>139</v>
       </c>
@@ -39184,7 +39467,7 @@
         <v>1.2250000000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>139</v>
       </c>
@@ -39234,7 +39517,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="777" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>139</v>
       </c>
@@ -39268,6 +39551,7 @@
       <c r="O777">
         <v>123938</v>
       </c>
+      <c r="P777" s="4"/>
       <c r="Q777">
         <v>5.5</v>
       </c>
@@ -39275,7 +39559,7 @@
         <v>1.2150000000000001</v>
       </c>
     </row>
-    <row r="778" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>139</v>
       </c>
@@ -39316,7 +39600,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="779" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>139</v>
       </c>
@@ -39348,7 +39632,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="780" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>139</v>
       </c>
@@ -39430,7 +39714,7 @@
         <v>1.157</v>
       </c>
     </row>
-    <row r="782" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>139</v>
       </c>
@@ -39471,7 +39755,7 @@
         <v>1.135</v>
       </c>
     </row>
-    <row r="783" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>139</v>
       </c>
@@ -39512,7 +39796,7 @@
         <v>1.0609999999999999</v>
       </c>
     </row>
-    <row r="784" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>139</v>
       </c>
@@ -39562,7 +39846,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="785" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>139</v>
       </c>
@@ -39596,6 +39880,7 @@
       <c r="O785">
         <v>124306.4</v>
       </c>
+      <c r="P785"/>
       <c r="Q785">
         <v>2.5</v>
       </c>
@@ -39604,7 +39889,7 @@
       </c>
       <c r="S785"/>
     </row>
-    <row r="786" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>139</v>
       </c>
@@ -39620,6 +39905,7 @@
       <c r="O786">
         <v>124336</v>
       </c>
+      <c r="P786"/>
       <c r="Q786">
         <v>8.5</v>
       </c>
@@ -39662,6 +39948,7 @@
       <c r="O787">
         <v>124337.3</v>
       </c>
+      <c r="P787"/>
       <c r="Q787">
         <v>3.5</v>
       </c>
@@ -39670,7 +39957,7 @@
       </c>
       <c r="S787"/>
     </row>
-    <row r="788" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>139</v>
       </c>
@@ -39704,6 +39991,7 @@
       <c r="O788">
         <v>124369.4</v>
       </c>
+      <c r="P788"/>
       <c r="Q788">
         <v>2.5</v>
       </c>
@@ -39712,7 +40000,7 @@
       </c>
       <c r="S788"/>
     </row>
-    <row r="789" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>139</v>
       </c>
@@ -39746,6 +40034,7 @@
       <c r="O789">
         <v>124372.6</v>
       </c>
+      <c r="P789"/>
       <c r="Q789">
         <v>0.5</v>
       </c>
@@ -39754,7 +40043,7 @@
       </c>
       <c r="S789"/>
     </row>
-    <row r="790" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>139</v>
       </c>
@@ -39788,6 +40077,7 @@
       <c r="O790">
         <v>124488.6</v>
       </c>
+      <c r="P790"/>
       <c r="Q790">
         <v>1.5</v>
       </c>
@@ -39796,7 +40086,7 @@
       </c>
       <c r="S790"/>
     </row>
-    <row r="791" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>139</v>
       </c>
@@ -39830,6 +40120,7 @@
       <c r="O791">
         <v>124571.3</v>
       </c>
+      <c r="P791"/>
       <c r="Q791">
         <v>2.5</v>
       </c>
@@ -39838,7 +40129,7 @@
       </c>
       <c r="S791"/>
     </row>
-    <row r="792" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>139</v>
       </c>
@@ -39881,6 +40172,7 @@
       <c r="O792">
         <v>124596.3</v>
       </c>
+      <c r="P792"/>
       <c r="Q792">
         <v>0.5</v>
       </c>
@@ -39889,7 +40181,7 @@
       </c>
       <c r="S792"/>
     </row>
-    <row r="793" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>139</v>
       </c>
@@ -39921,7 +40213,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="794" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>139</v>
       </c>
@@ -39955,6 +40247,7 @@
       <c r="O794">
         <v>124695.5</v>
       </c>
+      <c r="P794"/>
       <c r="Q794">
         <v>1.5</v>
       </c>
@@ -39997,6 +40290,7 @@
       <c r="O795">
         <v>124705.2</v>
       </c>
+      <c r="P795"/>
       <c r="Q795">
         <v>3.5</v>
       </c>
@@ -40005,7 +40299,7 @@
       </c>
       <c r="S795"/>
     </row>
-    <row r="796" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>139</v>
       </c>
@@ -40039,6 +40333,7 @@
       <c r="O796">
         <v>124751.6</v>
       </c>
+      <c r="P796"/>
       <c r="Q796">
         <v>4.5</v>
       </c>
@@ -40047,7 +40342,7 @@
       </c>
       <c r="S796"/>
     </row>
-    <row r="797" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>139</v>
       </c>
@@ -40081,6 +40376,7 @@
       <c r="O797">
         <v>124875.6</v>
       </c>
+      <c r="P797"/>
       <c r="Q797">
         <v>4.5</v>
       </c>
@@ -40089,7 +40385,7 @@
       </c>
       <c r="S797"/>
     </row>
-    <row r="798" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>139</v>
       </c>
@@ -40123,6 +40419,7 @@
       <c r="O798">
         <v>124905.1</v>
       </c>
+      <c r="P798"/>
       <c r="Q798">
         <v>1.5</v>
       </c>
@@ -40165,6 +40462,7 @@
       <c r="O799">
         <v>124989</v>
       </c>
+      <c r="P799"/>
       <c r="Q799">
         <v>3.5</v>
       </c>
@@ -40173,7 +40471,7 @@
       </c>
       <c r="S799"/>
     </row>
-    <row r="800" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>139</v>
       </c>
@@ -40207,6 +40505,7 @@
       <c r="O800">
         <v>124999.8</v>
       </c>
+      <c r="P800"/>
       <c r="Q800">
         <v>2.5</v>
       </c>
@@ -40215,7 +40514,7 @@
       </c>
       <c r="S800"/>
     </row>
-    <row r="801" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>139</v>
       </c>
@@ -40257,7 +40556,7 @@
       </c>
       <c r="S801"/>
     </row>
-    <row r="802" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>139</v>
       </c>
@@ -40291,6 +40590,7 @@
       <c r="O802">
         <v>125237.6</v>
       </c>
+      <c r="P802"/>
       <c r="Q802">
         <v>4.5</v>
       </c>
@@ -40342,6 +40642,7 @@
       <c r="O803">
         <v>125263.1</v>
       </c>
+      <c r="P803"/>
       <c r="Q803">
         <v>3.5</v>
       </c>
@@ -40350,7 +40651,7 @@
       </c>
       <c r="S803"/>
     </row>
-    <row r="804" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>139</v>
       </c>
@@ -40416,6 +40717,7 @@
       <c r="O805">
         <v>125530.6</v>
       </c>
+      <c r="P805"/>
       <c r="Q805">
         <v>3.5</v>
       </c>
@@ -40424,7 +40726,7 @@
       </c>
       <c r="S805"/>
     </row>
-    <row r="806" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>139</v>
       </c>
@@ -40458,6 +40760,7 @@
       <c r="O806">
         <v>125559.5</v>
       </c>
+      <c r="P806"/>
       <c r="Q806">
         <v>1.5</v>
       </c>
@@ -40466,7 +40769,7 @@
       </c>
       <c r="S806"/>
     </row>
-    <row r="807" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>139</v>
       </c>
@@ -40500,6 +40803,7 @@
       <c r="O807">
         <v>125690.4</v>
       </c>
+      <c r="P807"/>
       <c r="Q807">
         <v>2.5</v>
       </c>
@@ -40508,7 +40812,7 @@
       </c>
       <c r="S807"/>
     </row>
-    <row r="808" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>139</v>
       </c>
@@ -40542,6 +40846,7 @@
       <c r="O808">
         <v>125806.1</v>
       </c>
+      <c r="P808"/>
       <c r="Q808">
         <v>0.5</v>
       </c>
@@ -40550,7 +40855,7 @@
       </c>
       <c r="S808"/>
     </row>
-    <row r="809" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>139</v>
       </c>
@@ -40584,6 +40889,7 @@
       <c r="O809">
         <v>125889.9</v>
       </c>
+      <c r="P809"/>
       <c r="Q809">
         <v>1.5</v>
       </c>
@@ -40592,7 +40898,7 @@
       </c>
       <c r="S809"/>
     </row>
-    <row r="810" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>139</v>
       </c>
@@ -40626,6 +40932,7 @@
       <c r="O810">
         <v>126005.2</v>
       </c>
+      <c r="P810"/>
       <c r="Q810">
         <v>2.5</v>
       </c>
@@ -40634,7 +40941,7 @@
       </c>
       <c r="S810"/>
     </row>
-    <row r="811" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>139</v>
       </c>
@@ -40668,6 +40975,7 @@
       <c r="O811">
         <v>126138.2</v>
       </c>
+      <c r="P811"/>
       <c r="Q811">
         <v>4.5</v>
       </c>
@@ -40676,7 +40984,7 @@
       </c>
       <c r="S811"/>
     </row>
-    <row r="812" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>139</v>
       </c>
@@ -40710,6 +41018,7 @@
       <c r="O812">
         <v>126302.39999999999</v>
       </c>
+      <c r="P812"/>
       <c r="Q812">
         <v>0.5</v>
       </c>
@@ -40718,7 +41027,7 @@
       </c>
       <c r="S812"/>
     </row>
-    <row r="813" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>139</v>
       </c>
@@ -40752,6 +41061,7 @@
       <c r="O813">
         <v>126304.3</v>
       </c>
+      <c r="P813"/>
       <c r="Q813">
         <v>2.5</v>
       </c>
@@ -40760,7 +41070,7 @@
       </c>
       <c r="S813"/>
     </row>
-    <row r="814" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>139</v>
       </c>
@@ -40794,6 +41104,7 @@
       <c r="O814">
         <v>126408.2</v>
       </c>
+      <c r="P814"/>
       <c r="Q814">
         <v>2.5</v>
       </c>
@@ -40802,7 +41113,7 @@
       </c>
       <c r="S814"/>
     </row>
-    <row r="815" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>139</v>
       </c>
@@ -40839,7 +41150,7 @@
       <c r="O815">
         <v>126817.5</v>
       </c>
-      <c r="P815">
+      <c r="P815" s="4">
         <v>-74.2</v>
       </c>
       <c r="Q815">
@@ -40886,6 +41197,7 @@
       <c r="O816">
         <v>126856.4</v>
       </c>
+      <c r="P816"/>
       <c r="Q816">
         <v>3.5</v>
       </c>
@@ -40928,6 +41240,7 @@
       <c r="O817">
         <v>127128.4</v>
       </c>
+      <c r="P817"/>
       <c r="Q817">
         <v>3.5</v>
       </c>
@@ -40936,7 +41249,7 @@
       </c>
       <c r="S817"/>
     </row>
-    <row r="818" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>139</v>
       </c>
@@ -40970,6 +41283,7 @@
       <c r="O818">
         <v>127403.7</v>
       </c>
+      <c r="P818"/>
       <c r="Q818">
         <v>1.5</v>
       </c>
@@ -40978,7 +41292,7 @@
       </c>
       <c r="S818"/>
     </row>
-    <row r="819" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>139</v>
       </c>
@@ -41012,6 +41326,7 @@
       <c r="O819">
         <v>127490</v>
       </c>
+      <c r="P819"/>
       <c r="Q819">
         <v>6.5</v>
       </c>
@@ -41054,6 +41369,7 @@
       <c r="O820">
         <v>127710</v>
       </c>
+      <c r="P820"/>
       <c r="Q820">
         <v>3.5</v>
       </c>
@@ -41062,7 +41378,7 @@
       </c>
       <c r="S820"/>
     </row>
-    <row r="821" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>139</v>
       </c>
@@ -41096,6 +41412,7 @@
       <c r="O821">
         <v>127866.8</v>
       </c>
+      <c r="P821"/>
       <c r="Q821">
         <v>1.5</v>
       </c>
@@ -41138,6 +41455,7 @@
       <c r="O822">
         <v>128027.2</v>
       </c>
+      <c r="P822"/>
       <c r="Q822">
         <v>3.5</v>
       </c>
@@ -41146,7 +41464,7 @@
       </c>
       <c r="S822"/>
     </row>
-    <row r="823" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>139</v>
       </c>
@@ -41180,6 +41498,7 @@
       <c r="O823">
         <v>128336.4</v>
       </c>
+      <c r="P823"/>
       <c r="Q823">
         <v>4.5</v>
       </c>
@@ -41188,7 +41507,7 @@
       </c>
       <c r="S823"/>
     </row>
-    <row r="824" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>139</v>
       </c>
@@ -41230,7 +41549,7 @@
       </c>
       <c r="S824"/>
     </row>
-    <row r="825" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>139</v>
       </c>
@@ -41264,6 +41583,7 @@
       <c r="O825">
         <v>128617.9</v>
       </c>
+      <c r="P825"/>
       <c r="Q825">
         <v>2.5</v>
       </c>
@@ -41272,7 +41592,7 @@
       </c>
       <c r="S825"/>
     </row>
-    <row r="826" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>139</v>
       </c>
@@ -41306,6 +41626,7 @@
       <c r="O826">
         <v>128662.39999999999</v>
       </c>
+      <c r="P826"/>
       <c r="Q826">
         <v>1.5</v>
       </c>
@@ -41314,7 +41635,7 @@
       </c>
       <c r="S826"/>
     </row>
-    <row r="827" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>139</v>
       </c>
@@ -41348,6 +41669,7 @@
       <c r="O827">
         <v>128811.4</v>
       </c>
+      <c r="P827"/>
       <c r="Q827">
         <v>0.5</v>
       </c>
@@ -41397,7 +41719,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="829" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>139</v>
       </c>
@@ -41431,6 +41753,7 @@
       <c r="O829">
         <v>129085.9</v>
       </c>
+      <c r="P829"/>
       <c r="Q829">
         <v>2.5</v>
       </c>
@@ -41439,7 +41762,7 @@
       </c>
       <c r="S829"/>
     </row>
-    <row r="830" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>139</v>
       </c>
@@ -41480,7 +41803,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="831" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>139</v>
       </c>
@@ -41514,6 +41837,7 @@
       <c r="O831">
         <v>129334.8</v>
       </c>
+      <c r="P831"/>
       <c r="Q831">
         <v>1.5</v>
       </c>
@@ -41522,7 +41846,7 @@
       </c>
       <c r="S831"/>
     </row>
-    <row r="832" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>139</v>
       </c>
@@ -41572,7 +41896,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="833" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>139</v>
       </c>
@@ -41606,6 +41930,7 @@
       <c r="O833">
         <v>129486.6</v>
       </c>
+      <c r="P833"/>
       <c r="Q833">
         <v>2.5</v>
       </c>
@@ -41614,7 +41939,7 @@
       </c>
       <c r="S833"/>
     </row>
-    <row r="834" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>139</v>
       </c>
@@ -41648,6 +41973,7 @@
       <c r="O834">
         <v>129564</v>
       </c>
+      <c r="P834"/>
       <c r="Q834">
         <v>4.5</v>
       </c>
@@ -41656,7 +41982,7 @@
       </c>
       <c r="S834"/>
     </row>
-    <row r="835" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>139</v>
       </c>
@@ -41678,8 +42004,15 @@
       <c r="J835" t="s">
         <v>188</v>
       </c>
-      <c r="O835">
+      <c r="N835" s="3">
+        <v>129498.0707</v>
+      </c>
+      <c r="O835" s="3">
         <v>129628.2</v>
+      </c>
+      <c r="P835" s="5">
+        <f>N835-O835</f>
+        <v>-130.12930000000051</v>
       </c>
       <c r="Q835">
         <v>5.5</v>
@@ -41687,7 +42020,9 @@
       <c r="R835">
         <v>0.79700000000000004</v>
       </c>
-      <c r="S835"/>
+      <c r="S835" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="836" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
@@ -41723,6 +42058,7 @@
       <c r="O836">
         <v>129738.7</v>
       </c>
+      <c r="P836"/>
       <c r="Q836">
         <v>3.5</v>
       </c>
@@ -41731,7 +42067,7 @@
       </c>
       <c r="S836"/>
     </row>
-    <row r="837" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>139</v>
       </c>
@@ -41759,7 +42095,7 @@
       <c r="O837">
         <v>129826.7</v>
       </c>
-      <c r="P837">
+      <c r="P837" s="4">
         <v>107.8</v>
       </c>
       <c r="Q837">
@@ -41772,7 +42108,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="838" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>139</v>
       </c>
@@ -41822,7 +42158,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="839" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>139</v>
       </c>
@@ -41856,6 +42192,7 @@
       <c r="O839">
         <v>130042</v>
       </c>
+      <c r="P839"/>
       <c r="Q839">
         <v>2.5</v>
       </c>
@@ -41866,7 +42203,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="840" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>139</v>
       </c>
@@ -41941,6 +42278,7 @@
       <c r="O841">
         <v>130141.8</v>
       </c>
+      <c r="P841"/>
       <c r="Q841">
         <v>3.5</v>
       </c>
@@ -41949,7 +42287,7 @@
       </c>
       <c r="S841"/>
     </row>
-    <row r="842" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>139</v>
       </c>
@@ -41983,6 +42321,7 @@
       <c r="O842">
         <v>130258.2</v>
       </c>
+      <c r="P842"/>
       <c r="Q842">
         <v>2.5</v>
       </c>
@@ -42025,6 +42364,7 @@
       <c r="O843">
         <v>130272.1</v>
       </c>
+      <c r="P843"/>
       <c r="Q843">
         <v>3.5</v>
       </c>
@@ -42033,7 +42373,7 @@
       </c>
       <c r="S843"/>
     </row>
-    <row r="844" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>139</v>
       </c>
@@ -42067,6 +42407,7 @@
       <c r="O844">
         <v>130273.2</v>
       </c>
+      <c r="P844"/>
       <c r="Q844">
         <v>4.5</v>
       </c>
@@ -42075,7 +42416,7 @@
       </c>
       <c r="S844"/>
     </row>
-    <row r="845" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>139</v>
       </c>
@@ -42109,6 +42450,7 @@
       <c r="O845">
         <v>130288</v>
       </c>
+      <c r="P845"/>
       <c r="Q845">
         <v>1.5</v>
       </c>
@@ -42117,7 +42459,7 @@
       </c>
       <c r="S845"/>
     </row>
-    <row r="846" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>139</v>
       </c>
@@ -42151,6 +42493,7 @@
       <c r="O846">
         <v>130432.6</v>
       </c>
+      <c r="P846"/>
       <c r="Q846">
         <v>1.5</v>
       </c>
@@ -42159,7 +42502,7 @@
       </c>
       <c r="S846"/>
     </row>
-    <row r="847" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>139</v>
       </c>
@@ -42193,6 +42536,7 @@
       <c r="O847">
         <v>130935.4</v>
       </c>
+      <c r="P847"/>
       <c r="Q847">
         <v>2.5</v>
       </c>
@@ -42201,7 +42545,7 @@
       </c>
       <c r="S847"/>
     </row>
-    <row r="848" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>139</v>
       </c>
@@ -42238,7 +42582,7 @@
       <c r="O848">
         <v>131074.6</v>
       </c>
-      <c r="P848">
+      <c r="P848" s="4">
         <v>125.7</v>
       </c>
       <c r="Q848">
@@ -42251,7 +42595,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="849" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>139</v>
       </c>
@@ -42285,6 +42629,7 @@
       <c r="O849">
         <v>131122.79999999999</v>
       </c>
+      <c r="P849"/>
       <c r="Q849">
         <v>0.5</v>
       </c>
@@ -42293,7 +42638,7 @@
       </c>
       <c r="S849"/>
     </row>
-    <row r="850" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>139</v>
       </c>
@@ -42377,6 +42722,7 @@
       <c r="O851">
         <v>131294.1</v>
       </c>
+      <c r="P851"/>
       <c r="Q851">
         <v>3.5</v>
       </c>
@@ -42385,7 +42731,7 @@
       </c>
       <c r="S851"/>
     </row>
-    <row r="852" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>139</v>
       </c>
@@ -42436,7 +42782,7 @@
       </c>
       <c r="S852"/>
     </row>
-    <row r="853" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>139</v>
       </c>
@@ -42470,6 +42816,7 @@
       <c r="O853">
         <v>131498.1</v>
       </c>
+      <c r="P853"/>
       <c r="Q853">
         <v>4.5</v>
       </c>
@@ -42478,7 +42825,7 @@
       </c>
       <c r="S853"/>
     </row>
-    <row r="854" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>139</v>
       </c>
@@ -42520,7 +42867,7 @@
       </c>
       <c r="S854"/>
     </row>
-    <row r="855" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>139</v>
       </c>
@@ -42561,7 +42908,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="856" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>139</v>
       </c>
@@ -42595,6 +42942,7 @@
       <c r="O856">
         <v>131895.4</v>
       </c>
+      <c r="P856"/>
       <c r="Q856">
         <v>4.5</v>
       </c>
@@ -42603,7 +42951,7 @@
       </c>
       <c r="S856"/>
     </row>
-    <row r="857" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>139</v>
       </c>
@@ -42627,7 +42975,7 @@
       </c>
       <c r="S857"/>
     </row>
-    <row r="858" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>139</v>
       </c>
@@ -42643,6 +42991,7 @@
       <c r="O858">
         <v>132069.6</v>
       </c>
+      <c r="P858"/>
       <c r="Q858">
         <v>7.5</v>
       </c>
@@ -42651,7 +43000,7 @@
       </c>
       <c r="S858"/>
     </row>
-    <row r="859" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>139</v>
       </c>
@@ -42701,7 +43050,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="860" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>139</v>
       </c>
@@ -42735,6 +43084,7 @@
       <c r="O860">
         <v>132112.5</v>
       </c>
+      <c r="P860"/>
       <c r="Q860">
         <v>2.5</v>
       </c>
@@ -42777,6 +43127,7 @@
       <c r="O861">
         <v>132136</v>
       </c>
+      <c r="P861"/>
       <c r="Q861">
         <v>3.5</v>
       </c>
@@ -42785,7 +43136,7 @@
       </c>
       <c r="S861"/>
     </row>
-    <row r="862" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>139</v>
       </c>
@@ -42819,6 +43170,7 @@
       <c r="O862">
         <v>132226.20000000001</v>
       </c>
+      <c r="P862"/>
       <c r="Q862">
         <v>4.5</v>
       </c>
@@ -42827,7 +43179,7 @@
       </c>
       <c r="S862"/>
     </row>
-    <row r="863" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>139</v>
       </c>
@@ -42861,6 +43213,7 @@
       <c r="O863">
         <v>132305.29999999999</v>
       </c>
+      <c r="P863"/>
       <c r="Q863">
         <v>1.5</v>
       </c>
@@ -42903,6 +43256,7 @@
       <c r="O864">
         <v>132460.5</v>
       </c>
+      <c r="P864"/>
       <c r="Q864">
         <v>3.5</v>
       </c>
@@ -42911,7 +43265,7 @@
       </c>
       <c r="S864"/>
     </row>
-    <row r="865" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>139</v>
       </c>
@@ -42945,6 +43299,7 @@
       <c r="O865">
         <v>132788.5</v>
       </c>
+      <c r="P865"/>
       <c r="Q865">
         <v>2.5</v>
       </c>
@@ -42987,6 +43342,7 @@
       <c r="O866">
         <v>132963.70000000001</v>
       </c>
+      <c r="P866"/>
       <c r="Q866">
         <v>3.5</v>
       </c>
@@ -42995,7 +43351,7 @@
       </c>
       <c r="S866"/>
     </row>
-    <row r="867" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>139</v>
       </c>
@@ -43029,6 +43385,7 @@
       <c r="O867">
         <v>133097.9</v>
       </c>
+      <c r="P867"/>
       <c r="Q867">
         <v>0.5</v>
       </c>
@@ -43037,7 +43394,7 @@
       </c>
       <c r="S867"/>
     </row>
-    <row r="868" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>139</v>
       </c>
@@ -43069,7 +43426,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="869" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>139</v>
       </c>
@@ -43088,7 +43445,7 @@
       <c r="O869">
         <v>133515.5</v>
       </c>
-      <c r="P869">
+      <c r="P869" s="4">
         <v>-11.6</v>
       </c>
       <c r="Q869">
@@ -43101,7 +43458,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="870" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>139</v>
       </c>
@@ -43135,6 +43492,7 @@
       <c r="O870">
         <v>133599.70000000001</v>
       </c>
+      <c r="P870"/>
       <c r="Q870">
         <v>1.5</v>
       </c>
@@ -43143,7 +43501,7 @@
       </c>
       <c r="S870"/>
     </row>
-    <row r="871" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>139</v>
       </c>
@@ -43186,6 +43544,7 @@
       <c r="O871">
         <v>133665.4</v>
       </c>
+      <c r="P871"/>
       <c r="Q871">
         <v>2.5</v>
       </c>
@@ -43194,7 +43553,7 @@
       </c>
       <c r="S871"/>
     </row>
-    <row r="872" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>139</v>
       </c>
@@ -43236,7 +43595,7 @@
       </c>
       <c r="S872"/>
     </row>
-    <row r="873" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>139</v>
       </c>
@@ -43261,6 +43620,7 @@
       <c r="O873">
         <v>134001.60000000001</v>
       </c>
+      <c r="P873"/>
       <c r="Q873">
         <v>6.5</v>
       </c>
@@ -43269,7 +43629,7 @@
       </c>
       <c r="S873"/>
     </row>
-    <row r="874" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>139</v>
       </c>
@@ -43294,6 +43654,7 @@
       <c r="O874">
         <v>134002</v>
       </c>
+      <c r="P874"/>
       <c r="Q874">
         <v>7.5</v>
       </c>
@@ -43302,7 +43663,7 @@
       </c>
       <c r="S874"/>
     </row>
-    <row r="875" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>139</v>
       </c>
@@ -43327,6 +43688,7 @@
       <c r="O875">
         <v>134076.9</v>
       </c>
+      <c r="P875"/>
       <c r="Q875">
         <v>1.5</v>
       </c>
@@ -43335,7 +43697,7 @@
       </c>
       <c r="S875"/>
     </row>
-    <row r="876" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>139</v>
       </c>
@@ -43377,7 +43739,7 @@
       </c>
       <c r="S876"/>
     </row>
-    <row r="877" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>139</v>
       </c>
@@ -43402,6 +43764,7 @@
       <c r="O877">
         <v>134186.79999999999</v>
       </c>
+      <c r="P877"/>
       <c r="Q877">
         <v>2.5</v>
       </c>
@@ -43410,7 +43773,7 @@
       </c>
       <c r="S877"/>
     </row>
-    <row r="878" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>139</v>
       </c>
@@ -43426,6 +43789,7 @@
       <c r="O878">
         <v>134191.4</v>
       </c>
+      <c r="P878"/>
       <c r="Q878">
         <v>8.5</v>
       </c>
@@ -43434,7 +43798,7 @@
       </c>
       <c r="S878"/>
     </row>
-    <row r="879" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>139</v>
       </c>
@@ -43468,6 +43832,7 @@
       <c r="O879">
         <v>134204.5</v>
       </c>
+      <c r="P879"/>
       <c r="Q879">
         <v>6.5</v>
       </c>
@@ -43476,7 +43841,7 @@
       </c>
       <c r="S879"/>
     </row>
-    <row r="880" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>139</v>
       </c>
@@ -43509,7 +43874,7 @@
       </c>
       <c r="S880"/>
     </row>
-    <row r="881" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>139</v>
       </c>
@@ -43546,7 +43911,7 @@
       <c r="O881">
         <v>134379.9</v>
       </c>
-      <c r="P881">
+      <c r="P881" s="4">
         <v>14.26</v>
       </c>
       <c r="Q881">
@@ -43559,7 +43924,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="882" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>139</v>
       </c>
@@ -43600,7 +43965,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="883" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>139</v>
       </c>
@@ -43641,7 +44006,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="884" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>139</v>
       </c>
@@ -43678,7 +44043,7 @@
       <c r="O884">
         <v>134395.29999999999</v>
       </c>
-      <c r="P884">
+      <c r="P884" s="4">
         <v>7.53</v>
       </c>
       <c r="Q884">
@@ -43691,7 +44056,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="885" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>139</v>
       </c>
@@ -43732,7 +44097,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="886" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>139</v>
       </c>
@@ -43814,7 +44179,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="888" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>139</v>
       </c>
@@ -43839,6 +44204,7 @@
       <c r="O888">
         <v>134428.70000000001</v>
       </c>
+      <c r="P888"/>
       <c r="Q888">
         <v>4.5</v>
       </c>
@@ -43847,7 +44213,7 @@
       </c>
       <c r="S888"/>
     </row>
-    <row r="889" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>139</v>
       </c>
@@ -43872,6 +44238,7 @@
       <c r="O889">
         <v>134464</v>
       </c>
+      <c r="P889"/>
       <c r="Q889">
         <v>4.5</v>
       </c>
@@ -43921,7 +44288,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="891" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>139</v>
       </c>
@@ -43962,7 +44329,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="892" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>139</v>
       </c>
@@ -43987,6 +44354,7 @@
       <c r="O892">
         <v>134489.29999999999</v>
       </c>
+      <c r="P892"/>
       <c r="Q892">
         <v>7.5</v>
       </c>
@@ -43995,7 +44363,7 @@
       </c>
       <c r="S892"/>
     </row>
-    <row r="893" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>139</v>
       </c>
@@ -44036,7 +44404,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="894" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>139</v>
       </c>
@@ -44077,7 +44445,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="895" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>139</v>
       </c>
@@ -44118,7 +44486,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="896" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>139</v>
       </c>
@@ -44159,7 +44527,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="897" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>139</v>
       </c>
@@ -44193,6 +44561,7 @@
       <c r="O897">
         <v>134542.70000000001</v>
       </c>
+      <c r="P897"/>
       <c r="Q897">
         <v>0.5</v>
       </c>
@@ -44201,7 +44570,7 @@
       </c>
       <c r="S897"/>
     </row>
-    <row r="898" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>139</v>
       </c>
@@ -44242,7 +44611,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="899" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>139</v>
       </c>
@@ -44276,6 +44645,7 @@
       <c r="O899">
         <v>134560.6</v>
       </c>
+      <c r="P899"/>
       <c r="Q899">
         <v>0.5</v>
       </c>
@@ -44318,6 +44688,7 @@
       <c r="O900">
         <v>134679.5</v>
       </c>
+      <c r="P900"/>
       <c r="Q900">
         <v>3.5</v>
       </c>
@@ -44326,7 +44697,7 @@
       </c>
       <c r="S900"/>
     </row>
-    <row r="901" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>139</v>
       </c>
@@ -44360,6 +44731,7 @@
       <c r="O901">
         <v>134714.79999999999</v>
       </c>
+      <c r="P901"/>
       <c r="Q901">
         <v>4.5</v>
       </c>
@@ -44368,7 +44740,7 @@
       </c>
       <c r="S901"/>
     </row>
-    <row r="902" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>139</v>
       </c>
@@ -44402,6 +44774,7 @@
       <c r="O902">
         <v>134810.9</v>
       </c>
+      <c r="P902"/>
       <c r="Q902">
         <v>0.5</v>
       </c>
@@ -44410,7 +44783,7 @@
       </c>
       <c r="S902"/>
     </row>
-    <row r="903" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>139</v>
       </c>
@@ -44444,6 +44817,7 @@
       <c r="O903">
         <v>134848.29999999999</v>
       </c>
+      <c r="P903"/>
       <c r="Q903">
         <v>1.5</v>
       </c>
@@ -44452,7 +44826,7 @@
       </c>
       <c r="S903"/>
     </row>
-    <row r="904" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>139</v>
       </c>
@@ -44486,6 +44860,7 @@
       <c r="O904">
         <v>134861.29999999999</v>
       </c>
+      <c r="P904"/>
       <c r="Q904">
         <v>2.5</v>
       </c>
@@ -44494,7 +44869,7 @@
       </c>
       <c r="S904"/>
     </row>
-    <row r="905" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>139</v>
       </c>
@@ -44519,6 +44894,7 @@
       <c r="O905">
         <v>134997.79999999999</v>
       </c>
+      <c r="P905"/>
       <c r="Q905">
         <v>0.5</v>
       </c>
@@ -44527,7 +44903,7 @@
       </c>
       <c r="S905"/>
     </row>
-    <row r="906" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>139</v>
       </c>
@@ -44561,6 +44937,7 @@
       <c r="O906">
         <v>135028.9</v>
       </c>
+      <c r="P906"/>
       <c r="Q906">
         <v>4.5</v>
       </c>
@@ -44569,7 +44946,7 @@
       </c>
       <c r="S906"/>
     </row>
-    <row r="907" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>139</v>
       </c>
@@ -44603,6 +44980,7 @@
       <c r="O907">
         <v>135076.70000000001</v>
       </c>
+      <c r="P907"/>
       <c r="Q907">
         <v>1.5</v>
       </c>
@@ -44611,7 +44989,7 @@
       </c>
       <c r="S907"/>
     </row>
-    <row r="908" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>139</v>
       </c>
@@ -44645,6 +45023,7 @@
       <c r="O908">
         <v>135129.29999999999</v>
       </c>
+      <c r="P908"/>
       <c r="Q908">
         <v>1.5</v>
       </c>
@@ -44687,6 +45066,7 @@
       <c r="O909">
         <v>135131.5</v>
       </c>
+      <c r="P909"/>
       <c r="Q909">
         <v>3.5</v>
       </c>
@@ -44695,7 +45075,7 @@
       </c>
       <c r="S909"/>
     </row>
-    <row r="910" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>139</v>
       </c>
@@ -44729,6 +45109,7 @@
       <c r="O910">
         <v>135190.39999999999</v>
       </c>
+      <c r="P910"/>
       <c r="Q910">
         <v>2.5</v>
       </c>
@@ -44771,6 +45152,7 @@
       <c r="O911">
         <v>135213.6</v>
       </c>
+      <c r="P911"/>
       <c r="Q911">
         <v>3.5</v>
       </c>
@@ -44811,7 +45193,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="913" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>139</v>
       </c>
@@ -44845,6 +45227,7 @@
       <c r="O913">
         <v>135571.79999999999</v>
       </c>
+      <c r="P913"/>
       <c r="Q913">
         <v>1.5</v>
       </c>
@@ -44853,7 +45236,7 @@
       </c>
       <c r="S913"/>
     </row>
-    <row r="914" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>139</v>
       </c>
@@ -44869,6 +45252,7 @@
       <c r="O914">
         <v>135576.6</v>
       </c>
+      <c r="P914"/>
       <c r="Q914">
         <v>2.5</v>
       </c>
@@ -44877,7 +45261,7 @@
       </c>
       <c r="S914"/>
     </row>
-    <row r="915" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>139</v>
       </c>
@@ -44911,6 +45295,7 @@
       <c r="O915">
         <v>135712.20000000001</v>
       </c>
+      <c r="P915"/>
       <c r="Q915">
         <v>0.5</v>
       </c>
@@ -44919,7 +45304,7 @@
       </c>
       <c r="S915"/>
     </row>
-    <row r="916" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>139</v>
       </c>
@@ -44953,6 +45338,7 @@
       <c r="O916">
         <v>135975.5</v>
       </c>
+      <c r="P916"/>
       <c r="Q916">
         <v>6.5</v>
       </c>
@@ -44961,7 +45347,7 @@
       </c>
       <c r="S916"/>
     </row>
-    <row r="917" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>139</v>
       </c>
@@ -44986,6 +45372,7 @@
       <c r="O917">
         <v>135976.6</v>
       </c>
+      <c r="P917"/>
       <c r="Q917">
         <v>2.5</v>
       </c>
@@ -44994,7 +45381,7 @@
       </c>
       <c r="S917"/>
     </row>
-    <row r="918" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>139</v>
       </c>
@@ -45069,6 +45456,7 @@
       <c r="O919">
         <v>136082.5</v>
       </c>
+      <c r="P919"/>
       <c r="Q919">
         <v>3.5</v>
       </c>
@@ -45077,7 +45465,7 @@
       </c>
       <c r="S919"/>
     </row>
-    <row r="920" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>139</v>
       </c>
@@ -45102,6 +45490,7 @@
       <c r="O920">
         <v>136186.29999999999</v>
       </c>
+      <c r="P920"/>
       <c r="Q920">
         <v>1.5</v>
       </c>
@@ -45110,7 +45499,7 @@
       </c>
       <c r="S920"/>
     </row>
-    <row r="921" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>139</v>
       </c>
@@ -45141,8 +45530,15 @@
       <c r="M921" t="s">
         <v>153</v>
       </c>
-      <c r="O921">
+      <c r="N921" s="3">
+        <v>136033.576</v>
+      </c>
+      <c r="O921" s="3">
         <v>136212</v>
+      </c>
+      <c r="P921" s="3">
+        <f>N921-O921</f>
+        <v>-178.42399999999907</v>
       </c>
       <c r="Q921">
         <v>4.5</v>
@@ -45150,9 +45546,11 @@
       <c r="R921">
         <v>0.98799999999999999</v>
       </c>
-      <c r="S921"/>
-    </row>
-    <row r="922" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S921" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="922" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>139</v>
       </c>
@@ -45186,6 +45584,7 @@
       <c r="O922">
         <v>136261.9</v>
       </c>
+      <c r="P922"/>
       <c r="Q922">
         <v>4.5</v>
       </c>
@@ -45194,7 +45593,7 @@
       </c>
       <c r="S922"/>
     </row>
-    <row r="923" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>139</v>
       </c>
@@ -45270,6 +45669,7 @@
       <c r="O924">
         <v>136306.5</v>
       </c>
+      <c r="P924"/>
       <c r="Q924">
         <v>3.5</v>
       </c>
@@ -45278,7 +45678,7 @@
       </c>
       <c r="S924"/>
     </row>
-    <row r="925" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>139</v>
       </c>
@@ -45312,6 +45712,7 @@
       <c r="O925">
         <v>136376.6</v>
       </c>
+      <c r="P925"/>
       <c r="Q925">
         <v>2.5</v>
       </c>
@@ -45320,7 +45721,7 @@
       </c>
       <c r="S925"/>
     </row>
-    <row r="926" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>139</v>
       </c>
@@ -45345,6 +45746,7 @@
       <c r="O926">
         <v>136478.29999999999</v>
       </c>
+      <c r="P926"/>
       <c r="Q926">
         <v>4.5</v>
       </c>
@@ -45353,7 +45755,7 @@
       </c>
       <c r="S926"/>
     </row>
-    <row r="927" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>139</v>
       </c>
@@ -45385,7 +45787,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="928" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>139</v>
       </c>
@@ -45404,7 +45806,7 @@
       <c r="O928">
         <v>136525.20000000001</v>
       </c>
-      <c r="P928">
+      <c r="P928" s="4">
         <v>30.25</v>
       </c>
       <c r="Q928">
@@ -45417,7 +45819,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="929" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>139</v>
       </c>
@@ -45449,7 +45851,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="930" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>139</v>
       </c>
@@ -45481,7 +45883,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="931" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>139</v>
       </c>
@@ -45513,7 +45915,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="932" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>139</v>
       </c>
@@ -45532,7 +45934,7 @@
       <c r="O932">
         <v>136553.9</v>
       </c>
-      <c r="P932">
+      <c r="P932" s="4">
         <v>16.91</v>
       </c>
       <c r="Q932">
@@ -45545,7 +45947,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="933" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>139</v>
       </c>
@@ -45577,7 +45979,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="934" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>139</v>
       </c>
@@ -45609,7 +46011,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="935" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>139</v>
       </c>
@@ -45643,6 +46045,7 @@
       <c r="O935">
         <v>136568.70000000001</v>
       </c>
+      <c r="P935"/>
       <c r="Q935">
         <v>1.5</v>
       </c>
@@ -45676,6 +46079,7 @@
       <c r="O936">
         <v>136591.4</v>
       </c>
+      <c r="P936"/>
       <c r="Q936">
         <v>3.5</v>
       </c>
@@ -45684,7 +46088,7 @@
       </c>
       <c r="S936"/>
     </row>
-    <row r="937" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>139</v>
       </c>
@@ -45716,7 +46120,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="938" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>139</v>
       </c>
@@ -45750,6 +46154,7 @@
       <c r="O938">
         <v>136597.70000000001</v>
       </c>
+      <c r="P938"/>
       <c r="Q938">
         <v>0.5</v>
       </c>
@@ -45792,6 +46197,7 @@
       <c r="O939">
         <v>136601.4</v>
       </c>
+      <c r="P939"/>
       <c r="Q939">
         <v>3.5</v>
       </c>
@@ -45800,7 +46206,7 @@
       </c>
       <c r="S939"/>
     </row>
-    <row r="940" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>139</v>
       </c>
@@ -45834,6 +46240,7 @@
       <c r="O940">
         <v>136605.70000000001</v>
       </c>
+      <c r="P940"/>
       <c r="Q940">
         <v>2.5</v>
       </c>
@@ -45874,7 +46281,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="942" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>139</v>
       </c>
@@ -45924,7 +46331,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="943" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>139</v>
       </c>
@@ -45956,7 +46363,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="944" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>139</v>
       </c>
@@ -45988,7 +46395,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="945" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>139</v>
       </c>
@@ -46029,7 +46436,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="946" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>139</v>
       </c>
@@ -46070,7 +46477,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="947" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>139</v>
       </c>
@@ -46112,7 +46519,7 @@
       </c>
       <c r="S947"/>
     </row>
-    <row r="948" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>139</v>
       </c>
@@ -46146,6 +46553,7 @@
       <c r="O948">
         <v>136700.70000000001</v>
       </c>
+      <c r="P948"/>
       <c r="Q948">
         <v>1.5</v>
       </c>
@@ -46154,7 +46562,7 @@
       </c>
       <c r="S948"/>
     </row>
-    <row r="949" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>139</v>
       </c>
@@ -46179,6 +46587,7 @@
       <c r="O949">
         <v>136713.60000000001</v>
       </c>
+      <c r="P949"/>
       <c r="Q949">
         <v>0.5</v>
       </c>
@@ -46187,7 +46596,7 @@
       </c>
       <c r="S949"/>
     </row>
-    <row r="950" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>139</v>
       </c>
@@ -46221,6 +46630,7 @@
       <c r="O950">
         <v>136752.1</v>
       </c>
+      <c r="P950"/>
       <c r="Q950">
         <v>2.5</v>
       </c>
@@ -46229,7 +46639,7 @@
       </c>
       <c r="S950"/>
     </row>
-    <row r="951" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>139</v>
       </c>
@@ -46254,6 +46664,7 @@
       <c r="O951">
         <v>136778</v>
       </c>
+      <c r="P951"/>
       <c r="Q951">
         <v>6.5</v>
       </c>
@@ -46262,7 +46673,7 @@
       </c>
       <c r="S951"/>
     </row>
-    <row r="952" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>139</v>
       </c>
@@ -46296,6 +46707,7 @@
       <c r="O952">
         <v>136836.9</v>
       </c>
+      <c r="P952"/>
       <c r="Q952">
         <v>4.5</v>
       </c>
@@ -46338,6 +46750,7 @@
       <c r="O953">
         <v>136881.70000000001</v>
       </c>
+      <c r="P953"/>
       <c r="Q953">
         <v>3.5</v>
       </c>
@@ -46346,7 +46759,7 @@
       </c>
       <c r="S953"/>
     </row>
-    <row r="954" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>139</v>
       </c>
@@ -46389,6 +46802,7 @@
       <c r="O954">
         <v>136895.1</v>
       </c>
+      <c r="P954"/>
       <c r="Q954">
         <v>1.5</v>
       </c>
@@ -46397,7 +46811,7 @@
       </c>
       <c r="S954"/>
     </row>
-    <row r="955" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>139</v>
       </c>
@@ -46473,6 +46887,7 @@
       <c r="O956">
         <v>137023.4</v>
       </c>
+      <c r="P956"/>
       <c r="Q956">
         <v>3.5</v>
       </c>
@@ -46481,7 +46896,7 @@
       </c>
       <c r="S956"/>
     </row>
-    <row r="957" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>139</v>
       </c>
@@ -46515,6 +46930,7 @@
       <c r="O957">
         <v>137083.5</v>
       </c>
+      <c r="P957"/>
       <c r="Q957">
         <v>4.5</v>
       </c>
@@ -46557,6 +46973,7 @@
       <c r="O958">
         <v>137240.9</v>
       </c>
+      <c r="P958"/>
       <c r="Q958">
         <v>3.5</v>
       </c>
@@ -46599,6 +47016,7 @@
       <c r="O959">
         <v>137284.29999999999</v>
       </c>
+      <c r="P959"/>
       <c r="Q959">
         <v>3.5</v>
       </c>
@@ -46607,7 +47025,7 @@
       </c>
       <c r="S959"/>
     </row>
-    <row r="960" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>139</v>
       </c>
@@ -46641,6 +47059,7 @@
       <c r="O960">
         <v>137289.70000000001</v>
       </c>
+      <c r="P960"/>
       <c r="Q960">
         <v>2.5</v>
       </c>
@@ -46649,7 +47068,7 @@
       </c>
       <c r="S960"/>
     </row>
-    <row r="961" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>139</v>
       </c>
@@ -46683,6 +47102,7 @@
       <c r="O961">
         <v>137383.70000000001</v>
       </c>
+      <c r="P961"/>
       <c r="Q961">
         <v>4.5</v>
       </c>
@@ -46691,7 +47111,7 @@
       </c>
       <c r="S961"/>
     </row>
-    <row r="962" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>139</v>
       </c>
@@ -46725,6 +47145,7 @@
       <c r="O962">
         <v>137484.4</v>
       </c>
+      <c r="P962"/>
       <c r="Q962">
         <v>1.5</v>
       </c>
@@ -46733,7 +47154,7 @@
       </c>
       <c r="S962"/>
     </row>
-    <row r="963" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>139</v>
       </c>
@@ -46767,6 +47188,7 @@
       <c r="O963">
         <v>138243.1</v>
       </c>
+      <c r="P963"/>
       <c r="Q963">
         <v>0.5</v>
       </c>
@@ -46775,7 +47197,7 @@
       </c>
       <c r="S963"/>
     </row>
-    <row r="964" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>139</v>
       </c>
@@ -46809,6 +47231,7 @@
       <c r="O964">
         <v>138471.9</v>
       </c>
+      <c r="P964"/>
       <c r="Q964">
         <v>2.5</v>
       </c>
@@ -46817,7 +47240,7 @@
       </c>
       <c r="S964"/>
     </row>
-    <row r="965" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>139</v>
       </c>
@@ -46842,6 +47265,7 @@
       <c r="O965">
         <v>138572.70000000001</v>
       </c>
+      <c r="P965"/>
       <c r="Q965">
         <v>4.5</v>
       </c>
@@ -46850,7 +47274,7 @@
       </c>
       <c r="S965"/>
     </row>
-    <row r="966" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>139</v>
       </c>
@@ -46891,7 +47315,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="967" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>139</v>
       </c>
@@ -46932,7 +47356,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="968" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>139</v>
       </c>
@@ -46973,7 +47397,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="969" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>139</v>
       </c>
@@ -47005,7 +47429,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="970" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>139</v>
       </c>
@@ -47046,7 +47470,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="971" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>139</v>
       </c>
@@ -47065,7 +47489,7 @@
       <c r="O971">
         <v>138785.29999999999</v>
       </c>
-      <c r="P971">
+      <c r="P971" s="4">
         <v>14.61</v>
       </c>
       <c r="Q971">
@@ -47078,7 +47502,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="972" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>139</v>
       </c>
@@ -47110,7 +47534,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="973" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>139</v>
       </c>
@@ -47142,7 +47566,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="974" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>139</v>
       </c>
@@ -47161,7 +47585,7 @@
       <c r="O974">
         <v>138823.4</v>
       </c>
-      <c r="P974">
+      <c r="P974" s="4">
         <v>-1</v>
       </c>
       <c r="Q974">
@@ -47174,7 +47598,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="975" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>139</v>
       </c>
@@ -47206,7 +47630,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="976" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>139</v>
       </c>
@@ -47270,7 +47694,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="978" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>139</v>
       </c>
@@ -47302,7 +47726,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="979" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>139</v>
       </c>
@@ -47350,6 +47774,7 @@
       <c r="O980">
         <v>138907.6</v>
       </c>
+      <c r="P980"/>
       <c r="Q980">
         <v>3.5</v>
       </c>
@@ -47358,7 +47783,7 @@
       </c>
       <c r="S980"/>
     </row>
-    <row r="981" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>139</v>
       </c>
@@ -47390,7 +47815,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="982" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>139</v>
       </c>
@@ -47406,6 +47831,7 @@
       <c r="O982">
         <v>138940.79999999999</v>
       </c>
+      <c r="P982"/>
       <c r="Q982">
         <v>2.5</v>
       </c>
@@ -47414,7 +47840,7 @@
       </c>
       <c r="S982"/>
     </row>
-    <row r="983" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>139</v>
       </c>
@@ -47430,6 +47856,7 @@
       <c r="O983">
         <v>138944.5</v>
       </c>
+      <c r="P983"/>
       <c r="Q983">
         <v>1.5</v>
       </c>
@@ -47438,7 +47865,7 @@
       </c>
       <c r="S983"/>
     </row>
-    <row r="984" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>139</v>
       </c>
@@ -47480,7 +47907,7 @@
       </c>
       <c r="S984"/>
     </row>
-    <row r="985" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>139</v>
       </c>
@@ -47505,6 +47932,7 @@
       <c r="O985">
         <v>139026.9</v>
       </c>
+      <c r="P985"/>
       <c r="Q985">
         <v>4.5</v>
       </c>
@@ -47538,6 +47966,7 @@
       <c r="O986">
         <v>139073.5</v>
       </c>
+      <c r="P986"/>
       <c r="Q986">
         <v>3.5</v>
       </c>
@@ -47546,7 +47975,7 @@
       </c>
       <c r="S986"/>
     </row>
-    <row r="987" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>139</v>
       </c>
@@ -47571,6 +48000,7 @@
       <c r="O987">
         <v>139513.5</v>
       </c>
+      <c r="P987"/>
       <c r="Q987">
         <v>1.5</v>
       </c>
@@ -47579,7 +48009,7 @@
       </c>
       <c r="S987"/>
     </row>
-    <row r="988" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>139</v>
       </c>
@@ -47604,6 +48034,7 @@
       <c r="O988">
         <v>139515.29999999999</v>
       </c>
+      <c r="P988"/>
       <c r="Q988">
         <v>2.5</v>
       </c>
@@ -47612,7 +48043,7 @@
       </c>
       <c r="S988"/>
     </row>
-    <row r="989" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>139</v>
       </c>
@@ -47645,7 +48076,7 @@
       </c>
       <c r="S989"/>
     </row>
-    <row r="990" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>139</v>
       </c>
@@ -47670,6 +48101,7 @@
       <c r="O990">
         <v>139531.29999999999</v>
       </c>
+      <c r="P990"/>
       <c r="Q990">
         <v>6.5</v>
       </c>
@@ -47678,7 +48110,7 @@
       </c>
       <c r="S990"/>
     </row>
-    <row r="991" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>139</v>
       </c>
@@ -47703,6 +48135,7 @@
       <c r="O991">
         <v>139543.5</v>
       </c>
+      <c r="P991"/>
       <c r="Q991">
         <v>2.5</v>
       </c>
@@ -47736,6 +48169,7 @@
       <c r="O992">
         <v>139544.29999999999</v>
       </c>
+      <c r="P992"/>
       <c r="Q992">
         <v>3.5</v>
       </c>
@@ -47776,7 +48210,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="994" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>139</v>
       </c>
@@ -47817,7 +48251,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="995" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>139</v>
       </c>
@@ -47858,7 +48292,7 @@
         <v>1.0569999999999999</v>
       </c>
     </row>
-    <row r="996" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>139</v>
       </c>
@@ -47883,6 +48317,7 @@
       <c r="O996">
         <v>139570.6</v>
       </c>
+      <c r="P996" s="4"/>
       <c r="Q996">
         <v>5.5</v>
       </c>
@@ -47890,7 +48325,7 @@
         <v>1.0109999999999999</v>
       </c>
     </row>
-    <row r="997" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>139</v>
       </c>
@@ -47924,6 +48359,7 @@
       <c r="O997">
         <v>139788</v>
       </c>
+      <c r="P997" s="4"/>
       <c r="Q997">
         <v>5.5</v>
       </c>
@@ -47931,7 +48367,7 @@
         <v>0.99199999999999999</v>
       </c>
     </row>
-    <row r="998" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>139</v>
       </c>
@@ -48004,7 +48440,7 @@
         <v>1.0669999999999999</v>
       </c>
     </row>
-    <row r="1000" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>139</v>
       </c>
@@ -48038,6 +48474,7 @@
       <c r="O1000">
         <v>139822</v>
       </c>
+      <c r="P1000" s="4"/>
       <c r="Q1000">
         <v>5.5</v>
       </c>
@@ -48045,7 +48482,7 @@
         <v>1.1419999999999999</v>
       </c>
     </row>
-    <row r="1001" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>139</v>
       </c>
@@ -48077,7 +48514,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="1002" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>139</v>
       </c>
@@ -48118,7 +48555,7 @@
         <v>1.1739999999999999</v>
       </c>
     </row>
-    <row r="1003" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>139</v>
       </c>
@@ -48150,7 +48587,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="1004" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>139</v>
       </c>
@@ -48182,7 +48619,7 @@
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="1005" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>139</v>
       </c>
@@ -48255,7 +48692,7 @@
         <v>1.1259999999999999</v>
       </c>
     </row>
-    <row r="1007" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>139</v>
       </c>
@@ -48296,7 +48733,7 @@
         <v>1.0149999999999999</v>
       </c>
     </row>
-    <row r="1008" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>139</v>
       </c>
@@ -48319,7 +48756,7 @@
         <v>0.51800000000000002</v>
       </c>
     </row>
-    <row r="1009" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>139</v>
       </c>
@@ -48342,7 +48779,7 @@
         <v>1.266</v>
       </c>
     </row>
-    <row r="1010" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>139</v>
       </c>
@@ -48365,7 +48802,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="1011" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>139</v>
       </c>
@@ -48388,7 +48825,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1012" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>139</v>
       </c>
@@ -48411,7 +48848,7 @@
         <v>1.1950000000000001</v>
       </c>
     </row>
-    <row r="1013" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>139</v>
       </c>
@@ -48457,7 +48894,7 @@
         <v>1.159</v>
       </c>
     </row>
-    <row r="1015" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>139</v>
       </c>
@@ -48503,7 +48940,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="1017" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>139</v>
       </c>
@@ -48535,7 +48972,7 @@
         <v>1.123</v>
       </c>
     </row>
-    <row r="1018" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>139</v>
       </c>
@@ -48560,6 +48997,7 @@
       <c r="O1018">
         <v>140970.6</v>
       </c>
+      <c r="P1018" s="4"/>
       <c r="Q1018">
         <v>5.5</v>
       </c>
@@ -48567,7 +49005,7 @@
         <v>0.96899999999999997</v>
       </c>
     </row>
-    <row r="1019" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>139</v>
       </c>
@@ -48590,7 +49028,7 @@
         <v>1.109</v>
       </c>
     </row>
-    <row r="1020" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>139</v>
       </c>
@@ -48622,7 +49060,7 @@
         <v>0.95699999999999996</v>
       </c>
     </row>
-    <row r="1021" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>139</v>
       </c>
@@ -48647,6 +49085,7 @@
       <c r="O1021">
         <v>140979.5</v>
       </c>
+      <c r="P1021" s="4"/>
       <c r="Q1021">
         <v>5.5</v>
       </c>
@@ -48695,7 +49134,7 @@
         <v>0.45300000000000001</v>
       </c>
     </row>
-    <row r="1023" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>139</v>
       </c>
@@ -48736,7 +49175,7 @@
         <v>2.1589999999999998</v>
       </c>
     </row>
-    <row r="1024" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>139</v>
       </c>
@@ -48777,7 +49216,7 @@
         <v>1.393</v>
       </c>
     </row>
-    <row r="1025" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>139</v>
       </c>
@@ -48811,6 +49250,7 @@
       <c r="O1025">
         <v>141422.70000000001</v>
       </c>
+      <c r="P1025"/>
       <c r="Q1025">
         <v>0.5</v>
       </c>
@@ -48819,7 +49259,7 @@
       </c>
       <c r="S1025"/>
     </row>
-    <row r="1026" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>139</v>
       </c>
@@ -48844,6 +49284,7 @@
       <c r="O1026">
         <v>141423.5</v>
       </c>
+      <c r="P1026"/>
       <c r="Q1026">
         <v>8.5</v>
       </c>
@@ -48852,7 +49293,7 @@
       </c>
       <c r="S1026"/>
     </row>
-    <row r="1027" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>139</v>
       </c>
@@ -48886,6 +49327,7 @@
       <c r="O1027">
         <v>141424.1</v>
       </c>
+      <c r="P1027"/>
       <c r="Q1027">
         <v>7.5</v>
       </c>
@@ -48894,7 +49336,7 @@
       </c>
       <c r="S1027"/>
     </row>
-    <row r="1028" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>139</v>
       </c>
@@ -48928,6 +49370,7 @@
       <c r="O1028">
         <v>141425.60000000001</v>
       </c>
+      <c r="P1028"/>
       <c r="Q1028">
         <v>2.5</v>
       </c>
@@ -48936,7 +49379,7 @@
       </c>
       <c r="S1028"/>
     </row>
-    <row r="1029" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>139</v>
       </c>
@@ -48970,6 +49413,7 @@
       <c r="O1029">
         <v>141426</v>
       </c>
+      <c r="P1029"/>
       <c r="Q1029">
         <v>1.5</v>
       </c>
@@ -49012,6 +49456,7 @@
       <c r="O1030">
         <v>141432.20000000001</v>
       </c>
+      <c r="P1030"/>
       <c r="Q1030">
         <v>3.5</v>
       </c>
@@ -49020,7 +49465,7 @@
       </c>
       <c r="S1030"/>
     </row>
-    <row r="1031" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>139</v>
       </c>
@@ -49054,6 +49499,7 @@
       <c r="O1031">
         <v>141432.79999999999</v>
       </c>
+      <c r="P1031"/>
       <c r="Q1031">
         <v>2.5</v>
       </c>
@@ -49062,7 +49508,7 @@
       </c>
       <c r="S1031"/>
     </row>
-    <row r="1032" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>139</v>
       </c>
@@ -49096,6 +49542,7 @@
       <c r="O1032">
         <v>141436</v>
       </c>
+      <c r="P1032"/>
       <c r="Q1032">
         <v>4.5</v>
       </c>
@@ -49104,7 +49551,7 @@
       </c>
       <c r="S1032"/>
     </row>
-    <row r="1033" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>139</v>
       </c>
@@ -49146,7 +49593,7 @@
       </c>
       <c r="S1033"/>
     </row>
-    <row r="1034" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>139</v>
       </c>
@@ -49180,6 +49627,7 @@
       <c r="O1034">
         <v>141437.70000000001</v>
       </c>
+      <c r="P1034"/>
       <c r="Q1034">
         <v>6.5</v>
       </c>
@@ -49188,7 +49636,7 @@
       </c>
       <c r="S1034"/>
     </row>
-    <row r="1035" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>139</v>
       </c>
@@ -49222,6 +49670,7 @@
       <c r="O1035">
         <v>141438.29999999999</v>
       </c>
+      <c r="P1035"/>
       <c r="Q1035">
         <v>4.5</v>
       </c>
@@ -49264,6 +49713,7 @@
       <c r="O1036">
         <v>141438.9</v>
       </c>
+      <c r="P1036"/>
       <c r="Q1036">
         <v>3.5</v>
       </c>
@@ -49272,7 +49722,7 @@
       </c>
       <c r="S1036"/>
     </row>
-    <row r="1037" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>139</v>
       </c>
@@ -49329,6 +49779,11 @@
         <filter val="e"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="16">
+      <filters>
+        <filter val="3.5"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
